--- a/data/Resources and Terminology for Healthcare Indsutry Trends Website.xlsx
+++ b/data/Resources and Terminology for Healthcare Indsutry Trends Website.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://impactadvisors3-my.sharepoint.com/personal/john_decicco_impact-advisors_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{15AE2BCB-BB6C-4B9B-9467-C99DEEA88F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6556BCE9-2C9C-42B7-87BC-20CBF2E3985C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{AE6C2486-B33D-41C7-9864-3BA3013F76A0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="1" xr2:uid="{AE6C2486-B33D-41C7-9864-3BA3013F76A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Healthcare Resources" sheetId="1" r:id="rId1"/>
     <sheet name="Healthcare Terminology " sheetId="2" r:id="rId2"/>
+    <sheet name="Today's Healthcare Signal " sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1829" uniqueCount="1000">
   <si>
     <t xml:space="preserve">Title of Source </t>
   </si>
@@ -774,6 +775,213 @@
     <t>When health care teams run short, physician burnout rises | American Medical Association</t>
   </si>
   <si>
+    <t xml:space="preserve">CPHQ: The Certified Professional In Healthcare Quality </t>
+  </si>
+  <si>
+    <t>NAHQ</t>
+  </si>
+  <si>
+    <t>NAHQ - What is CPHQ Certification? Goals + Requirements</t>
+  </si>
+  <si>
+    <t>AHRMM Essentials of Health Care Supply Chain Certificate Series</t>
+  </si>
+  <si>
+    <t>Essentials of Health Care Supply Chain Certificate Series | AHRMM</t>
+  </si>
+  <si>
+    <t>Certified Associate in Healthcare Information and Management Systems</t>
+  </si>
+  <si>
+    <t>HIMSS</t>
+  </si>
+  <si>
+    <t>CAHIMS: Certified Associate in Healthcare Information &amp; Management Systems | HIMSS</t>
+  </si>
+  <si>
+    <t>What are the Value-Based Programs?</t>
+  </si>
+  <si>
+    <t>CMS</t>
+  </si>
+  <si>
+    <t>https://www.cms.gov/medicare/quality/value-based-programs</t>
+  </si>
+  <si>
+    <t>Patient POS Collections Pose a Growing Problem for RCM Departments</t>
+  </si>
+  <si>
+    <t>Patient POS collections pose a growing problem for RCM departments | HFMA</t>
+  </si>
+  <si>
+    <t>Prior Authorization is Draining Revenue, Which is Why Automation Has Become a Strategic Imperative</t>
+  </si>
+  <si>
+    <t>Prior authorization is draining revenue, which is why automation has become a strategic imperative | HFMA</t>
+  </si>
+  <si>
+    <t>Medicare in the 21st Century: Understanding the Program to Promote Improvements</t>
+  </si>
+  <si>
+    <t>nih.gov</t>
+  </si>
+  <si>
+    <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11042511/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is Medicare: Coverage, Cost and Enrollment </t>
+  </si>
+  <si>
+    <t>U.S.news</t>
+  </si>
+  <si>
+    <t>What Is Medicare? Coverage, Cost and Eligibility| U.S. News</t>
+  </si>
+  <si>
+    <t>Medicaid: An Overview</t>
+  </si>
+  <si>
+    <t>Congress.gov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is the Difference Between Nonprofit and For-Profit Hospitals </t>
+  </si>
+  <si>
+    <t>Definitive Healthcare</t>
+  </si>
+  <si>
+    <t>Difference between for-profit and nonprofit hospitals</t>
+  </si>
+  <si>
+    <t>What's The Difference Between For-Profit and Nonprofit Hospitals</t>
+  </si>
+  <si>
+    <t>Healthcare Brew</t>
+  </si>
+  <si>
+    <t>What’s the difference between for-profit and nonprofit hospitals?</t>
+  </si>
+  <si>
+    <t>Certified Professional in Supply Management (CPSM)</t>
+  </si>
+  <si>
+    <t>ISM</t>
+  </si>
+  <si>
+    <t>CPSM® Certified Professional in Supply Management®</t>
+  </si>
+  <si>
+    <t>Certified in Planning &amp; Inventory Management (CPIM)</t>
+  </si>
+  <si>
+    <t>ASCM</t>
+  </si>
+  <si>
+    <t>Certified in Planning and Inventory Management - CPIM | ASCM</t>
+  </si>
+  <si>
+    <t>Certified Professional in Healthcare Quality (CPHQ)</t>
+  </si>
+  <si>
+    <t>Revenue Cycle Management in Healthcare Explained</t>
+  </si>
+  <si>
+    <t>Medical Billing Process Explained | Step-By-Step RCM Cycle</t>
+  </si>
+  <si>
+    <t>Medical Billing Process Explained | Step-by-Step RCM Cycle</t>
+  </si>
+  <si>
+    <t>New Reports Reveal the Impact of Health Insurance Coverage Denials on Americans</t>
+  </si>
+  <si>
+    <t>New report reveals the impact of health insurance coverage denials on Americans</t>
+  </si>
+  <si>
+    <t>How AI Can Heal Healthcare | Edmund Jackson | Tedx</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=7ZsyYCZB3Nw</t>
+  </si>
+  <si>
+    <t>AI in Healthcare Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johns Hopkins University </t>
+  </si>
+  <si>
+    <t>AI in Healthcare Program - Johns Hopkins University</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guiding The Flock: 3 Simple Rules to Improve Hospital -Wide Patient Flow. </t>
+  </si>
+  <si>
+    <t>IHI</t>
+  </si>
+  <si>
+    <t>Guiding the Flock: 3 Simple Rules to Improve Hospital-wide Patient Flow | Institute for Healthcare Improvement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Key Considerations For Revenue Cycle Outsourcing </t>
+  </si>
+  <si>
+    <t>Key Considerations for Revenue Cycle Outsourcing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Key Facts About Hospitals </t>
+  </si>
+  <si>
+    <t>KFF</t>
+  </si>
+  <si>
+    <t>Key Facts About Hospitals | KFF</t>
+  </si>
+  <si>
+    <t>A Look At Hospital Operating Margins In The United States</t>
+  </si>
+  <si>
+    <t>U.S. Hospital Operating Margins : Profit &amp; Cost Trends</t>
+  </si>
+  <si>
+    <t>From -2.2% to 16.5%: 37 Health Systems Ranked By Operating Margins in 2025</t>
+  </si>
+  <si>
+    <t>From -2.2% to 16.5%: 37 health systems ranked by operating margins in 2025</t>
+  </si>
+  <si>
+    <t>Understanding Medical Claims: What They Are and How They Work</t>
+  </si>
+  <si>
+    <t>HealthPartners</t>
+  </si>
+  <si>
+    <t>Understanding medical claims: What they are and how they work | HealthPartners Blog</t>
+  </si>
+  <si>
+    <t>Denial Management in Healthcare: Definitions, Types, and More</t>
+  </si>
+  <si>
+    <t>Medesk</t>
+  </si>
+  <si>
+    <t>Denial Management in Healthcare - Definition, Types, and More</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What Is a Claim Scrubber And Why It Matters More Than Ever </t>
+  </si>
+  <si>
+    <t>PGM</t>
+  </si>
+  <si>
+    <t>What Is a Claim Scrubber? How AI Improves Claim Scrubbing and Reduces Denials</t>
+  </si>
+  <si>
+    <t>Healthcare Supply Chain Management: Optimize Cost &amp; Efficiency</t>
+  </si>
+  <si>
+    <t>HealthcareReader</t>
+  </si>
+  <si>
     <t xml:space="preserve">Term Name </t>
   </si>
   <si>
@@ -807,9 +1015,6 @@
     <t>A claim is a request for payment that a healthcare provider submits to a payer, such as Medicare, Medicaid, or a commercial insurance company, for services provided to a patient</t>
   </si>
   <si>
-    <t>CMS</t>
-  </si>
-  <si>
     <t>A patient receives an X-ray at a hospital. After the visit is documented and coded, the hospital submits a claim to the patient's insurance company asking to be paid for the X-ray service.</t>
   </si>
   <si>
@@ -1788,9 +1993,6 @@
     <t>Margin improvement is the work of increasing the financial difference between revenue and expenses. In healthcare, this can mean improving reimbursement, reducing denials, increasing collections, controlling labor and supply costs, improving productivity, and redesigning operations without harming care quality.</t>
   </si>
   <si>
-    <t>KFF</t>
-  </si>
-  <si>
     <t>A hospital has rising supply costs, high contract labor expense, and delayed payments from claim denials. A margin improvement project may focus on reducing avoidable denials, improving staffing productivity, standardizing supplies, renegotiating vendor contracts, and increasing collections so the organization can become more financially sustainable while still protecting patient care.</t>
   </si>
   <si>
@@ -2152,6 +2354,693 @@
   </si>
   <si>
     <t>During a Lawson-to-Workday transition, the project team may load sample employee data into a Workday sandbox to test whether job titles, pay groups, departments, benefits, and security roles are mapping correctly. If something breaks or data looks wrong, they can fix it in the sandbox before going live.</t>
+  </si>
+  <si>
+    <t>Provider</t>
+  </si>
+  <si>
+    <t>A provider is an individual clinician or healthcare organization that delivers care or medical services to patients. This can include physicians, nurses, hospitals, clinics, health systems, specialists, urgent care centers, and other care delivery organizations.</t>
+  </si>
+  <si>
+    <t>A patient visits a cardiologist for chest pain. The cardiologist is the provider because they are delivering the medical service. If the patient has surgery at a hospital, the hospital is also considered a provider because it is delivering healthcare services to the patient.</t>
+  </si>
+  <si>
+    <t>A physician enterprise is the organized network of employed or affiliated physicians, advanced practice providers, clinics, and ambulatory practices that operate under a health system or healthcare organization. It focuses on managing provider productivity, clinic operations, access, referrals, compensation, revenue cycle performance, and alignment between physicians and the broader health system.</t>
+  </si>
+  <si>
+    <t>MGMA/HFMA</t>
+  </si>
+  <si>
+    <t>A health system owns multiple primary care clinics, specialty practices, and outpatient physician groups. The physician enterprise team monitors provider schedules, patient access, referral leakage, coding accuracy, physician compensation models, and clinic profitability to make sure the physician network supports both patient care and financial performance.</t>
+  </si>
+  <si>
+    <t>Panel Size</t>
+  </si>
+  <si>
+    <t>Panel size is the number of patients assigned to or actively managed by a provider, care team, or clinic. It is commonly used in primary care to measure provider workload, patient access, and capacity. A larger panel means the provider is responsible for more patients, which can affect appointment availability, care continuity, and staffing needs.</t>
+  </si>
+  <si>
+    <t>A primary care physician has 2,000 patients assigned to them. Leadership reviews the physician’s panel size and notices that appointment wait times are increasing. The clinic may add another provider, use advanced practice providers, or redistribute patients across the care team to improve access.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minutes by Specialty </t>
+  </si>
+  <si>
+    <t>Minutes by specialty refers to the amount of provider schedule time, appointment time, or clinical capacity allocated by medical specialty. It is often used to compare how long visits should take across specialties, evaluate provider productivity, build clinic templates, and understand patient access. Different specialties may require different appointment lengths based on complexity, documentation needs, procedures, and patient type.</t>
+  </si>
+  <si>
+    <t>MGMA/AMGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A health system reviews clinic templates and sees that primary care new patient visits are scheduled for 40 minutes, cardiology follow-ups for 20 minutes, and dermatology visits for 15 minutes. Leadership analyzes minutes by specialty to determine whether each specialty has enough appointment capacity, whether visit lengths are appropriate, and where access delays may be occurring. </t>
+  </si>
+  <si>
+    <t>Claim Submission</t>
+  </si>
+  <si>
+    <t>Claim submission is the process of sending a healthcare claim from a provider to a payer for reimbursement after services have been delivered. The claim includes patient information, provider information, diagnosis codes, procedure codes, dates of service, charges, and insurance details.</t>
+  </si>
+  <si>
+    <t>CMS/HFMA</t>
+  </si>
+  <si>
+    <t>A patient visits a hospital outpatient clinic for an X-ray. After the visit, the billing team creates a claim with the correct diagnosis and procedure codes and submits it electronically to the patient's insurance company for payment</t>
+  </si>
+  <si>
+    <t>Not-for-Profit Hospital</t>
+  </si>
+  <si>
+    <t>A not-for-profit hospital is a hospital that is organized to serve a community or charitable purpose rather than to generate profit for owners or shareholders. Any excess revenue is typically reinvested back into the hospital through facility improvements, community benefit programs, patient care services, staffing, technology, or expanded access to care.</t>
+  </si>
+  <si>
+    <t>IRS/AHA</t>
+  </si>
+  <si>
+    <t>A community health system earns more revenue than expenses in a given year. Instead of distributing profits to shareholders, the hospital uses the excess funds to expand its emergency department, invest in a new HER module, fund charity care, and support community health programs</t>
+  </si>
+  <si>
+    <t>For-Profit Hospital</t>
+  </si>
+  <si>
+    <t>A For-Profit Hospital is a hospital owned by investors, shareholders, or a private company with the goal of generating profit while delivering healthcare services. Unlike a Not-For-Profit hospital, excess revenue may be reinvested into operations or distributed to owners/shareholders.</t>
+  </si>
+  <si>
+    <t>AHA/CMS</t>
+  </si>
+  <si>
+    <t>A national hospital company owns multiple hospitals across different states. One hospital generates more revenue than expenses, and part of that profit may be used to expand services, purchase new technology, acquire other facilities, or return value to investors.</t>
+  </si>
+  <si>
+    <t>Value Chain</t>
+  </si>
+  <si>
+    <t>A value chain is the full set of activities an organization performs to create, deliver, and support a product or service. In healthcare, it helps show how different functions such as supply chain, clinical operations, revenue cycle, finance, IT, and patient access work together to deliver patient care and create organizational value.</t>
+  </si>
+  <si>
+    <t>Harvard Business Review</t>
+  </si>
+  <si>
+    <t>A hospital’s value chain may start with patient scheduling and registration, continue through clinical care delivery, pharmacy, supplies, documentation, billing, and collections, and end with follow-up care. A consultant may analyze the value chain to find where costs are too high, handoffs are inefficient, or patient experience is breaking down.</t>
+  </si>
+  <si>
+    <t>Benefits</t>
+  </si>
+  <si>
+    <t>Benefits are the healthcare services, treatments, medications, or procedures that an insurance plan agrees to cover for a member. Benefits determine what care is covered, what rules apply, and what portion of the cost may be paid by the payer versus the patient.</t>
+  </si>
+  <si>
+    <t>CMS/Healthcare.gov</t>
+  </si>
+  <si>
+    <t>A patient has insurance benefits that cover annual wellness visits, emergency care, specialist visits, and prescription drugs. Before a scheduled MRI, the provider verifies the patient’s benefits to confirm whether the MRI is covered, whether prior authorization is required, and how much the patient may owe.</t>
+  </si>
+  <si>
+    <t>Capitation</t>
+  </si>
+  <si>
+    <t>Capitation is a payment model where a provider or healthcare organization receives a fixed amount of money per patient for a set period of time, regardless of how many services the patient uses. The provider takes on more financial risk because they are paid the same amount whether the patient needs very little care or a large amount of care.</t>
+  </si>
+  <si>
+    <t>A primary care group is paid $40 per member per month to manage a group of patients. If a patient only comes in once, the provider still receives $40 that month. If another patient needs several visits, care coordination, and follow-up, the provider still receives $40, so the organization is incentivized to manage care efficiently and keep patients healthy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coinsurance </t>
+  </si>
+  <si>
+    <t>Coinsurance is the percentage of healthcare costs a patient is responsible for paying after their deductible has been met. Unlike a copay, which is usually a fixed dollar amount, coinsurance is based on a percentage of the allowed cost for the service.</t>
+  </si>
+  <si>
+    <t>A patient has a plan with 20% coinsurance after meeting their deductible. If the allowed amount for an MRI is $1,000, the insurance plan pays 80%, or $800, and the patient pays 20%, or $200.</t>
+  </si>
+  <si>
+    <t>PO Number</t>
+  </si>
+  <si>
+    <t>A PO number, or purchase order number, is the unique identifier assigned to a purchase order. It is used to track what was ordered, who approved it, the supplier, item quantities, pricing, delivery status, receiving, invoicing, and payment</t>
+  </si>
+  <si>
+    <t>A hospital orders 500 boxes of gloves from a medical supply distributor. The ERP system creates PO #458921. When the gloves arrive and the invoice is received, the supply chain and accounts payable teams use that PO number to match the order, receipt, and invoice before paying the vendor.</t>
+  </si>
+  <si>
+    <t>Lead Time</t>
+  </si>
+  <si>
+    <t>Lead time is the amount of time between when an order is placed and when the item or service is received and available for use. In healthcare supply chain, lead time is important because delays can cause stockouts, procedure delays, or urgent rush orders.</t>
+  </si>
+  <si>
+    <t>A hospital orders surgical gloves from a distributor on Monday, and the gloves arrive on Friday. The lead time is 4 days. If the hospital knows the lead time is 4 days, it must reorder early enough to avoid running out before the next shipment arrives.</t>
+  </si>
+  <si>
+    <t>Point of Use (POS)</t>
+  </si>
+  <si>
+    <t>Point of use is the specific location where supplies, medications, equipment, or products are actually consumed or used in patient care. In healthcare, this could be an operating room, nursing unit, procedure room, emergency department, or clinic.</t>
+  </si>
+  <si>
+    <t>A hospital stores IV start kits in the emergency department supply room because nurses use them there when starting IVs for patients. The emergency department is the point of use because that is where the supply is consumed during care delivery.</t>
+  </si>
+  <si>
+    <t>Just-in-Time (JIT)</t>
+  </si>
+  <si>
+    <t>Just-in-time, often called JIT, is an inventory strategy where supplies are ordered and delivered close to the time they are needed instead of being stored in large quantities. The goal is to reduce excess inventory, storage costs, and waste, but it can create risk if there are supplier delays, backorders, or sudden demand spikes.</t>
+  </si>
+  <si>
+    <t>A hospital uses just-in-time ordering for standard medical supplies so it does not have to store large amounts of gloves, syringes, and IV tubing. This helps reduce storage space and carrying costs, but if the distributor has a delay, the hospital may face a stockout and need to place an emergency order.</t>
+  </si>
+  <si>
+    <t>Contractors</t>
+  </si>
+  <si>
+    <t>Contractors are external workers hired for a specific project, time period, or skill need. They are not permanent employees of the organization and are often used when a company needs temporary support or specialized expertise.</t>
+  </si>
+  <si>
+    <t>IRS</t>
+  </si>
+  <si>
+    <t>A Hospital may bring in contractors to help cleanLawson employee data, validate Workday fields, or support HR operations during the Fulton acquisition without hiring permanent full-time employees.</t>
+  </si>
+  <si>
+    <t>Bandwidth</t>
+  </si>
+  <si>
+    <t>Bandwidth refers to a team's available capacity, time, and resources to take on work. In a business setting, saying a team "does not have bandwidth" means they are already stretched and may not be able to support additional responsibilities effectively.</t>
+  </si>
+  <si>
+    <t>A Hospital's HR may not have enough bandwidth to support the Fulton acquisition because the same team must manage daily HR operations while also helping with Lawson-to-Workday data conversion, payroll validation, benefits review, testing, and go-live support.</t>
+  </si>
+  <si>
+    <t>Staff Augmentation</t>
+  </si>
+  <si>
+    <t>Staff augmentation is when an organization brings in external workers or consultants temporarily to add capacity or specialized skills to an existing team. These resources support the client's team but usually do not become permanent employees</t>
+  </si>
+  <si>
+    <t>SHRM</t>
+  </si>
+  <si>
+    <t>A Hospital could use staff augmentation by bringing in temporary data conversion analysts, HRIS contractors, or payroll testing support to help the HR team manage the Fulton acquisition and Lawson-to-Workday transition.</t>
+  </si>
+  <si>
+    <t>Backfill Support</t>
+  </si>
+  <si>
+    <t>Backfill support is when an organization temporarily brings in someone to cover an employee's normal responsibilities so that employee can focus on another priority, project, or temporary need.</t>
+  </si>
+  <si>
+    <t>Organizations may use backfill support by bringing in a temporary HR operations specialist to handle daily employee questions and HR tickets while Lakeview's internal HR team focuses on the Fulton acquisition and Lawson-to-Workday data conversion.</t>
+  </si>
+  <si>
+    <t>Work Relative Value Unit (wRVU)</t>
+  </si>
+  <si>
+    <t>A Work Relative Value Unit, often called a wRVU, is a measure of the provider work effort required to perform a medical service or procedure. It reflects factors such as time, technical skill, mental effort, judgment, and stress involved in delivering care. Hospitals and physician groups often use wRVUs to measure provider productivity, compare workload across providers, and support physician compensation models.</t>
+  </si>
+  <si>
+    <t>CMS/MGMA</t>
+  </si>
+  <si>
+    <t>A cardiologist, primary care physician, and orthopedic surgeon may all generate different wRVUs based on the types and complexity of services they provide. If a physician compensation plan rewards productivity, leadership may review the provider’s total wRVUs to determine whether they are meeting expected productivity targets.</t>
+  </si>
+  <si>
+    <t>Claim Scrubber</t>
+  </si>
+  <si>
+    <t>A claim scrubber is software or system functionality that reviews healthcare claims for errors before they are submitted to a payer. It checks for issues such as missing patient information, invalid codes, modifier errors, medical necessity concerns, payer-specific billing rules, and formatting problems.</t>
+  </si>
+  <si>
+    <t>HFMA/CMS</t>
+  </si>
+  <si>
+    <t>Before a hospital submits claims to Medicare or a commercial payer, the claim scrubber flags a missing diagnosis code on an outpatient procedure claim. The billing team corrects the error before submission, helping prevent a denial or rejection.</t>
+  </si>
+  <si>
+    <t>Explanation of Benefits (EOB)</t>
+  </si>
+  <si>
+    <t>An Explanation of Benefits, often called an EOB, is a document sent by an insurance company to a patient after a claim is processed. It explains what services were billed, what the insurance plan covered, what the payer paid, what was denied or adjusted, and what amount the patient may owe. It is not a bill, but it helps the patient understand how the claim was handled.</t>
+  </si>
+  <si>
+    <t>A patient has an MRI at a hospital. A few weeks later, the patient receives an EOB showing the hospital billed $2,000, the payer allowed $1,200, insurance paid $900, and the patient may owe $300 due to coinsurance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Out-of-Pocket Maximum </t>
+  </si>
+  <si>
+    <t>The out-of-pocket maximum is the most a patient has to pay for covered healthcare services during a plan year. Once the patient reaches this limit through deductibles, copays, and coinsurance, the insurance plan usually pays 100% of covered in-network services for the rest of the plan year.</t>
+  </si>
+  <si>
+    <t>A patient’s insurance plan has a $6,000 out-of-pocket maximum. Throughout the year, the patient pays $2,000 toward their deductible, $1,500 in coinsurance, and $2,500 in copays. Once they reach $6,000 total, their insurance covers covered in-network care at 100% for the rest of the plan year.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safety Stock </t>
+  </si>
+  <si>
+    <t>Safety stock is extra inventory kept on hand to reduce the risk of running out of supplies when demand is higher than expected or when deliveries are delayed. In healthcare, safety stock is especially important for critical clinical supplies because a stockout can disrupt patient care.</t>
+  </si>
+  <si>
+    <t>AHRMM/APICS</t>
+  </si>
+  <si>
+    <t>A hospital normally uses 100 boxes of gloves per week, but keeps an additional 25 boxes as safety stock in case usage spikes or the supplier shipment is delayed. During flu season, the hospital may increase safety stock for masks, gloves, IV supplies, and testing materials to avoid shortages.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bill-Only Item </t>
+  </si>
+  <si>
+    <t>A bill-only item is a product, often an implant or surgical device, that is used during a procedure and billed after the case rather than being ordered through the normal purchase order process beforehand. These items are commonly tied to vendor representatives, physician preference items, implants, and operating room documentation.</t>
+  </si>
+  <si>
+    <t>AHRMM/HFMA</t>
+  </si>
+  <si>
+    <t>During an orthopedic surgery, a vendor representative brings several implant options. The surgeon uses one implant during the case. After the procedure, the hospital records the item, verifies the implant details, and processes it as a bill-only item so the vendor can be paid and the item can be charged appropriately to the patient encounter.</t>
+  </si>
+  <si>
+    <t>Application Programming Interface (API)</t>
+  </si>
+  <si>
+    <t>An API, or Application Programming Interface, is a way for two software systems to communicate and exchange data with each other. In healthcare and ERP environments, APIs are often used to connect systems such as EHRs, ERPs, scheduling platforms, billing systems, supply chain tools, and reporting applications.</t>
+  </si>
+  <si>
+    <t>A hospital’s scheduling system uses an API to send appointment data to another platform. In an ERP implementation, Workday may use APIs to exchange employee, vendor, payroll, or financial data with third-party systems.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gantt Chart </t>
+  </si>
+  <si>
+    <t>A gantt chart is a visual project schedule that shows tasks, timelines, durations, dependencies, and progress across a calendar. It helps project teams understand what work need to happen, when it needs to happen, and which tasks may overlap or depend on one another.</t>
+  </si>
+  <si>
+    <t>During a hospital systen implementation , the project manager uses a Gantt chart to show when discovery, design, data conversion, testing, training, cutover, and go-live activities will occur. If data conversion is delayed, the chart helps the team see how that delay could impact testing and go-live readiness.'</t>
+  </si>
+  <si>
+    <t>Steering Committee</t>
+  </si>
+  <si>
+    <t>A steering committee is a group of senior leaders and key decision-makers who provide oversight, direction, and approval for a project or program. They help resolve escalated issues, approve major decisions, monitor project health, and make sure the project stays aligned with organizational goals.</t>
+  </si>
+  <si>
+    <t>During a hospital system implementation, the steering committee may include the CFO, CHRO, CIO, supply chain leadership, and project sponsors. If the project team discovers that data conversion is behind schedule and could delay go-live, the issue may be escalated to the steering committee for a decision on timeline, staffing, or scope.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project Charter </t>
+  </si>
+  <si>
+    <t>A project charter is a formal document that authorizes a project and defines its purpose, objectives, scope, key stakeholders, roles, high-level timeline, risks, assumptions, and success criteria. It gives the project team direction and confirms leadership alignment before detailed work begins.</t>
+  </si>
+  <si>
+    <t>During a hospital ERP implementation, the project charter may state that the organization is moving from Lawson to Workday, identify the CHRO and CIO as sponsors, define which workstreams are included, outline major milestones, and establish what success looks like for go-live.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterfall Methodology </t>
+  </si>
+  <si>
+    <t>Waterfall methodology is a sequential project management approach where work moves through defined phases in order, such as discovery, requirements, design, build, testing, deployment, and support. Each phase is typically completed before the next phase begins, making it useful when scope, requirements, and timelines need to be clearly controlled.</t>
+  </si>
+  <si>
+    <t>In a hospital construction or facility expansion project, the team may follow a waterfall approach by first defining the project requirements, then completing architectural design, obtaining approvals, beginning construction, performing inspections, training staff on the new space, and finally opening the facility. For example, final inspections would not occur until construction is complete and the space is ready for review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retrospective </t>
+  </si>
+  <si>
+    <t>a retrospective is a meeting held after a sprint, project phase, or major milestone where the team reflects on what went well, what did not go well, and what should be improved going forward. The goal is continuous improvement, not blaming individuals.</t>
+  </si>
+  <si>
+    <t>After launching a new hospital patient portal feature, the project team holds a retrospective and realizes that patient instructions were unclear, call center volume increased, and testing did not include enough older patients. For the next release, they improve patient education materials, involve call center staff earlier, and test with a broader patient group.</t>
+  </si>
+  <si>
+    <t>Premium Pay</t>
+  </si>
+  <si>
+    <t>Premium pay is additional compensation paid above an employee’s regular base rate for specific work situations, such as overtime, night shifts, weekends, holidays, on-call work, or hard-to-fill shifts. In hospitals, premium pay is important because it can significantly increase labor costs, especially when staffing shortages require overtime or incentive shifts.</t>
+  </si>
+  <si>
+    <t>A hospital pays nurses their regular hourly rate plus an additional shift differential for working overnight. During a staffing shortage, the hospital may also offer extra incentive pay for weekend shifts, increasing total labor expense for that department.</t>
+  </si>
+  <si>
+    <t>Vacancy Rate</t>
+  </si>
+  <si>
+    <t>Vacancy rate is the percentage of approved positions that are currently unfilled. In hospitals, it helps leaders understand staffing gaps, recruiting needs, labor pressure, and the potential need for overtime, agency labor, or contract support.</t>
+  </si>
+  <si>
+    <t>A hospital nursing department has 100 approved RN positions, but 12 are currently open. The vacancy rate is 12%. Leadership may use this information to assess staffing risk, recruitment needs, and whether temporary labor is needed to maintain patient care coverage.</t>
+  </si>
+  <si>
+    <t>Float Pool</t>
+  </si>
+  <si>
+    <t>A float pool is a group of flexible employees who are not permanently assigned to one unit or department and can be deployed where staffing needs are highest. In hospitals, float pools are often used for nursing, patient care technicians, or other clinical roles to reduce staffing gaps, overtime, and reliance on agency labor.</t>
+  </si>
+  <si>
+    <t>AHA/HFMA</t>
+  </si>
+  <si>
+    <t>A hospital has a nursing float pool made up of experienced nurses who can work across medical-surgical, telemetry, and step-down units. If one unit has multiple call-outs or a sudden increase in patient census, the staffing office assigns float pool nurses to that unit to maintain safe coverage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Six Sigma </t>
+  </si>
+  <si>
+    <t>Six Sigma is a data-driven process improvement methodology focused on reducing defects, errors, and variation in a process. In healthcare, it is often used to improve quality, patient safety, efficiency, and consistency by identifying root causes of problems and using data to improve performance.</t>
+  </si>
+  <si>
+    <t>ASQ/IHI</t>
+  </si>
+  <si>
+    <t>A hospital laboratory notices frequent specimen labeling errors. The quality team uses Six Sigma methods to measure the error rate, identify where mistakes occur, improve the labeling workflow, and monitor results to reduce future defects.</t>
+  </si>
+  <si>
+    <t>Pay-for-Performance</t>
+  </si>
+  <si>
+    <t>Pay-for-performance is a healthcare payment model where providers or hospitals can receive financial rewards or penalties based on performance against defined quality, safety, efficiency, patient experience, or outcome measures. The goal is to encourage better care rather than paying only based on the volume of services delivered.</t>
+  </si>
+  <si>
+    <t>CMS/AHRQ</t>
+  </si>
+  <si>
+    <t>A hospital may receive incentive payments if it reduces readmissions, improves patient experience scores, lowers infection rates, or meets certain quality benchmarks. If performance is poor, the hospital may lose reimbursement or receive a payment penalty.</t>
+  </si>
+  <si>
+    <t>Preventive Care</t>
+  </si>
+  <si>
+    <t>Preventive care refers to healthcare services focused on preventing illness, detecting disease early, and reducing future health risks before they become more serious or costly. This can include screening, vaccines, annual wellness visits, counseling, and routine health checks.</t>
+  </si>
+  <si>
+    <t>A primary care clinic identifies patients who are overdue for flu shots, colon cancer screenings, and annual wellness visits. The clinic reaches out to schedule those services so health risks can be addressed early instead of waiting until patients become seriously ill.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variation </t>
+  </si>
+  <si>
+    <t>Variation refers to differences in how a process is performed or how outcomes occur across people, departments, locations, or time periods. In hospitals, reducing unnecessary variation helps improve consistency, quality, safety, efficiency, and patient experience.</t>
+  </si>
+  <si>
+    <t>IHI/ASQ</t>
+  </si>
+  <si>
+    <t>One hospital unit consistently discharges patients before noon, while another unit usually discharges patients late in the afternoon. A consultant may analyze this variation to understand differences in staffing, physician rounding, case management, transportation, or discharge planning processes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Throughput </t>
+  </si>
+  <si>
+    <t>Throughput is the movement of patients through the hospital from arrival to discharge. It measures how efficiently patients flow through care areas such as the emergency department, inpatient units, imaging, surgery, and discharge processes. Poor throughput can lead to long wait times, ED boarding, delayed admissions, capacity issues, and lower patient experience.</t>
+  </si>
+  <si>
+    <t>A hospital notices that admitted patients are waiting in the emergency department for several hours because inpatient beds are not opening quickly enough. A consultant may review discharge timing, bed management, transport delays, case management, and staffing to improve patient throughput.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vertical Integration </t>
+  </si>
+  <si>
+    <t>Vertical integration is when an organization expands across different stages of the healthcare value chain, such as a payer owning clinics, a hospital acquiring physician practices, or a health system operating post-acute facilities. The goal is often to improve coordination, control costs, retain patients, and manage care more effectively across settings.</t>
+  </si>
+  <si>
+    <t>HFMA/KFF</t>
+  </si>
+  <si>
+    <t>A health system acquires primary care practices, urgent care centers, and home health services so it can manage patients before, during, and after hospital care instead of only treating them inside the hospital.</t>
+  </si>
+  <si>
+    <t>Horizontal Integration</t>
+  </si>
+  <si>
+    <t>Horizontal integration is when an organization expands by acquiring, merging with, or partnering with organizations that operate at the same level of the healthcare value chain. In healthcare, this often means one hospital acquiring another hospital, one physician group merging with another physician group, or one health system expanding its footprint through similar facilities.</t>
+  </si>
+  <si>
+    <t>A large health system acquires another hospital in the same region to increase market share, expand patient access, reduce duplicative services, and strengthen negotiating power with payers.</t>
+  </si>
+  <si>
+    <t>Episode of Care</t>
+  </si>
+  <si>
+    <t>An episode of care is the full set of healthcare services provided to treat a patient for a specific condition, procedure, or health event over a defined period of time. It may include the initial visit, hospital stay, physician services, medications, follow-up appointments, rehabilitation, and post-acute care.</t>
+  </si>
+  <si>
+    <t>For a knee replacement, the episode of care may include the pre-surgery consultation, the surgery itself, inpatient hospital services, physical therapy, follow-up visits, and any related complications within a set time window.</t>
+  </si>
+  <si>
+    <t>EBITDA</t>
+  </si>
+  <si>
+    <t>EBITDA stands for Earnings Before Interest, Taxes, Depreciation, and Amortization. It is a profitability metric used to estimate how much a business earns from operations before financing decisions, tax effects, and certain non-cash expenses are included.</t>
+  </si>
+  <si>
+    <t>Corporate Finance Institute</t>
+  </si>
+  <si>
+    <t>A healthcare consulting team may review a hospital’s EBITDA to understand operating profitability before considering debt costs, taxes, depreciation on buildings/equipment, and amortization of intangible assets.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Capital </t>
+  </si>
+  <si>
+    <t>Working capital measures the short-term financial resources an organization has available to run daily operations. It is commonly calculated as current assets minus current liabilities. In healthcare, it helps show whether a hospital or health system has enough liquidity to cover near-term expenses such as payroll, supplies, vendor payments, and other operating needs.</t>
+  </si>
+  <si>
+    <t>A hospital with strong working capital can pay employees, purchase medical supplies, cover vendor invoices, and manage cash flow while waiting for reimbursement from Medicare, Medicaid, Commercial payers, or patients.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Daily Census </t>
+  </si>
+  <si>
+    <t>Average Daily Census is the average number of patients in a hospital, unit, or care area per day over a specific period of time. It is commonly used to understand patient volume, staffing needs, bed utilization, and operational capacity.</t>
+  </si>
+  <si>
+    <t>If a hospital medical-surgical unit had 900 total patient days in a 30-day month, its average census would be 30 patients per day. Leaders may use this number to decide whether nurse staffing levels match patient volume.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupancy Rate </t>
+  </si>
+  <si>
+    <t>Occupancy rate measures the percentage of available beds that are occupied by patients over a specific period of time. It helps hospitals understand capacity, patient volume, bed utilization, and whether they may be over or under capacity.</t>
+  </si>
+  <si>
+    <t>If a hospital has 100 staffed beds and an average of 85 beds are occupied, the occupancy rate is 85%. Leaders may use this metric to determine whether they need more beds, better discharge planning, or improved patient throughput.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bottleneck </t>
+  </si>
+  <si>
+    <t>A bottleneck is a point in a process where work slows down because demand exceeds capacity, causing delays, backlogs, or reduced throughput. In healthcare, bottlenecks often occur in areas like patient registration, bed assignment, imaging, lab turnaround, discharge, or prior authorization.</t>
+  </si>
+  <si>
+    <t>IHI/Lean Six Sigma</t>
+  </si>
+  <si>
+    <t>If the emergency department has patients ready to be admitted but no inpatient beds are available, bed availability becomes the bottleneck. This can delay patient movement, increase wait times, and reduce overall hospital throughput.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Patient Lag </t>
+  </si>
+  <si>
+    <t>New patient lage is the amount of time between when a new patient requests or is referred for an appointment and when they are actually seen by a provider. It is commonly used to measure patient access, scheduling capacity, and referral efficiency.</t>
+  </si>
+  <si>
+    <t>MGMA/IHI</t>
+  </si>
+  <si>
+    <t>If a new cardiology patient calls on July 1 and the first available appointment is July 29, the new patient lag is 28 days. A high new patient lag may signal provider capacity issues, inefficient scheduling templates, or referral bottlenecks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upside Risk </t>
+  </si>
+  <si>
+    <t>Upside risk is a value-based care arrangement where a provider can earn additional payment or shared savings if they meet cost and quality targets, but they are not financially penalized if performance is worse than expected. It is generally considered a lower-risk entry point into value-based care.</t>
+  </si>
+  <si>
+    <t>An accountable care organization reduces avoidable hospitalizations and total cost of care while meeting quality measures. Because it is in an upside-risk arrangement, it receives a portion of the savings but does not owe money back if costs exceed the benchmark.</t>
+  </si>
+  <si>
+    <t>Downside Risk</t>
+  </si>
+  <si>
+    <t>Downside risk is a value-based care arrangement where a provider may have to repay money or absorb financial losses if they do not meet agreed-upon cost, quality, or performance targets. It is considered a more advanced risk model because the provider is financially accountable for poor performance, not just rewarded for strong performance.</t>
+  </si>
+  <si>
+    <t>An accountable care organization agrees to manage a patient population under a shared-risk contract. If total cost of care is higher than the benchmark and quality goals are not met, the organization may owe money back to the payer.</t>
+  </si>
+  <si>
+    <t>Master Patient Index</t>
+  </si>
+  <si>
+    <t>A Master Patient Index is a system or database that maintains a unique record for each patient across an organization’s systems. It helps match patient identities, reduce duplicate records, and ensure clinical, billing, and demographic information connects to the correct person.</t>
+  </si>
+  <si>
+    <t>ONC/HealthIT.gov</t>
+  </si>
+  <si>
+    <t>During a hospital acquisition, the project team may compare patient records from the acquired hospital's legacy system against the parent health system's MPI to prevent duplicate patient records and make sure claims, appointments, and medical history are tied to the right patient.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic </t>
+  </si>
+  <si>
+    <t>Epic is one of the largest electronic health record, or EHR, platforms used by hospitals and health systems to manage clinical documentation, patient records, scheduling, orders, billing workflows, and patient-facing tools. In healthcare consulting, Epic is often discussed as a major player in the clinical and revenue cycle technology space, not usually as the core ERP system.</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>A health system may use Epic for patient registration, physician documentation, lab orders, medication records, MyChart patient communication, and charge capture. During an ERP project, consultants may need to understand how Epic connects with systems like Workday or Oracle for billing, staffing, finance, or supply chain data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle </t>
+  </si>
+  <si>
+    <t>Oracle is a major enterprise software company that provides cloud-based ERP applications for finance, supply chain, procurement, human capital management, reporting, and enterprise operations. In healthcare, Oracle is a big player in the ERP and enterprise technology space, especially for organizations looking to manage back-office operations across finance, HR, and supply chain.</t>
+  </si>
+  <si>
+    <t>A hospital may use Oracle Cloud ERP to manage general ledger, accounts payable, procurement, inventory, vendor management, financial reporting, and supply chain operations across the health system.</t>
+  </si>
+  <si>
+    <t>Workday is a major cloud-based ERP platform focused heavily on human capital management, finance, payroll, workforce planning, analytics, and enterprise operations. In healthcare, Workday is a big player in the HR, finance, and cloud ERP space, especially for health systems modernizing from legacy platforms like Lawson.</t>
+  </si>
+  <si>
+    <t>A health system may use Workday to manage employee records, job profiles, compensation, benefits, payroll, position management, recruiting, finance, and reporting. During an acquisition, consultants may help move employee and finance data from a legacy system into Workday.</t>
+  </si>
+  <si>
+    <t>Post-Merger Integration</t>
+  </si>
+  <si>
+    <t>Post-merger integration is the process of combining two organizations after a merger or acquisition so they can operate as one coordinated entity. In healthcare, this may include aligning leadership, operations, technology systems, HR policies, finance processes, supply chain contracts, clinical workflows, reporting structures, and culture.</t>
+  </si>
+  <si>
+    <t>PMI/HFMA</t>
+  </si>
+  <si>
+    <t>After a health system acquires a smaller hospital, the post-merger integration team may help move the acquired hospital from Lawson to Workday, standardize HR and finance processes, align vendor contracts, integrate reporting, and prepare employees for new workflows.</t>
+  </si>
+  <si>
+    <t>Net Promoter Score (NPS)</t>
+  </si>
+  <si>
+    <t>Net Promoter Score is a customer or patient experience metric that measures how likely someone is to recommend an organization, service, provider, or care experience to others. It is commonly calculated from survey responses and used to understand loyalty, satisfaction, and overall experience.</t>
+  </si>
+  <si>
+    <t>Bain &amp; Co</t>
+  </si>
+  <si>
+    <t>A health system may ask patients, "How likely are you to recommend this clinic to a friend or family member?" If scores are low, leaders may investigate wait times, communications, scheduling issues, or provider experience to improve patient satisfaction.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contribution Margin </t>
+  </si>
+  <si>
+    <t>Contribution margin is the revenue remaining after variable costs are deducted. It helps determine how much a service contributes toward covering fixed costs and generating profits.</t>
+  </si>
+  <si>
+    <t>Orthopedic surgery may have strong contribution margin if reimbursement is high and implant costs are well managed.</t>
+  </si>
+  <si>
+    <t>Indirect costs</t>
+  </si>
+  <si>
+    <t>Indirect costs are expenses that support operations but are not easily tied to one specific patient or procedure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A hospital's building lease, salaried leadership, and depreciation expenses may remain relatively fixed even if patient volume changes. </t>
+  </si>
+  <si>
+    <t>Capital Expenditure</t>
+  </si>
+  <si>
+    <t>Capital expenditure, or CapEx, refers to spending on long-term assets such as buildings, major equipment, technology, or infrastructure.</t>
+  </si>
+  <si>
+    <t>A hospital purchasing a new MRI machine records it as a capital expenditure.</t>
+  </si>
+  <si>
+    <t>Accounts Receivables (A/R)</t>
+  </si>
+  <si>
+    <t>Accounts receivable is the money owed to a healthcare organization for services that have already been provided but have not yet been collected from payers or patients. In healthcare, A/R is closely tied to billing, claims follow-up, payer reimbursement, denials, and patient collections.</t>
+  </si>
+  <si>
+    <t>A hospital performs a surgery, submits the claim to the patient’s insurance company, and waits for payment. Until the payer or patient pays, that outstanding balance sits in accounts receivable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding </t>
+  </si>
+  <si>
+    <t>Coding is the revenue cycle process of converting clinical documentation into standardized medical codes, such as diagnosis codes, procedure codes, and service codes. These codes help determine what was done, why it was medically necessary, and how the provider should be reimbursed</t>
+  </si>
+  <si>
+    <t>CMS/AHIMA</t>
+  </si>
+  <si>
+    <t>A patient is treated for pneumonia during an inpatient stay. The provider documents the diagnosis, treatment, medications, and procedures. A medical coder reviews the documentation and assigns the correct ICD-10 diagnosis code and procedure codes so the hospital can submit an accurate claim to the payer.</t>
+  </si>
+  <si>
+    <t>Website Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link </t>
+  </si>
+  <si>
+    <t>HFMA.org</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beckers Hospital Review </t>
+  </si>
+  <si>
+    <t>Becker's Hospital Review | Healthcare News &amp; Analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beckers Supply Chain </t>
+  </si>
+  <si>
+    <t>Supply Chain Archives - Becker's Hospital Review | Healthcare News &amp; Analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beckers Clinical Leadership </t>
+  </si>
+  <si>
+    <t>Becker's Clinical Leadership Archives - Becker's Hospital Review | Healthcare News &amp; Analysis</t>
+  </si>
+  <si>
+    <t>American College of Healthcare Executives | American College of Healthcare Executives</t>
+  </si>
+  <si>
+    <t>MGMA.com</t>
+  </si>
+  <si>
+    <t>Medical Group Management Association - MGMA</t>
+  </si>
+  <si>
+    <t>CMS.gov</t>
+  </si>
+  <si>
+    <t>MLN Matters® Articles | CMS</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>HIMSS.org</t>
+  </si>
+  <si>
+    <t>Healthcare Information and Management Systems Society | HIMSS</t>
+  </si>
+  <si>
+    <t>IHI.org</t>
+  </si>
+  <si>
+    <t>Home | Institute for Healthcare Improvement</t>
+  </si>
+  <si>
+    <t>NAHQ.org</t>
+  </si>
+  <si>
+    <t>Home - NAHQ</t>
+  </si>
+  <si>
+    <t>https://www.ahrmm.org/</t>
   </si>
 </sst>
 </file>
@@ -2202,11 +3091,20 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -2215,12 +3113,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2242,8 +3143,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A2C3F0C7-761E-4B5C-A66C-E7C10F64F36F}" name="Table4" displayName="Table4" ref="A1:F106" totalsRowShown="0">
-  <autoFilter ref="A1:F106" xr:uid="{A2C3F0C7-761E-4B5C-A66C-E7C10F64F36F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A2C3F0C7-761E-4B5C-A66C-E7C10F64F36F}" name="Table4" displayName="Table4" ref="A1:F134" totalsRowShown="0">
+  <autoFilter ref="A1:F134" xr:uid="{A2C3F0C7-761E-4B5C-A66C-E7C10F64F36F}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{3A186EF0-DE4D-4AF5-9E14-55E37A3897F0}" name="Title of Source "/>
     <tableColumn id="2" xr3:uid="{431EDF38-AFCC-4E7A-8DE6-340618238528}" name="Website"/>
@@ -2257,14 +3158,25 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3A77FCFC-C270-4744-BFD3-3F97DC940B05}" name="Table5" displayName="Table5" ref="A1:E140" totalsRowShown="0">
-  <autoFilter ref="A1:E140" xr:uid="{3A77FCFC-C270-4744-BFD3-3F97DC940B05}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3A77FCFC-C270-4744-BFD3-3F97DC940B05}" name="Table5" displayName="Table5" ref="A1:E201" totalsRowShown="0">
+  <autoFilter ref="A1:E201" xr:uid="{3A77FCFC-C270-4744-BFD3-3F97DC940B05}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{6D94F78D-1D88-44BF-BBF7-E41A3F3189C7}" name="Term Name "/>
     <tableColumn id="4" xr3:uid="{DAAC4614-0F72-4E8E-BC14-F93F50235DB0}" name="Category "/>
     <tableColumn id="2" xr3:uid="{A014C31F-4B3E-4BF3-8DD8-B9FB470372C9}" name="Definition "/>
     <tableColumn id="5" xr3:uid="{71B94FD6-3256-47AB-830E-EB8F5B3204BD}" name="Source"/>
     <tableColumn id="3" xr3:uid="{8A59A37A-1B86-4E7C-AC63-A513FA4A9B90}" name="Real World Example"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{784C7AC4-9FB5-4B70-80B8-CEDD6F54E6AD}" name="Table1" displayName="Table1" ref="A1:B13" totalsRowShown="0">
+  <autoFilter ref="A1:B13" xr:uid="{784C7AC4-9FB5-4B70-80B8-CEDD6F54E6AD}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{A6B81BD4-499C-446C-B47D-C4E5B034153F}" name="Website Name"/>
+    <tableColumn id="3" xr3:uid="{90F40EED-2070-4DA8-9D31-3E64E20D5963}" name="Link "/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2587,10 +3499,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55440D71-C7D2-4E96-BABC-0BFC761058E3}">
-  <dimension ref="A1:F106"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="80.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="83.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="20.42578125" customWidth="1"/>
     <col min="5" max="5" width="35.140625" bestFit="1" customWidth="1"/>
@@ -4650,6 +5562,12 @@
       <c r="C103" t="s">
         <v>106</v>
       </c>
+      <c r="D103" t="s">
+        <v>134</v>
+      </c>
+      <c r="E103" t="s">
+        <v>19</v>
+      </c>
       <c r="F103" s="1" t="s">
         <v>236</v>
       </c>
@@ -4704,11 +5622,574 @@
       <c r="C106" t="s">
         <v>106</v>
       </c>
+      <c r="D106" t="s">
+        <v>111</v>
+      </c>
       <c r="E106" t="s">
         <v>10</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>243</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" t="s">
+        <v>244</v>
+      </c>
+      <c r="B107" t="s">
+        <v>245</v>
+      </c>
+      <c r="C107" t="s">
+        <v>102</v>
+      </c>
+      <c r="D107" t="s">
+        <v>54</v>
+      </c>
+      <c r="E107" t="s">
+        <v>10</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" t="s">
+        <v>247</v>
+      </c>
+      <c r="B108" t="s">
+        <v>187</v>
+      </c>
+      <c r="C108" t="s">
+        <v>102</v>
+      </c>
+      <c r="D108" t="s">
+        <v>45</v>
+      </c>
+      <c r="E108" t="s">
+        <v>10</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" t="s">
+        <v>249</v>
+      </c>
+      <c r="B109" t="s">
+        <v>250</v>
+      </c>
+      <c r="C109" t="s">
+        <v>102</v>
+      </c>
+      <c r="D109" t="s">
+        <v>9</v>
+      </c>
+      <c r="E109" t="s">
+        <v>10</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" t="s">
+        <v>252</v>
+      </c>
+      <c r="B110" t="s">
+        <v>253</v>
+      </c>
+      <c r="C110" t="s">
+        <v>106</v>
+      </c>
+      <c r="D110" t="s">
+        <v>54</v>
+      </c>
+      <c r="E110" t="s">
+        <v>10</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111" t="s">
+        <v>255</v>
+      </c>
+      <c r="B111" t="s">
+        <v>105</v>
+      </c>
+      <c r="C111" t="s">
+        <v>106</v>
+      </c>
+      <c r="D111" t="s">
+        <v>36</v>
+      </c>
+      <c r="E111" t="s">
+        <v>10</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" t="s">
+        <v>257</v>
+      </c>
+      <c r="B112" t="s">
+        <v>105</v>
+      </c>
+      <c r="C112" t="s">
+        <v>106</v>
+      </c>
+      <c r="D112" t="s">
+        <v>36</v>
+      </c>
+      <c r="E112" t="s">
+        <v>19</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" t="s">
+        <v>259</v>
+      </c>
+      <c r="B113" t="s">
+        <v>260</v>
+      </c>
+      <c r="C113" t="s">
+        <v>106</v>
+      </c>
+      <c r="D113" t="s">
+        <v>13</v>
+      </c>
+      <c r="E113" t="s">
+        <v>10</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" t="s">
+        <v>262</v>
+      </c>
+      <c r="B114" t="s">
+        <v>263</v>
+      </c>
+      <c r="C114" t="s">
+        <v>106</v>
+      </c>
+      <c r="D114" t="s">
+        <v>13</v>
+      </c>
+      <c r="E114" t="s">
+        <v>10</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115" t="s">
+        <v>265</v>
+      </c>
+      <c r="B115" t="s">
+        <v>266</v>
+      </c>
+      <c r="C115" t="s">
+        <v>106</v>
+      </c>
+      <c r="D115" t="s">
+        <v>13</v>
+      </c>
+      <c r="E115" t="s">
+        <v>19</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116" t="s">
+        <v>267</v>
+      </c>
+      <c r="B116" t="s">
+        <v>268</v>
+      </c>
+      <c r="C116" t="s">
+        <v>106</v>
+      </c>
+      <c r="D116" t="s">
+        <v>13</v>
+      </c>
+      <c r="E116" t="s">
+        <v>10</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
+      <c r="A117" t="s">
+        <v>270</v>
+      </c>
+      <c r="B117" t="s">
+        <v>271</v>
+      </c>
+      <c r="C117" t="s">
+        <v>106</v>
+      </c>
+      <c r="D117" t="s">
+        <v>13</v>
+      </c>
+      <c r="E117" t="s">
+        <v>10</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118" t="s">
+        <v>273</v>
+      </c>
+      <c r="B118" t="s">
+        <v>274</v>
+      </c>
+      <c r="C118" t="s">
+        <v>102</v>
+      </c>
+      <c r="D118" t="s">
+        <v>45</v>
+      </c>
+      <c r="E118" t="s">
+        <v>10</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="A119" t="s">
+        <v>276</v>
+      </c>
+      <c r="B119" t="s">
+        <v>277</v>
+      </c>
+      <c r="C119" t="s">
+        <v>102</v>
+      </c>
+      <c r="D119" t="s">
+        <v>45</v>
+      </c>
+      <c r="E119" t="s">
+        <v>10</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
+      <c r="A120" t="s">
+        <v>279</v>
+      </c>
+      <c r="B120" t="s">
+        <v>245</v>
+      </c>
+      <c r="C120" t="s">
+        <v>102</v>
+      </c>
+      <c r="D120" t="s">
+        <v>54</v>
+      </c>
+      <c r="E120" t="s">
+        <v>10</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121" t="s">
+        <v>280</v>
+      </c>
+      <c r="B121" t="s">
+        <v>174</v>
+      </c>
+      <c r="C121" t="s">
+        <v>175</v>
+      </c>
+      <c r="D121" t="s">
+        <v>36</v>
+      </c>
+      <c r="E121" t="s">
+        <v>10</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
+      <c r="A122" t="s">
+        <v>281</v>
+      </c>
+      <c r="B122" t="s">
+        <v>174</v>
+      </c>
+      <c r="C122" t="s">
+        <v>175</v>
+      </c>
+      <c r="D122" t="s">
+        <v>36</v>
+      </c>
+      <c r="E122" t="s">
+        <v>10</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="A123" t="s">
+        <v>283</v>
+      </c>
+      <c r="B123" t="s">
+        <v>174</v>
+      </c>
+      <c r="C123" t="s">
+        <v>175</v>
+      </c>
+      <c r="D123" t="s">
+        <v>13</v>
+      </c>
+      <c r="E123" t="s">
+        <v>10</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
+      <c r="A124" t="s">
+        <v>285</v>
+      </c>
+      <c r="B124" t="s">
+        <v>174</v>
+      </c>
+      <c r="C124" t="s">
+        <v>175</v>
+      </c>
+      <c r="D124" t="s">
+        <v>13</v>
+      </c>
+      <c r="E124" t="s">
+        <v>10</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
+      <c r="A125" t="s">
+        <v>287</v>
+      </c>
+      <c r="B125" t="s">
+        <v>288</v>
+      </c>
+      <c r="C125" t="s">
+        <v>102</v>
+      </c>
+      <c r="D125" t="s">
+        <v>13</v>
+      </c>
+      <c r="E125" t="s">
+        <v>19</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="A126" t="s">
+        <v>290</v>
+      </c>
+      <c r="B126" t="s">
+        <v>291</v>
+      </c>
+      <c r="C126" t="s">
+        <v>106</v>
+      </c>
+      <c r="D126" t="s">
+        <v>9</v>
+      </c>
+      <c r="E126" t="s">
+        <v>10</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="A127" t="s">
+        <v>293</v>
+      </c>
+      <c r="B127" t="s">
+        <v>105</v>
+      </c>
+      <c r="C127" t="s">
+        <v>106</v>
+      </c>
+      <c r="D127" t="s">
+        <v>36</v>
+      </c>
+      <c r="E127" t="s">
+        <v>10</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="A128" t="s">
+        <v>295</v>
+      </c>
+      <c r="B128" t="s">
+        <v>296</v>
+      </c>
+      <c r="C128" t="s">
+        <v>106</v>
+      </c>
+      <c r="D128" t="s">
+        <v>13</v>
+      </c>
+      <c r="E128" t="s">
+        <v>10</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="A129" t="s">
+        <v>298</v>
+      </c>
+      <c r="B129" t="s">
+        <v>268</v>
+      </c>
+      <c r="C129" t="s">
+        <v>106</v>
+      </c>
+      <c r="D129" t="s">
+        <v>13</v>
+      </c>
+      <c r="E129" t="s">
+        <v>10</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="A130" t="s">
+        <v>300</v>
+      </c>
+      <c r="B130" t="s">
+        <v>149</v>
+      </c>
+      <c r="C130" t="s">
+        <v>106</v>
+      </c>
+      <c r="D130" t="s">
+        <v>13</v>
+      </c>
+      <c r="E130" t="s">
+        <v>19</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
+      <c r="A131" t="s">
+        <v>302</v>
+      </c>
+      <c r="B131" t="s">
+        <v>303</v>
+      </c>
+      <c r="C131" t="s">
+        <v>106</v>
+      </c>
+      <c r="D131" t="s">
+        <v>13</v>
+      </c>
+      <c r="E131" t="s">
+        <v>10</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="A132" t="s">
+        <v>305</v>
+      </c>
+      <c r="B132" t="s">
+        <v>306</v>
+      </c>
+      <c r="C132" t="s">
+        <v>106</v>
+      </c>
+      <c r="D132" t="s">
+        <v>13</v>
+      </c>
+      <c r="E132" t="s">
+        <v>10</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="A133" t="s">
+        <v>308</v>
+      </c>
+      <c r="B133" t="s">
+        <v>309</v>
+      </c>
+      <c r="C133" t="s">
+        <v>106</v>
+      </c>
+      <c r="D133" t="s">
+        <v>36</v>
+      </c>
+      <c r="E133" t="s">
+        <v>10</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="A134" t="s">
+        <v>311</v>
+      </c>
+      <c r="B134" t="s">
+        <v>312</v>
+      </c>
+      <c r="C134" t="s">
+        <v>106</v>
+      </c>
+      <c r="D134" t="s">
+        <v>45</v>
+      </c>
+      <c r="E134" t="s">
+        <v>10</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -4819,17 +6300,45 @@
     <hyperlink ref="F104" r:id="rId103" display="https://www.hfma.org/fast-finance/hospital-labor-trends-in-2025-show-slower-hiring-but-continued-workforce-growth/" xr:uid="{B0736A7F-D913-4F73-851B-F05549530245}"/>
     <hyperlink ref="F105" r:id="rId104" display="https://www.hfma.org/how-a-health-system-can-reduce-premium-labor-while-building-a-sustainable-workforce/" xr:uid="{8BC4E5B2-6187-46B1-9AF1-FE48BB0CC1E9}"/>
     <hyperlink ref="F106" r:id="rId105" display="https://www.ama-assn.org/practice-management/physician-health/when-health-care-teams-run-short-physician-burnout-rises" xr:uid="{65DE0C67-E3A2-4C5A-ADA4-65C4C20C03CB}"/>
+    <hyperlink ref="F107" r:id="rId106" display="https://nahq.org/credentials/cphq-certified-professional-in-healthcare-quality/?keyword=certified%20professional%20in%20healthcare%20quality%20cphq&amp;matchtype=e&amp;device=c&amp;lpurl=https%3A%2F%2Fnahq.org%2Fcredentials%2Fcphq-certified-professional-in-healthcare-quality%2F&amp;campaign=Microsoft%20-%20CPHQ&amp;adgroup=CPHQ%20-%20General&amp;msclkid=c95bc5130bb019a47546af568a0234f8&amp;utm_source=bing&amp;utm_medium=cpc&amp;utm_campaign=Microsoft%20-%20CPHQ&amp;utm_term=certified%20professional%20in%20healthcare%20quality%20cphq&amp;utm_content=CPHQ%20-%20General" xr:uid="{2135AC31-B441-4060-B91F-8896C3CE4900}"/>
+    <hyperlink ref="F108" r:id="rId107" display="https://www.ahrmm.org/resource-repository-ahrmm/essentials-certificate-bundle-1" xr:uid="{0985B110-A074-44A6-9B8A-EF99637976E3}"/>
+    <hyperlink ref="F109" r:id="rId108" display="https://www.himss.org/certifications/cahims/" xr:uid="{3DEAE48F-4440-4AC7-931B-06FA9BBF28A8}"/>
+    <hyperlink ref="F110" r:id="rId109" xr:uid="{3D40C12B-AC12-4AA6-9011-94F6C4A8A329}"/>
+    <hyperlink ref="F111" r:id="rId110" display="https://www.hfma.org/revenue-cycle/billing-and-collections/patient-pos-collections-pose-a-growing-rcm-problem/" xr:uid="{23C8C91C-3AE3-4ECE-A00A-71F4444F3999}"/>
+    <hyperlink ref="F112" r:id="rId111" display="https://www.hfma.org/revenue-cycle/billing-and-collections/prior-authorization-is-draining-revenue-which-is-why-automation-has-become-a-strategic-imperative/" xr:uid="{5F97E33A-3A37-4F35-A16C-F1C8048400F2}"/>
+    <hyperlink ref="F113" r:id="rId112" xr:uid="{E990ED3E-9EB6-48C3-B3E1-DF5C7A2E51B6}"/>
+    <hyperlink ref="F114" r:id="rId113" display="https://health.usnews.com/medicare/articles/your-guide-to-medicare-coverage" xr:uid="{8C2BB7DF-05B7-4E73-8000-FF3577982A8C}"/>
+    <hyperlink ref="F115" r:id="rId114" display="https://www.congress.gov/crs_external_products/R/PDF/R43357/R43357.21.pdf" xr:uid="{7DA15771-DF6C-44DB-9EE8-4D16385D3F13}"/>
+    <hyperlink ref="F116" r:id="rId115" display="https://www.definitivehc.com/blog/the-difference-between-non-profit-and-for-profit-hospitals" xr:uid="{B07FFCA1-A00F-4A3A-9647-7C004223DF68}"/>
+    <hyperlink ref="F117" r:id="rId116" display="https://www.healthcare-brew.com/stories/2025/09/29/difference-between-for-profit-nonprofit-hospitals" xr:uid="{4079EBF4-92E8-4661-9B88-BD03A939A8E3}"/>
+    <hyperlink ref="F118" r:id="rId117" display="https://www.ismworld.org/certification-and-training/certification/cpsm/" xr:uid="{F0C7F2F2-E750-402D-BAE2-FF6DBFC5D7D2}"/>
+    <hyperlink ref="F119" r:id="rId118" location=":~:text=%E2%80%9CWhen%20you%20earn%20the%20Certified%20in%20Planning%20and,these%20components%20relates%20to%20the%20extended%20supply%20chain.%E2%80%9D" display="https://www.ascm.org/lp/certified-in-planning-and-inventory-management/ - :~:text=%E2%80%9CWhen%20you%20earn%20the%20Certified%20in%20Planning%20and,these%20components%20relates%20to%20the%20extended%20supply%20chain.%E2%80%9D" xr:uid="{2C969DD3-158B-4C56-B92A-26CC19DECBD8}"/>
+    <hyperlink ref="F120" r:id="rId119" display="https://nahq.org/credentials/cphq-certified-professional-in-healthcare-quality/?keyword=certified%20professional%20in%20healthcare%20quality%20cphq&amp;matchtype=e&amp;device=c&amp;lpurl=https%3A%2F%2Fnahq.org%2Fcredentials%2Fcphq-certified-professional-in-healthcare-quality%2F&amp;campaign=Microsoft%20-%20CPHQ&amp;adgroup=CPHQ%20-%20General&amp;msclkid=27800f402d1312e5a181650640c4bdb2&amp;utm_source=bing&amp;utm_medium=cpc&amp;utm_campaign=Microsoft%20-%20CPHQ&amp;utm_term=certified%20professional%20in%20healthcare%20quality%20cphq&amp;utm_content=CPHQ%20-%20General" xr:uid="{97B5871A-61EA-456D-8752-E194DDF02A7C}"/>
+    <hyperlink ref="F121" r:id="rId120" display="https://www.youtube.com/watch?v=rqdWr9ynZ_o" xr:uid="{ED5CA218-8464-4984-8C51-20DE3A1F2D23}"/>
+    <hyperlink ref="F122" r:id="rId121" display="https://www.youtube.com/watch?v=bkjDJhlj6Vg" xr:uid="{0E476557-7343-4522-86EC-97ABA5E0DB63}"/>
+    <hyperlink ref="F123" r:id="rId122" display="https://www.youtube.com/watch?v=TDi_ITG293c" xr:uid="{6462665F-F98D-45A3-AE9A-4A9DF6E71BD7}"/>
+    <hyperlink ref="F124" r:id="rId123" xr:uid="{A2764952-FE1A-4B39-B12D-FCD7705F3A09}"/>
+    <hyperlink ref="F125" r:id="rId124" display="https://online.lifelonglearning.jhu.edu/jhu-online-ai-in-healthcare-certificate-program?utm_source=bing&amp;utm_medium=search&amp;utm_campaign=JHU_AIHC_Bing_Search_healthcare_exact_US_Healthcare&amp;campaign_id=533144939&amp;adgroup_id=1351302472142947&amp;ad_id=&amp;utm_target=kwd-84457628177695:loc-190&amp;Keyword=ai%20in%20healthcare&amp;placement=&amp;msclkid=ef15f6989aa51849445c9cdee861aaf7" xr:uid="{4916515B-9679-4C08-B17B-CD5F3921D3C7}"/>
+    <hyperlink ref="F126" r:id="rId125" display="https://www.ihi.org/library/blog/guiding-flock-3-simple-rules-improve-hospital-wide-patient-flow" xr:uid="{369DD27B-44E6-4DCF-84BF-5E7AC4139E0A}"/>
+    <hyperlink ref="F127" r:id="rId126" display="https://www.hfma.org/61738/" xr:uid="{35A380CC-5D2A-477B-A8C8-A62F9A058AE7}"/>
+    <hyperlink ref="F128" r:id="rId127" display="https://www.kff.org/health-costs/key-facts-about-hospitals/" xr:uid="{164B5830-EB4F-4F3A-9B7C-B747CA31F522}"/>
+    <hyperlink ref="F129" r:id="rId128" display="https://www.definitivehc.com/resources/healthcare-insights/hospital-operating-margins-united-states" xr:uid="{C8840CEA-825B-45BE-998B-03FB7A4E646C}"/>
+    <hyperlink ref="F130" r:id="rId129" display="https://www.beckershospitalreview.com/finance/from-2-2-to-16-5-36-health-systems-ranked-by-operating-margins-in-2025/" xr:uid="{2D21D198-5EDA-45D5-9D56-08081F0ACF46}"/>
+    <hyperlink ref="F131" r:id="rId130" display="https://www.healthpartners.com/blog/medical-claim/" xr:uid="{29FC3D76-2E8E-4CE3-8013-076AACECA8EB}"/>
+    <hyperlink ref="F132" r:id="rId131" display="https://www.medesk.net/en/blog/denial-management/" xr:uid="{FA17B41C-8B24-4291-A101-5198BBC8E873}"/>
+    <hyperlink ref="F133" r:id="rId132" display="https://www.pgmbilling.com/blog/what-is-a-claim-scrubber-and-why-it-matters-more-than-ever/" xr:uid="{1F547038-58B3-469A-B4B1-374DF14DF44A}"/>
+    <hyperlink ref="F134" r:id="rId133" display="https://healthcarereaders.com/insights/supply-chain-management-in-healthcare" xr:uid="{AF85B86A-1A58-4C25-98F0-322102D0D4DA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId106"/>
+    <tablePart r:id="rId134"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57CA2FE6-5472-4004-98CD-B2FEB2BFF00A}">
-  <dimension ref="A1:E140"/>
+  <dimension ref="A1:E201"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="37.5703125" bestFit="1" customWidth="1"/>
@@ -4841,172 +6350,172 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>244</v>
+        <v>313</v>
       </c>
       <c r="B1" t="s">
-        <v>245</v>
+        <v>314</v>
       </c>
       <c r="C1" t="s">
-        <v>246</v>
+        <v>315</v>
       </c>
       <c r="D1" t="s">
-        <v>247</v>
+        <v>316</v>
       </c>
       <c r="E1" t="s">
-        <v>248</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="72.599999999999994">
       <c r="A2" t="s">
-        <v>249</v>
+        <v>318</v>
       </c>
       <c r="B2" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>251</v>
+        <v>320</v>
       </c>
       <c r="D2" t="s">
         <v>105</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>252</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="43.5">
       <c r="A3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="D3" t="s">
         <v>253</v>
       </c>
-      <c r="B3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="D3" t="s">
-        <v>255</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>256</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="57.95">
       <c r="A4" t="s">
-        <v>257</v>
+        <v>325</v>
       </c>
       <c r="B4" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>258</v>
+        <v>326</v>
       </c>
       <c r="D4" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>259</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="72.599999999999994">
       <c r="A5" t="s">
-        <v>260</v>
+        <v>328</v>
       </c>
       <c r="B5" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>261</v>
+        <v>329</v>
       </c>
       <c r="D5" t="s">
         <v>105</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>262</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="57.95">
       <c r="A6" t="s">
-        <v>263</v>
+        <v>331</v>
       </c>
       <c r="B6" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>264</v>
+        <v>332</v>
       </c>
       <c r="D6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>265</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="72.599999999999994">
       <c r="A7" t="s">
-        <v>266</v>
+        <v>334</v>
       </c>
       <c r="B7" t="s">
         <v>54</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>267</v>
+        <v>335</v>
       </c>
       <c r="D7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>268</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="43.5">
       <c r="A8" t="s">
-        <v>269</v>
+        <v>337</v>
       </c>
       <c r="B8" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>270</v>
+        <v>338</v>
       </c>
       <c r="D8" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>271</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="57.95">
       <c r="A9" t="s">
-        <v>272</v>
+        <v>340</v>
       </c>
       <c r="B9" t="s">
         <v>54</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>273</v>
+        <v>341</v>
       </c>
       <c r="D9" t="s">
-        <v>274</v>
+        <v>342</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>275</v>
+        <v>343</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="72.599999999999994">
       <c r="A10" t="s">
-        <v>276</v>
+        <v>344</v>
       </c>
       <c r="B10" t="s">
-        <v>277</v>
+        <v>345</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>278</v>
+        <v>346</v>
       </c>
       <c r="D10" t="s">
-        <v>274</v>
+        <v>342</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>279</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="72.599999999999994">
@@ -5014,2191 +6523,3228 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>277</v>
+        <v>345</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>280</v>
+        <v>348</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>342</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>281</v>
+        <v>349</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="72.599999999999994">
       <c r="A12" t="s">
-        <v>282</v>
+        <v>350</v>
       </c>
       <c r="B12" t="s">
-        <v>277</v>
+        <v>345</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>283</v>
+        <v>351</v>
       </c>
       <c r="D12" t="s">
-        <v>284</v>
+        <v>352</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>285</v>
+        <v>353</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="72.599999999999994">
       <c r="A13" t="s">
-        <v>286</v>
+        <v>354</v>
       </c>
       <c r="B13" t="s">
         <v>45</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>287</v>
+        <v>355</v>
       </c>
       <c r="D13" t="s">
-        <v>288</v>
+        <v>356</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>289</v>
+        <v>357</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="57.95">
       <c r="A14" t="s">
-        <v>290</v>
+        <v>358</v>
       </c>
       <c r="B14" t="s">
         <v>45</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>291</v>
+        <v>359</v>
       </c>
       <c r="D14" t="s">
         <v>187</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>292</v>
+        <v>360</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="72.599999999999994">
       <c r="A15" t="s">
-        <v>293</v>
+        <v>361</v>
       </c>
       <c r="B15" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>294</v>
+        <v>362</v>
       </c>
       <c r="D15" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>295</v>
+        <v>363</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="72.599999999999994">
       <c r="A16" t="s">
-        <v>296</v>
+        <v>364</v>
       </c>
       <c r="B16" t="s">
-        <v>297</v>
+        <v>365</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>298</v>
+        <v>366</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>299</v>
+        <v>367</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="72.599999999999994">
       <c r="A17" t="s">
-        <v>300</v>
+        <v>368</v>
       </c>
       <c r="B17" t="s">
-        <v>297</v>
+        <v>365</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>301</v>
+        <v>369</v>
       </c>
       <c r="D17" t="s">
-        <v>302</v>
+        <v>370</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>303</v>
+        <v>371</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="72.599999999999994">
       <c r="A18" t="s">
-        <v>304</v>
+        <v>372</v>
       </c>
       <c r="B18" t="s">
-        <v>297</v>
+        <v>365</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>305</v>
+        <v>373</v>
       </c>
       <c r="D18" t="s">
-        <v>288</v>
+        <v>356</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>306</v>
+        <v>374</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="72.599999999999994">
       <c r="A19" t="s">
-        <v>307</v>
+        <v>375</v>
       </c>
       <c r="B19" t="s">
-        <v>297</v>
+        <v>365</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>308</v>
+        <v>376</v>
       </c>
       <c r="D19" t="s">
-        <v>288</v>
+        <v>356</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>309</v>
+        <v>377</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="72.599999999999994">
       <c r="A20" t="s">
-        <v>310</v>
+        <v>378</v>
       </c>
       <c r="B20" t="s">
-        <v>311</v>
+        <v>379</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>312</v>
+        <v>380</v>
       </c>
       <c r="D20" t="s">
-        <v>313</v>
+        <v>381</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>314</v>
+        <v>382</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="57.95">
       <c r="A21" t="s">
-        <v>315</v>
+        <v>383</v>
       </c>
       <c r="B21" t="s">
-        <v>311</v>
+        <v>379</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>316</v>
+        <v>384</v>
       </c>
       <c r="D21" t="s">
-        <v>317</v>
+        <v>385</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>318</v>
+        <v>386</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="72.599999999999994">
       <c r="A22" t="s">
-        <v>319</v>
+        <v>387</v>
       </c>
       <c r="B22" t="s">
-        <v>311</v>
+        <v>379</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>320</v>
+        <v>388</v>
       </c>
       <c r="D22" t="s">
-        <v>321</v>
+        <v>389</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>322</v>
+        <v>390</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="72.599999999999994">
       <c r="A23" t="s">
-        <v>323</v>
+        <v>391</v>
       </c>
       <c r="B23" t="s">
-        <v>311</v>
+        <v>379</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>324</v>
+        <v>392</v>
       </c>
       <c r="D23" t="s">
-        <v>321</v>
+        <v>389</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="87">
       <c r="A24" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="B24" t="s">
-        <v>297</v>
+        <v>365</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>327</v>
+        <v>395</v>
       </c>
       <c r="D24" t="s">
-        <v>288</v>
+        <v>356</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>328</v>
+        <v>396</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="72.599999999999994">
       <c r="A25" t="s">
-        <v>329</v>
+        <v>397</v>
       </c>
       <c r="B25" t="s">
-        <v>297</v>
+        <v>365</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>330</v>
+        <v>398</v>
       </c>
       <c r="D25" t="s">
-        <v>331</v>
+        <v>399</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>332</v>
+        <v>400</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="72.599999999999994">
       <c r="A26" t="s">
-        <v>333</v>
+        <v>401</v>
       </c>
       <c r="B26" t="s">
-        <v>297</v>
+        <v>365</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>334</v>
+        <v>402</v>
       </c>
       <c r="D26" t="s">
-        <v>335</v>
+        <v>403</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>336</v>
+        <v>404</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="72.599999999999994">
       <c r="A27" t="s">
-        <v>337</v>
+        <v>405</v>
       </c>
       <c r="B27" t="s">
-        <v>338</v>
+        <v>406</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>339</v>
+        <v>407</v>
       </c>
       <c r="D27" t="s">
         <v>187</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>340</v>
+        <v>408</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="57.95">
       <c r="A28" t="s">
-        <v>341</v>
+        <v>409</v>
       </c>
       <c r="B28" t="s">
         <v>134</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="D28" t="s">
-        <v>343</v>
+        <v>411</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>344</v>
+        <v>412</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="57.95">
       <c r="A29" t="s">
-        <v>345</v>
+        <v>413</v>
       </c>
       <c r="B29" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>346</v>
+        <v>414</v>
       </c>
       <c r="D29" t="s">
         <v>202</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>347</v>
+        <v>415</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="57.95">
       <c r="A30" t="s">
-        <v>348</v>
+        <v>416</v>
       </c>
       <c r="B30" t="s">
-        <v>311</v>
+        <v>379</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>349</v>
+        <v>417</v>
       </c>
       <c r="D30" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>350</v>
+        <v>418</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="72.599999999999994">
       <c r="A31" t="s">
-        <v>351</v>
+        <v>419</v>
       </c>
       <c r="B31" t="s">
-        <v>311</v>
+        <v>379</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>352</v>
+        <v>420</v>
       </c>
       <c r="D31" t="s">
-        <v>353</v>
+        <v>421</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>354</v>
+        <v>422</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="57.95">
       <c r="A32" t="s">
-        <v>355</v>
+        <v>423</v>
       </c>
       <c r="B32" t="s">
-        <v>311</v>
+        <v>379</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>356</v>
+        <v>424</v>
       </c>
       <c r="D32" t="s">
         <v>142</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>357</v>
+        <v>425</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="72.599999999999994">
       <c r="A33" t="s">
-        <v>358</v>
+        <v>426</v>
       </c>
       <c r="B33" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>359</v>
+        <v>427</v>
       </c>
       <c r="D33" t="s">
-        <v>360</v>
+        <v>428</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>361</v>
+        <v>429</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="72.599999999999994">
       <c r="A34" t="s">
-        <v>362</v>
+        <v>430</v>
       </c>
       <c r="B34" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>363</v>
+        <v>431</v>
       </c>
       <c r="D34" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>364</v>
+        <v>432</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="72.599999999999994">
       <c r="A35" t="s">
-        <v>365</v>
+        <v>433</v>
       </c>
       <c r="B35" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>366</v>
+        <v>434</v>
       </c>
       <c r="D35" t="s">
         <v>105</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>367</v>
+        <v>435</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="72.599999999999994">
       <c r="A36" t="s">
-        <v>368</v>
+        <v>436</v>
       </c>
       <c r="B36" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>369</v>
+        <v>437</v>
       </c>
       <c r="D36" t="s">
         <v>105</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>370</v>
+        <v>438</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="72.599999999999994">
       <c r="A37" t="s">
-        <v>371</v>
+        <v>439</v>
       </c>
       <c r="B37" t="s">
         <v>45</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>372</v>
+        <v>440</v>
       </c>
       <c r="D37" t="s">
         <v>187</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>373</v>
+        <v>441</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="101.45">
       <c r="A38" t="s">
-        <v>374</v>
+        <v>442</v>
       </c>
       <c r="B38" t="s">
-        <v>311</v>
+        <v>379</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>375</v>
+        <v>443</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>376</v>
+        <v>444</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="72.599999999999994">
       <c r="A39" t="s">
-        <v>377</v>
+        <v>445</v>
       </c>
       <c r="B39" t="s">
-        <v>297</v>
+        <v>365</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>378</v>
+        <v>446</v>
       </c>
       <c r="D39" t="s">
-        <v>288</v>
+        <v>356</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>379</v>
+        <v>447</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="72.599999999999994">
       <c r="A40" t="s">
-        <v>380</v>
+        <v>448</v>
       </c>
       <c r="B40" t="s">
-        <v>297</v>
+        <v>365</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>381</v>
+        <v>449</v>
       </c>
       <c r="D40" t="s">
-        <v>288</v>
+        <v>356</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>382</v>
+        <v>450</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="87">
       <c r="A41" t="s">
-        <v>383</v>
+        <v>451</v>
       </c>
       <c r="B41" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>384</v>
+        <v>452</v>
       </c>
       <c r="D41" t="s">
         <v>139</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>385</v>
+        <v>453</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="57.95">
       <c r="A42" t="s">
-        <v>386</v>
+        <v>454</v>
       </c>
       <c r="B42" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>387</v>
+        <v>455</v>
       </c>
       <c r="D42" t="s">
         <v>105</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>388</v>
+        <v>456</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="57.95">
       <c r="A43" t="s">
-        <v>389</v>
+        <v>457</v>
       </c>
       <c r="B43" t="s">
         <v>134</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>390</v>
+        <v>458</v>
       </c>
       <c r="D43" t="s">
-        <v>391</v>
+        <v>459</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>392</v>
+        <v>460</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="72.599999999999994">
       <c r="A44" t="s">
-        <v>393</v>
+        <v>461</v>
       </c>
       <c r="B44" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>394</v>
+        <v>462</v>
       </c>
       <c r="D44" t="s">
         <v>105</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>395</v>
+        <v>463</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="72.599999999999994">
       <c r="A45" t="s">
-        <v>396</v>
+        <v>464</v>
       </c>
       <c r="B45" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>397</v>
+        <v>465</v>
       </c>
       <c r="D45" t="s">
         <v>105</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>398</v>
+        <v>466</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="72.599999999999994">
       <c r="A46" t="s">
-        <v>399</v>
+        <v>467</v>
       </c>
       <c r="B46" t="s">
-        <v>311</v>
+        <v>379</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>400</v>
+        <v>468</v>
       </c>
       <c r="D46" t="s">
-        <v>317</v>
+        <v>385</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>401</v>
+        <v>469</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="72.599999999999994">
       <c r="A47" t="s">
-        <v>402</v>
+        <v>470</v>
       </c>
       <c r="B47" t="s">
-        <v>311</v>
+        <v>379</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>403</v>
+        <v>471</v>
       </c>
       <c r="D47" t="s">
-        <v>317</v>
+        <v>385</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>404</v>
+        <v>472</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="57.95">
       <c r="A48" t="s">
-        <v>405</v>
+        <v>473</v>
       </c>
       <c r="B48" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>406</v>
+        <v>474</v>
       </c>
       <c r="D48" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>407</v>
+        <v>475</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="72.599999999999994">
       <c r="A49" t="s">
-        <v>408</v>
+        <v>476</v>
       </c>
       <c r="B49" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>409</v>
+        <v>477</v>
       </c>
       <c r="D49" t="s">
-        <v>410</v>
+        <v>478</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>411</v>
+        <v>479</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="72.599999999999994">
       <c r="A50" t="s">
-        <v>412</v>
+        <v>480</v>
       </c>
       <c r="B50" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>413</v>
+        <v>481</v>
       </c>
       <c r="D50" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>414</v>
+        <v>482</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="72.599999999999994">
       <c r="A51" t="s">
-        <v>415</v>
+        <v>483</v>
       </c>
       <c r="B51" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>416</v>
+        <v>484</v>
       </c>
       <c r="D51" t="s">
-        <v>343</v>
+        <v>411</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>417</v>
+        <v>485</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="57.95">
       <c r="A52" t="s">
-        <v>418</v>
+        <v>486</v>
       </c>
       <c r="B52" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>419</v>
+        <v>487</v>
       </c>
       <c r="D52" t="s">
         <v>105</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>420</v>
+        <v>488</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="72.599999999999994">
       <c r="A53" t="s">
-        <v>421</v>
+        <v>489</v>
       </c>
       <c r="B53" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>422</v>
+        <v>490</v>
       </c>
       <c r="D53" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>423</v>
+        <v>491</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="72.599999999999994">
       <c r="A54" t="s">
-        <v>424</v>
+        <v>492</v>
       </c>
       <c r="B54" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>425</v>
+        <v>493</v>
       </c>
       <c r="D54" t="s">
-        <v>426</v>
+        <v>494</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>427</v>
+        <v>495</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="72.599999999999994">
       <c r="A55" t="s">
-        <v>428</v>
+        <v>496</v>
       </c>
       <c r="B55" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>429</v>
+        <v>497</v>
       </c>
       <c r="D55" t="s">
         <v>105</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>430</v>
+        <v>498</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="57.95">
       <c r="A56" t="s">
-        <v>431</v>
+        <v>499</v>
       </c>
       <c r="B56" t="s">
         <v>54</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>432</v>
+        <v>500</v>
       </c>
       <c r="D56" t="s">
-        <v>274</v>
+        <v>342</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>433</v>
+        <v>501</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="72.599999999999994">
       <c r="A57" t="s">
-        <v>408</v>
+        <v>476</v>
       </c>
       <c r="B57" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>434</v>
+        <v>502</v>
       </c>
       <c r="D57" t="s">
-        <v>410</v>
+        <v>478</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>435</v>
+        <v>503</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="72.599999999999994">
       <c r="A58" t="s">
-        <v>436</v>
+        <v>504</v>
       </c>
       <c r="B58" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>437</v>
+        <v>505</v>
       </c>
       <c r="D58" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>438</v>
+        <v>506</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="72.599999999999994">
       <c r="A59" t="s">
-        <v>439</v>
+        <v>507</v>
       </c>
       <c r="B59" t="s">
-        <v>338</v>
+        <v>406</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>440</v>
+        <v>508</v>
       </c>
       <c r="D59" t="s">
         <v>187</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>441</v>
+        <v>509</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="57.95">
       <c r="A60" t="s">
-        <v>442</v>
+        <v>510</v>
       </c>
       <c r="B60" t="s">
-        <v>338</v>
+        <v>406</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>443</v>
+        <v>511</v>
       </c>
       <c r="D60" t="s">
         <v>187</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>444</v>
+        <v>512</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="57.95">
       <c r="A61" t="s">
-        <v>445</v>
+        <v>513</v>
       </c>
       <c r="B61" t="s">
         <v>45</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>446</v>
+        <v>514</v>
       </c>
       <c r="D61" t="s">
         <v>187</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>447</v>
+        <v>515</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="57.95">
       <c r="A62" t="s">
-        <v>448</v>
+        <v>516</v>
       </c>
       <c r="B62" t="s">
         <v>45</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>449</v>
+        <v>517</v>
       </c>
       <c r="D62" t="s">
         <v>187</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>450</v>
+        <v>518</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="72.599999999999994">
       <c r="A63" t="s">
-        <v>451</v>
+        <v>519</v>
       </c>
       <c r="B63" t="s">
         <v>45</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>452</v>
+        <v>520</v>
       </c>
       <c r="D63" t="s">
         <v>187</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>453</v>
+        <v>521</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="57.95">
       <c r="A64" t="s">
-        <v>454</v>
+        <v>522</v>
       </c>
       <c r="B64" t="s">
         <v>45</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>455</v>
+        <v>523</v>
       </c>
       <c r="D64" t="s">
-        <v>288</v>
+        <v>356</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>456</v>
+        <v>524</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="57.95">
       <c r="A65" t="s">
-        <v>457</v>
+        <v>525</v>
       </c>
       <c r="B65" t="s">
         <v>45</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>458</v>
+        <v>526</v>
       </c>
       <c r="D65" t="s">
-        <v>459</v>
+        <v>527</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>460</v>
+        <v>528</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="72.599999999999994">
       <c r="A66" t="s">
-        <v>461</v>
+        <v>529</v>
       </c>
       <c r="B66" t="s">
         <v>45</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>462</v>
+        <v>530</v>
       </c>
       <c r="D66" t="s">
-        <v>288</v>
+        <v>356</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>463</v>
+        <v>531</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="87">
       <c r="A67" t="s">
-        <v>464</v>
+        <v>532</v>
       </c>
       <c r="B67" t="s">
         <v>45</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>465</v>
+        <v>533</v>
       </c>
       <c r="D67" t="s">
         <v>187</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>466</v>
+        <v>534</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="57.95">
       <c r="A68" t="s">
-        <v>467</v>
+        <v>535</v>
       </c>
       <c r="B68" t="s">
         <v>45</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>468</v>
+        <v>536</v>
       </c>
       <c r="D68" t="s">
-        <v>469</v>
+        <v>537</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>470</v>
+        <v>538</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="72.599999999999994">
       <c r="A69" t="s">
-        <v>471</v>
+        <v>539</v>
       </c>
       <c r="B69" t="s">
         <v>45</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>472</v>
+        <v>540</v>
       </c>
       <c r="D69" t="s">
-        <v>288</v>
+        <v>356</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>473</v>
+        <v>541</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="72.599999999999994">
       <c r="A70" t="s">
-        <v>474</v>
+        <v>542</v>
       </c>
       <c r="B70" t="s">
-        <v>338</v>
+        <v>406</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>475</v>
+        <v>543</v>
       </c>
       <c r="D70" t="s">
-        <v>288</v>
+        <v>356</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>476</v>
+        <v>544</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="72.599999999999994">
       <c r="A71" t="s">
-        <v>477</v>
+        <v>545</v>
       </c>
       <c r="B71" t="s">
-        <v>338</v>
+        <v>406</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>478</v>
+        <v>546</v>
       </c>
       <c r="D71" t="s">
         <v>187</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>479</v>
+        <v>547</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="72.599999999999994">
       <c r="A72" t="s">
-        <v>480</v>
+        <v>548</v>
       </c>
       <c r="B72" t="s">
         <v>45</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>481</v>
+        <v>549</v>
       </c>
       <c r="D72" t="s">
         <v>187</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>482</v>
+        <v>550</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="72.599999999999994">
       <c r="A73" t="s">
-        <v>483</v>
+        <v>551</v>
       </c>
       <c r="B73" t="s">
         <v>45</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>484</v>
+        <v>552</v>
       </c>
       <c r="D73" t="s">
         <v>187</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>485</v>
+        <v>553</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="72.599999999999994">
       <c r="A74" t="s">
-        <v>486</v>
+        <v>554</v>
       </c>
       <c r="B74" t="s">
         <v>45</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>485</v>
+        <v>553</v>
       </c>
       <c r="D74" t="s">
         <v>187</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>487</v>
+        <v>555</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="72.599999999999994">
       <c r="A75" t="s">
-        <v>488</v>
+        <v>556</v>
       </c>
       <c r="B75" t="s">
         <v>45</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>489</v>
+        <v>557</v>
       </c>
       <c r="D75" t="s">
         <v>187</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>490</v>
+        <v>558</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="72.599999999999994">
       <c r="A76" t="s">
-        <v>491</v>
+        <v>559</v>
       </c>
       <c r="B76" t="s">
         <v>45</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>492</v>
+        <v>560</v>
       </c>
       <c r="D76" t="s">
-        <v>493</v>
+        <v>561</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>494</v>
+        <v>562</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="72.599999999999994">
       <c r="A77" t="s">
-        <v>495</v>
+        <v>563</v>
       </c>
       <c r="B77" t="s">
         <v>45</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>496</v>
+        <v>564</v>
       </c>
       <c r="D77" t="s">
-        <v>288</v>
+        <v>356</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>497</v>
+        <v>565</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="72.599999999999994">
       <c r="A78" t="s">
-        <v>498</v>
+        <v>566</v>
       </c>
       <c r="B78" t="s">
         <v>45</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>499</v>
+        <v>567</v>
       </c>
       <c r="D78" t="s">
-        <v>493</v>
+        <v>561</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>500</v>
+        <v>568</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="57.95">
       <c r="A79" t="s">
-        <v>501</v>
+        <v>569</v>
       </c>
       <c r="B79" t="s">
         <v>45</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>502</v>
+        <v>570</v>
       </c>
       <c r="D79" t="s">
-        <v>288</v>
+        <v>356</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>503</v>
+        <v>571</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="72.599999999999994">
       <c r="A80" t="s">
-        <v>504</v>
+        <v>572</v>
       </c>
       <c r="B80" t="s">
         <v>45</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>505</v>
+        <v>573</v>
       </c>
       <c r="D80" t="s">
         <v>187</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>506</v>
+        <v>574</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="72.599999999999994">
       <c r="A81" t="s">
-        <v>507</v>
+        <v>575</v>
       </c>
       <c r="B81" t="s">
-        <v>311</v>
+        <v>379</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>508</v>
+        <v>576</v>
       </c>
       <c r="D81" t="s">
         <v>187</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>509</v>
+        <v>577</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="72.599999999999994">
       <c r="A82" t="s">
-        <v>510</v>
+        <v>578</v>
       </c>
       <c r="B82" t="s">
-        <v>311</v>
+        <v>379</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>511</v>
+        <v>579</v>
       </c>
       <c r="D82" t="s">
-        <v>512</v>
+        <v>580</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>513</v>
+        <v>581</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="72.599999999999994">
       <c r="A83" t="s">
-        <v>514</v>
+        <v>582</v>
       </c>
       <c r="B83" t="s">
-        <v>311</v>
+        <v>379</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>515</v>
+        <v>583</v>
       </c>
       <c r="D83" t="s">
-        <v>516</v>
+        <v>584</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>517</v>
+        <v>585</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="72.599999999999994">
       <c r="A84" t="s">
-        <v>518</v>
+        <v>586</v>
       </c>
       <c r="B84" t="s">
         <v>45</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>519</v>
+        <v>587</v>
       </c>
       <c r="D84" t="s">
         <v>187</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>520</v>
+        <v>588</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="72.599999999999994">
       <c r="A85" t="s">
-        <v>521</v>
+        <v>589</v>
       </c>
       <c r="B85" t="s">
         <v>45</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>522</v>
+        <v>590</v>
       </c>
       <c r="D85" t="s">
-        <v>288</v>
+        <v>356</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>523</v>
+        <v>591</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="87">
       <c r="A86" t="s">
-        <v>524</v>
+        <v>592</v>
       </c>
       <c r="B86" t="s">
         <v>45</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>525</v>
+        <v>593</v>
       </c>
       <c r="D86" t="s">
-        <v>526</v>
+        <v>594</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>527</v>
+        <v>595</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="57.95">
       <c r="A87" t="s">
-        <v>528</v>
+        <v>596</v>
       </c>
       <c r="B87" t="s">
         <v>111</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>529</v>
+        <v>597</v>
       </c>
       <c r="D87" t="s">
         <v>202</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>530</v>
+        <v>598</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="87">
       <c r="A88" t="s">
-        <v>531</v>
+        <v>599</v>
       </c>
       <c r="B88" t="s">
         <v>111</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>532</v>
+        <v>600</v>
       </c>
       <c r="D88" t="s">
-        <v>274</v>
+        <v>342</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>533</v>
+        <v>601</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="72.599999999999994">
       <c r="A89" t="s">
-        <v>534</v>
+        <v>602</v>
       </c>
       <c r="B89" t="s">
         <v>111</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>535</v>
+        <v>603</v>
       </c>
       <c r="D89" t="s">
         <v>202</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>536</v>
+        <v>604</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="57.95">
       <c r="A90" t="s">
-        <v>537</v>
+        <v>605</v>
       </c>
       <c r="B90" t="s">
         <v>111</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>538</v>
+        <v>606</v>
       </c>
       <c r="D90" t="s">
         <v>202</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>539</v>
+        <v>607</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="72.599999999999994">
       <c r="A91" t="s">
-        <v>540</v>
+        <v>608</v>
       </c>
       <c r="B91" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>541</v>
+        <v>609</v>
       </c>
       <c r="D91" t="s">
-        <v>410</v>
+        <v>478</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>542</v>
+        <v>610</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="57.95">
       <c r="A92" t="s">
-        <v>543</v>
+        <v>611</v>
       </c>
       <c r="B92" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>544</v>
+        <v>612</v>
       </c>
       <c r="D92" t="s">
         <v>105</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>545</v>
+        <v>613</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="87">
       <c r="A93" t="s">
-        <v>546</v>
+        <v>614</v>
       </c>
       <c r="B93" t="s">
         <v>111</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>547</v>
+        <v>615</v>
       </c>
       <c r="D93" t="s">
         <v>202</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>548</v>
+        <v>616</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="72.599999999999994">
       <c r="A94" t="s">
-        <v>549</v>
+        <v>617</v>
       </c>
       <c r="B94" t="s">
         <v>134</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>550</v>
+        <v>618</v>
       </c>
       <c r="D94" t="s">
-        <v>526</v>
+        <v>594</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>551</v>
+        <v>619</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="87">
       <c r="A95" t="s">
-        <v>552</v>
+        <v>620</v>
       </c>
       <c r="B95" t="s">
         <v>111</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>553</v>
+        <v>621</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>554</v>
+        <v>622</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="87">
       <c r="A96" t="s">
-        <v>555</v>
+        <v>623</v>
       </c>
       <c r="B96" t="s">
         <v>111</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>556</v>
+        <v>624</v>
       </c>
       <c r="D96" t="s">
         <v>202</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>557</v>
+        <v>625</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="87">
       <c r="A97" t="s">
-        <v>558</v>
+        <v>626</v>
       </c>
       <c r="B97" t="s">
         <v>111</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>559</v>
+        <v>627</v>
       </c>
       <c r="D97" t="s">
         <v>202</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>560</v>
+        <v>628</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="87">
       <c r="A98" t="s">
-        <v>561</v>
+        <v>629</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>562</v>
+        <v>630</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>563</v>
+        <v>631</v>
       </c>
       <c r="D98" t="s">
-        <v>426</v>
+        <v>494</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>564</v>
+        <v>632</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="57.95">
       <c r="A99" t="s">
-        <v>565</v>
+        <v>633</v>
       </c>
       <c r="B99" t="s">
-        <v>277</v>
+        <v>345</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>566</v>
+        <v>634</v>
       </c>
       <c r="D99" t="s">
-        <v>567</v>
+        <v>635</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>568</v>
+        <v>636</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="72.599999999999994">
       <c r="A100" t="s">
-        <v>569</v>
+        <v>637</v>
       </c>
       <c r="B100" t="s">
-        <v>311</v>
+        <v>379</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>570</v>
+        <v>638</v>
       </c>
       <c r="D100" t="s">
-        <v>571</v>
+        <v>639</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>572</v>
+        <v>640</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="57.95">
       <c r="A101" t="s">
-        <v>573</v>
+        <v>641</v>
       </c>
       <c r="B101" t="s">
         <v>134</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>574</v>
+        <v>642</v>
       </c>
       <c r="D101" t="s">
-        <v>575</v>
+        <v>643</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>576</v>
+        <v>644</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="87">
       <c r="A102" t="s">
-        <v>577</v>
+        <v>645</v>
       </c>
       <c r="B102" t="s">
         <v>134</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>578</v>
+        <v>646</v>
       </c>
       <c r="D102" t="s">
-        <v>567</v>
+        <v>635</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>579</v>
+        <v>647</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="87">
       <c r="A103" t="s">
-        <v>580</v>
+        <v>648</v>
       </c>
       <c r="B103" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>581</v>
+        <v>649</v>
       </c>
       <c r="D103" t="s">
-        <v>582</v>
+        <v>296</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>583</v>
+        <v>650</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="72.599999999999994">
       <c r="A104" t="s">
-        <v>584</v>
+        <v>651</v>
       </c>
       <c r="B104" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>585</v>
+        <v>652</v>
       </c>
       <c r="D104" t="s">
-        <v>586</v>
+        <v>653</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>587</v>
+        <v>654</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="57.95">
       <c r="A105" t="s">
-        <v>588</v>
+        <v>655</v>
       </c>
       <c r="B105" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>589</v>
+        <v>656</v>
       </c>
       <c r="D105" t="s">
         <v>105</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>590</v>
+        <v>657</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="72.599999999999994">
       <c r="A106" t="s">
-        <v>591</v>
+        <v>658</v>
       </c>
       <c r="B106" t="s">
-        <v>297</v>
+        <v>365</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>592</v>
+        <v>659</v>
       </c>
       <c r="D106" t="s">
-        <v>288</v>
+        <v>356</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>593</v>
+        <v>660</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="72.599999999999994">
       <c r="A107" t="s">
-        <v>594</v>
+        <v>661</v>
       </c>
       <c r="B107" t="s">
-        <v>311</v>
+        <v>379</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>595</v>
+        <v>662</v>
       </c>
       <c r="D107" t="s">
-        <v>274</v>
+        <v>342</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>596</v>
+        <v>663</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="72.599999999999994">
       <c r="A108" t="s">
-        <v>597</v>
+        <v>664</v>
       </c>
       <c r="B108" t="s">
-        <v>297</v>
+        <v>365</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>598</v>
+        <v>665</v>
       </c>
       <c r="D108" t="s">
-        <v>313</v>
+        <v>381</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>599</v>
+        <v>666</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="57.95">
       <c r="A109" t="s">
-        <v>600</v>
+        <v>667</v>
       </c>
       <c r="B109" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>601</v>
+        <v>668</v>
       </c>
       <c r="D109" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>602</v>
+        <v>669</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="72.599999999999994">
       <c r="A110" t="s">
-        <v>603</v>
+        <v>670</v>
       </c>
       <c r="B110" t="s">
-        <v>297</v>
+        <v>365</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>604</v>
+        <v>671</v>
       </c>
       <c r="D110" t="s">
-        <v>288</v>
+        <v>356</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>605</v>
+        <v>672</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="72.599999999999994">
       <c r="A111" t="s">
-        <v>606</v>
+        <v>673</v>
       </c>
       <c r="B111" t="s">
-        <v>297</v>
+        <v>365</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>607</v>
+        <v>674</v>
       </c>
       <c r="D111" t="s">
         <v>139</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>608</v>
+        <v>675</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="57.95">
       <c r="A112" t="s">
-        <v>609</v>
+        <v>676</v>
       </c>
       <c r="B112" t="s">
-        <v>297</v>
+        <v>365</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>610</v>
+        <v>677</v>
       </c>
       <c r="D112" t="s">
-        <v>288</v>
+        <v>356</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>611</v>
+        <v>678</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="57.95">
       <c r="A113" t="s">
-        <v>612</v>
+        <v>679</v>
       </c>
       <c r="B113" t="s">
         <v>45</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>613</v>
+        <v>680</v>
       </c>
       <c r="D113" t="s">
-        <v>274</v>
+        <v>342</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>614</v>
+        <v>681</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="72.599999999999994">
       <c r="A114" t="s">
-        <v>615</v>
+        <v>682</v>
       </c>
       <c r="B114" t="s">
-        <v>297</v>
+        <v>365</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>616</v>
+        <v>683</v>
       </c>
       <c r="D114" t="s">
-        <v>288</v>
+        <v>356</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>617</v>
+        <v>684</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="72.599999999999994">
       <c r="A115" t="s">
-        <v>618</v>
+        <v>685</v>
       </c>
       <c r="B115" t="s">
-        <v>311</v>
+        <v>379</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>619</v>
+        <v>686</v>
       </c>
       <c r="D115" t="s">
-        <v>620</v>
+        <v>687</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>621</v>
+        <v>688</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="87">
       <c r="A116" t="s">
-        <v>622</v>
+        <v>689</v>
       </c>
       <c r="B116" t="s">
-        <v>311</v>
+        <v>379</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>623</v>
+        <v>690</v>
       </c>
       <c r="D116" t="s">
-        <v>620</v>
+        <v>687</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>624</v>
+        <v>691</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="72.599999999999994">
       <c r="A117" t="s">
-        <v>625</v>
+        <v>692</v>
       </c>
       <c r="B117" t="s">
-        <v>311</v>
+        <v>379</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>626</v>
+        <v>693</v>
       </c>
       <c r="D117" t="s">
-        <v>620</v>
+        <v>687</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>627</v>
+        <v>694</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="87">
       <c r="A118" t="s">
-        <v>628</v>
+        <v>695</v>
       </c>
       <c r="B118" t="s">
-        <v>311</v>
+        <v>379</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>629</v>
+        <v>696</v>
       </c>
       <c r="D118" t="s">
-        <v>274</v>
+        <v>342</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>630</v>
+        <v>697</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="57.95">
       <c r="A119" t="s">
-        <v>631</v>
+        <v>698</v>
       </c>
       <c r="B119" t="s">
         <v>45</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>632</v>
+        <v>699</v>
       </c>
       <c r="D119" t="s">
         <v>187</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>633</v>
+        <v>700</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="72.599999999999994">
       <c r="A120" t="s">
-        <v>634</v>
+        <v>701</v>
       </c>
       <c r="B120" t="s">
-        <v>311</v>
+        <v>379</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>635</v>
+        <v>702</v>
       </c>
       <c r="D120" t="s">
-        <v>620</v>
+        <v>687</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>636</v>
+        <v>703</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="72.599999999999994">
       <c r="A121" t="s">
-        <v>637</v>
+        <v>704</v>
       </c>
       <c r="B121" t="s">
-        <v>311</v>
+        <v>379</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>638</v>
+        <v>705</v>
       </c>
       <c r="D121" t="s">
-        <v>620</v>
+        <v>687</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>639</v>
+        <v>706</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="72.599999999999994">
       <c r="A122" t="s">
-        <v>640</v>
+        <v>707</v>
       </c>
       <c r="B122" t="s">
-        <v>311</v>
+        <v>379</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>641</v>
+        <v>708</v>
       </c>
       <c r="D122" t="s">
-        <v>620</v>
+        <v>687</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>642</v>
+        <v>709</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="72.599999999999994">
       <c r="A123" t="s">
-        <v>643</v>
+        <v>710</v>
       </c>
       <c r="B123" t="s">
         <v>134</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>644</v>
+        <v>711</v>
       </c>
       <c r="D123" t="s">
-        <v>645</v>
+        <v>712</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>646</v>
+        <v>713</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="72.599999999999994">
       <c r="A124" t="s">
-        <v>647</v>
+        <v>714</v>
       </c>
       <c r="B124" t="s">
         <v>134</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>648</v>
+        <v>715</v>
       </c>
       <c r="D124" t="s">
-        <v>649</v>
+        <v>716</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>650</v>
+        <v>717</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="72.599999999999994">
       <c r="A125" t="s">
-        <v>651</v>
+        <v>718</v>
       </c>
       <c r="B125" t="s">
         <v>134</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>652</v>
+        <v>719</v>
       </c>
       <c r="D125" t="s">
-        <v>653</v>
+        <v>720</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>654</v>
+        <v>721</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="72.599999999999994">
       <c r="A126" t="s">
-        <v>655</v>
+        <v>722</v>
       </c>
       <c r="B126" t="s">
         <v>134</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>656</v>
+        <v>723</v>
       </c>
       <c r="D126" t="s">
-        <v>657</v>
+        <v>724</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>658</v>
+        <v>725</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="72.599999999999994">
       <c r="A127" t="s">
-        <v>659</v>
+        <v>726</v>
       </c>
       <c r="B127" t="s">
         <v>134</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>660</v>
+        <v>727</v>
       </c>
       <c r="D127" t="s">
-        <v>657</v>
+        <v>724</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>661</v>
+        <v>728</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="72.599999999999994">
       <c r="A128" t="s">
-        <v>662</v>
+        <v>729</v>
       </c>
       <c r="B128" t="s">
         <v>134</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>663</v>
+        <v>730</v>
       </c>
       <c r="D128" t="s">
-        <v>657</v>
+        <v>724</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>664</v>
+        <v>731</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="72.599999999999994">
       <c r="A129" t="s">
-        <v>665</v>
+        <v>732</v>
       </c>
       <c r="B129" t="s">
         <v>134</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>666</v>
+        <v>733</v>
       </c>
       <c r="D129" t="s">
-        <v>657</v>
+        <v>724</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>667</v>
+        <v>734</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="72.599999999999994">
       <c r="A130" t="s">
-        <v>668</v>
+        <v>735</v>
       </c>
       <c r="B130" t="s">
         <v>134</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>669</v>
+        <v>736</v>
       </c>
       <c r="D130" t="s">
-        <v>657</v>
+        <v>724</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>670</v>
+        <v>737</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="72.599999999999994">
       <c r="A131" t="s">
-        <v>671</v>
+        <v>738</v>
       </c>
       <c r="B131" t="s">
         <v>134</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>672</v>
+        <v>739</v>
       </c>
       <c r="D131" t="s">
-        <v>657</v>
+        <v>724</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>673</v>
+        <v>740</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="72.599999999999994">
       <c r="A132" t="s">
-        <v>674</v>
+        <v>741</v>
       </c>
       <c r="B132" t="s">
         <v>134</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>675</v>
+        <v>742</v>
       </c>
       <c r="D132" t="s">
-        <v>676</v>
+        <v>743</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>677</v>
+        <v>744</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="72.599999999999994">
       <c r="A133" t="s">
-        <v>678</v>
+        <v>745</v>
       </c>
       <c r="B133" t="s">
         <v>134</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>679</v>
+        <v>746</v>
       </c>
       <c r="D133" t="s">
-        <v>676</v>
+        <v>743</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>680</v>
+        <v>747</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="72.599999999999994">
       <c r="A134" t="s">
-        <v>681</v>
+        <v>748</v>
       </c>
       <c r="B134" t="s">
         <v>54</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>682</v>
+        <v>749</v>
       </c>
       <c r="D134" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>683</v>
+        <v>750</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="72.599999999999994">
       <c r="A135" t="s">
-        <v>684</v>
+        <v>751</v>
       </c>
       <c r="B135" t="s">
-        <v>685</v>
+        <v>752</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>686</v>
+        <v>753</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>687</v>
+        <v>754</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="72.599999999999994">
       <c r="A136" t="s">
-        <v>688</v>
+        <v>755</v>
       </c>
       <c r="B136" t="s">
-        <v>685</v>
+        <v>752</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>689</v>
+        <v>756</v>
       </c>
       <c r="D136" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>690</v>
+        <v>757</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="72.599999999999994">
       <c r="A137" t="s">
-        <v>691</v>
+        <v>758</v>
       </c>
       <c r="B137" t="s">
-        <v>685</v>
+        <v>752</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>692</v>
+        <v>759</v>
       </c>
       <c r="D137" t="s">
-        <v>274</v>
+        <v>342</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>693</v>
+        <v>760</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="72.599999999999994">
       <c r="A138" t="s">
-        <v>694</v>
+        <v>761</v>
       </c>
       <c r="B138" t="s">
-        <v>685</v>
+        <v>752</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>695</v>
+        <v>762</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>696</v>
+        <v>763</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="57.95">
       <c r="A139" t="s">
-        <v>697</v>
+        <v>764</v>
       </c>
       <c r="B139" t="s">
         <v>54</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>698</v>
+        <v>765</v>
       </c>
       <c r="D139" t="s">
-        <v>699</v>
+        <v>766</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>700</v>
+        <v>767</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="72.599999999999994">
       <c r="A140" t="s">
-        <v>701</v>
+        <v>768</v>
       </c>
       <c r="B140" t="s">
-        <v>297</v>
+        <v>365</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>702</v>
+        <v>769</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>703</v>
+        <v>770</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="57.95">
+      <c r="A141" t="s">
+        <v>771</v>
+      </c>
+      <c r="B141" t="s">
+        <v>379</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="D141" t="s">
+        <v>253</v>
+      </c>
+      <c r="E141" s="4" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="87">
+      <c r="A142" t="s">
+        <v>111</v>
+      </c>
+      <c r="B142" t="s">
+        <v>111</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="D142" t="s">
+        <v>775</v>
+      </c>
+      <c r="E142" s="4" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" ht="72.599999999999994">
+      <c r="A143" t="s">
+        <v>777</v>
+      </c>
+      <c r="B143" t="s">
+        <v>630</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>778</v>
+      </c>
+      <c r="D143" t="s">
+        <v>202</v>
+      </c>
+      <c r="E143" s="4" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" ht="87">
+      <c r="A144" t="s">
+        <v>780</v>
+      </c>
+      <c r="B144" t="s">
+        <v>111</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="D144" t="s">
+        <v>782</v>
+      </c>
+      <c r="E144" s="4" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" ht="57.95">
+      <c r="A145" t="s">
+        <v>784</v>
+      </c>
+      <c r="B145" t="s">
+        <v>319</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>785</v>
+      </c>
+      <c r="D145" t="s">
+        <v>786</v>
+      </c>
+      <c r="E145" s="4" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" ht="72.599999999999994">
+      <c r="A146" t="s">
+        <v>788</v>
+      </c>
+      <c r="B146" t="s">
+        <v>379</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>789</v>
+      </c>
+      <c r="D146" t="s">
+        <v>790</v>
+      </c>
+      <c r="E146" s="4" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" ht="57.95">
+      <c r="A147" t="s">
+        <v>792</v>
+      </c>
+      <c r="B147" t="s">
+        <v>379</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="D147" t="s">
+        <v>794</v>
+      </c>
+      <c r="E147" s="4" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" ht="72.599999999999994">
+      <c r="A148" t="s">
+        <v>796</v>
+      </c>
+      <c r="B148" t="s">
+        <v>379</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="D148" t="s">
+        <v>798</v>
+      </c>
+      <c r="E148" s="4" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" ht="72.599999999999994">
+      <c r="A149" t="s">
+        <v>800</v>
+      </c>
+      <c r="B149" t="s">
+        <v>319</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="D149" t="s">
+        <v>802</v>
+      </c>
+      <c r="E149" s="4" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" ht="72.599999999999994">
+      <c r="A150" t="s">
+        <v>804</v>
+      </c>
+      <c r="B150" t="s">
+        <v>379</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>805</v>
+      </c>
+      <c r="D150" t="s">
+        <v>802</v>
+      </c>
+      <c r="E150" s="4" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="57.95">
+      <c r="A151" t="s">
+        <v>807</v>
+      </c>
+      <c r="B151" t="s">
+        <v>379</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="D151" t="s">
+        <v>802</v>
+      </c>
+      <c r="E151" s="4" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" ht="57.95">
+      <c r="A152" t="s">
+        <v>810</v>
+      </c>
+      <c r="B152" t="s">
+        <v>406</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="D152" t="s">
+        <v>356</v>
+      </c>
+      <c r="E152" s="4" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" ht="57.95">
+      <c r="A153" t="s">
+        <v>813</v>
+      </c>
+      <c r="B153" t="s">
+        <v>45</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>814</v>
+      </c>
+      <c r="D153" t="s">
+        <v>356</v>
+      </c>
+      <c r="E153" s="4" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" ht="57.95">
+      <c r="A154" t="s">
+        <v>816</v>
+      </c>
+      <c r="B154" t="s">
+        <v>406</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>817</v>
+      </c>
+      <c r="D154" t="s">
+        <v>356</v>
+      </c>
+      <c r="E154" s="4" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" ht="72.599999999999994">
+      <c r="A155" t="s">
+        <v>819</v>
+      </c>
+      <c r="B155" t="s">
+        <v>45</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="D155" t="s">
+        <v>356</v>
+      </c>
+      <c r="E155" s="4" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" ht="43.5">
+      <c r="A156" t="s">
+        <v>822</v>
+      </c>
+      <c r="B156" t="s">
+        <v>365</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>823</v>
+      </c>
+      <c r="D156" t="s">
+        <v>824</v>
+      </c>
+      <c r="E156" s="4" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" ht="57.95">
+      <c r="A157" t="s">
+        <v>826</v>
+      </c>
+      <c r="B157" t="s">
+        <v>379</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>827</v>
+      </c>
+      <c r="D157" t="s">
+        <v>385</v>
+      </c>
+      <c r="E157" s="4" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" ht="57.95">
+      <c r="A158" t="s">
+        <v>829</v>
+      </c>
+      <c r="B158" t="s">
+        <v>365</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="D158" t="s">
+        <v>831</v>
+      </c>
+      <c r="E158" s="4" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" ht="57.95">
+      <c r="A159" t="s">
+        <v>833</v>
+      </c>
+      <c r="B159" t="s">
+        <v>379</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>834</v>
+      </c>
+      <c r="D159" t="s">
+        <v>831</v>
+      </c>
+      <c r="E159" s="4" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" ht="87">
+      <c r="A160" t="s">
+        <v>836</v>
+      </c>
+      <c r="B160" t="s">
+        <v>111</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="D160" t="s">
+        <v>838</v>
+      </c>
+      <c r="E160" s="4" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" ht="57.95">
+      <c r="A161" t="s">
+        <v>840</v>
+      </c>
+      <c r="B161" t="s">
+        <v>319</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>841</v>
+      </c>
+      <c r="D161" t="s">
+        <v>842</v>
+      </c>
+      <c r="E161" s="4" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" ht="72.599999999999994">
+      <c r="A162" t="s">
+        <v>844</v>
+      </c>
+      <c r="B162" t="s">
+        <v>319</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="D162" t="s">
+        <v>802</v>
+      </c>
+      <c r="E162" s="4" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" ht="72.599999999999994">
+      <c r="A163" t="s">
+        <v>847</v>
+      </c>
+      <c r="B163" t="s">
+        <v>379</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>848</v>
+      </c>
+      <c r="D163" t="s">
+        <v>802</v>
+      </c>
+      <c r="E163" s="4" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" ht="72.599999999999994">
+      <c r="A164" t="s">
+        <v>850</v>
+      </c>
+      <c r="B164" t="s">
+        <v>406</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>851</v>
+      </c>
+      <c r="D164" t="s">
+        <v>852</v>
+      </c>
+      <c r="E164" s="4" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="72.599999999999994">
+      <c r="A165" t="s">
+        <v>854</v>
+      </c>
+      <c r="B165" t="s">
+        <v>45</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>855</v>
+      </c>
+      <c r="D165" t="s">
+        <v>856</v>
+      </c>
+      <c r="E165" s="4" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" ht="72.599999999999994">
+      <c r="A166" t="s">
+        <v>858</v>
+      </c>
+      <c r="B166" t="s">
+        <v>406</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="D166" t="s">
+        <v>356</v>
+      </c>
+      <c r="E166" s="4" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" ht="72.599999999999994">
+      <c r="A167" t="s">
+        <v>861</v>
+      </c>
+      <c r="B167" t="s">
+        <v>379</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>862</v>
+      </c>
+      <c r="D167" t="s">
+        <v>687</v>
+      </c>
+      <c r="E167" s="4" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" ht="72.599999999999994">
+      <c r="A168" t="s">
+        <v>864</v>
+      </c>
+      <c r="B168" t="s">
+        <v>379</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>865</v>
+      </c>
+      <c r="D168" t="s">
+        <v>687</v>
+      </c>
+      <c r="E168" s="4" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="57.95">
+      <c r="A169" t="s">
+        <v>867</v>
+      </c>
+      <c r="B169" t="s">
+        <v>379</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>868</v>
+      </c>
+      <c r="D169" t="s">
+        <v>687</v>
+      </c>
+      <c r="E169" s="4" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" ht="87">
+      <c r="A170" t="s">
+        <v>870</v>
+      </c>
+      <c r="B170" t="s">
+        <v>379</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>871</v>
+      </c>
+      <c r="D170" t="s">
+        <v>687</v>
+      </c>
+      <c r="E170" s="4" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" ht="72.599999999999994">
+      <c r="A171" t="s">
+        <v>873</v>
+      </c>
+      <c r="B171" t="s">
+        <v>379</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>874</v>
+      </c>
+      <c r="D171" t="s">
+        <v>580</v>
+      </c>
+      <c r="E171" s="4" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" ht="72.599999999999994">
+      <c r="A172" t="s">
+        <v>876</v>
+      </c>
+      <c r="B172" t="s">
+        <v>134</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>877</v>
+      </c>
+      <c r="D172" t="s">
+        <v>105</v>
+      </c>
+      <c r="E172" s="4" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" ht="57.95">
+      <c r="A173" t="s">
+        <v>879</v>
+      </c>
+      <c r="B173" t="s">
+        <v>134</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>880</v>
+      </c>
+      <c r="D173" t="s">
+        <v>105</v>
+      </c>
+      <c r="E173" s="4" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" ht="72.599999999999994">
+      <c r="A174" t="s">
+        <v>882</v>
+      </c>
+      <c r="B174" t="s">
+        <v>134</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>883</v>
+      </c>
+      <c r="D174" t="s">
+        <v>884</v>
+      </c>
+      <c r="E174" s="4" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" ht="57.95">
+      <c r="A175" t="s">
+        <v>886</v>
+      </c>
+      <c r="B175" t="s">
+        <v>752</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D175" t="s">
+        <v>888</v>
+      </c>
+      <c r="E175" s="4" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" ht="72.599999999999994">
+      <c r="A176" t="s">
+        <v>890</v>
+      </c>
+      <c r="B176" t="s">
+        <v>752</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>891</v>
+      </c>
+      <c r="D176" t="s">
+        <v>892</v>
+      </c>
+      <c r="E176" s="4" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" ht="57.95">
+      <c r="A177" t="s">
+        <v>894</v>
+      </c>
+      <c r="B177" t="s">
+        <v>752</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>895</v>
+      </c>
+      <c r="D177" t="s">
+        <v>802</v>
+      </c>
+      <c r="E177" s="4" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" ht="72.599999999999994">
+      <c r="A178" t="s">
+        <v>897</v>
+      </c>
+      <c r="B178" t="s">
+        <v>54</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="D178" t="s">
+        <v>899</v>
+      </c>
+      <c r="E178" s="4" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" ht="72.599999999999994">
+      <c r="A179" t="s">
+        <v>901</v>
+      </c>
+      <c r="B179" t="s">
+        <v>54</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>902</v>
+      </c>
+      <c r="D179" t="s">
+        <v>794</v>
+      </c>
+      <c r="E179" s="4" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" ht="72.599999999999994">
+      <c r="A180" t="s">
+        <v>904</v>
+      </c>
+      <c r="B180" t="s">
+        <v>379</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>905</v>
+      </c>
+      <c r="D180" t="s">
+        <v>906</v>
+      </c>
+      <c r="E180" s="4" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" ht="72.599999999999994">
+      <c r="A181" t="s">
+        <v>908</v>
+      </c>
+      <c r="B181" t="s">
+        <v>379</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>909</v>
+      </c>
+      <c r="D181" t="s">
+        <v>906</v>
+      </c>
+      <c r="E181" s="4" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" ht="57.95">
+      <c r="A182" t="s">
+        <v>911</v>
+      </c>
+      <c r="B182" t="s">
+        <v>379</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="D182" t="s">
+        <v>892</v>
+      </c>
+      <c r="E182" s="4" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" ht="57.95">
+      <c r="A183" t="s">
+        <v>914</v>
+      </c>
+      <c r="B183" t="s">
+        <v>319</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="D183" t="s">
+        <v>916</v>
+      </c>
+      <c r="E183" s="4" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" ht="72.599999999999994">
+      <c r="A184" t="s">
+        <v>918</v>
+      </c>
+      <c r="B184" t="s">
+        <v>319</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="D184" t="s">
+        <v>916</v>
+      </c>
+      <c r="E184" s="4" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" ht="57.95">
+      <c r="A185" t="s">
+        <v>921</v>
+      </c>
+      <c r="B185" t="s">
+        <v>345</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="D185" t="s">
+        <v>884</v>
+      </c>
+      <c r="E185" s="4" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" ht="57.95">
+      <c r="A186" t="s">
+        <v>924</v>
+      </c>
+      <c r="B186" t="s">
+        <v>345</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="D186" t="s">
+        <v>884</v>
+      </c>
+      <c r="E186" s="4" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" ht="57.95">
+      <c r="A187" t="s">
+        <v>927</v>
+      </c>
+      <c r="B187" t="s">
+        <v>45</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>928</v>
+      </c>
+      <c r="D187" t="s">
+        <v>929</v>
+      </c>
+      <c r="E187" s="4" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" ht="57.95">
+      <c r="A188" t="s">
+        <v>931</v>
+      </c>
+      <c r="B188" t="s">
+        <v>111</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="D188" t="s">
+        <v>933</v>
+      </c>
+      <c r="E188" s="4" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" ht="57.95">
+      <c r="A189" t="s">
+        <v>935</v>
+      </c>
+      <c r="B189" t="s">
+        <v>379</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>936</v>
+      </c>
+      <c r="D189" t="s">
+        <v>786</v>
+      </c>
+      <c r="E189" s="4" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" ht="72.599999999999994">
+      <c r="A190" t="s">
+        <v>938</v>
+      </c>
+      <c r="B190" t="s">
+        <v>379</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>939</v>
+      </c>
+      <c r="D190" t="s">
+        <v>786</v>
+      </c>
+      <c r="E190" s="4" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" ht="57.95">
+      <c r="A191" t="s">
+        <v>941</v>
+      </c>
+      <c r="B191" t="s">
+        <v>365</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>942</v>
+      </c>
+      <c r="D191" t="s">
+        <v>943</v>
+      </c>
+      <c r="E191" s="4" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" ht="72.599999999999994">
+      <c r="A192" t="s">
+        <v>945</v>
+      </c>
+      <c r="B192" t="s">
+        <v>379</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>946</v>
+      </c>
+      <c r="D192" t="s">
+        <v>947</v>
+      </c>
+      <c r="E192" s="4" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" ht="87">
+      <c r="A193" t="s">
+        <v>949</v>
+      </c>
+      <c r="B193" t="s">
+        <v>379</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="D193" t="s">
+        <v>356</v>
+      </c>
+      <c r="E193" s="4" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" ht="72.599999999999994">
+      <c r="A194" t="s">
+        <v>403</v>
+      </c>
+      <c r="B194" t="s">
+        <v>379</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="D194" t="s">
+        <v>403</v>
+      </c>
+      <c r="E194" s="4" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" ht="72.599999999999994">
+      <c r="A195" t="s">
+        <v>954</v>
+      </c>
+      <c r="B195" t="s">
+        <v>379</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="D195" t="s">
+        <v>956</v>
+      </c>
+      <c r="E195" s="4" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" ht="57.95">
+      <c r="A196" t="s">
+        <v>958</v>
+      </c>
+      <c r="B196" t="s">
+        <v>54</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>959</v>
+      </c>
+      <c r="D196" t="s">
+        <v>960</v>
+      </c>
+      <c r="E196" s="4" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" ht="43.5">
+      <c r="A197" t="s">
+        <v>962</v>
+      </c>
+      <c r="B197" t="s">
+        <v>379</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>963</v>
+      </c>
+      <c r="D197" t="s">
+        <v>105</v>
+      </c>
+      <c r="E197" s="4" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" ht="29.1">
+      <c r="A198" t="s">
+        <v>965</v>
+      </c>
+      <c r="B198" t="s">
+        <v>379</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>966</v>
+      </c>
+      <c r="D198" t="s">
+        <v>916</v>
+      </c>
+      <c r="E198" s="4" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" ht="29.1">
+      <c r="A199" t="s">
+        <v>968</v>
+      </c>
+      <c r="B199" t="s">
+        <v>379</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>969</v>
+      </c>
+      <c r="D199" t="s">
+        <v>916</v>
+      </c>
+      <c r="E199" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" ht="57.95">
+      <c r="A200" t="s">
+        <v>971</v>
+      </c>
+      <c r="B200" t="s">
+        <v>319</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>972</v>
+      </c>
+      <c r="D200" t="s">
+        <v>842</v>
+      </c>
+      <c r="E200" s="4" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" ht="72.599999999999994">
+      <c r="A201" t="s">
+        <v>974</v>
+      </c>
+      <c r="B201" t="s">
+        <v>319</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>975</v>
+      </c>
+      <c r="D201" t="s">
+        <v>976</v>
+      </c>
+      <c r="E201" s="4" t="s">
+        <v>977</v>
       </c>
     </row>
   </sheetData>
@@ -7207,4 +9753,139 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8D0B573-CB40-455A-8450-09C524808966}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="77.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>978</v>
+      </c>
+      <c r="B1" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>980</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>981</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>983</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>985</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>712</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>988</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>990</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>274</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>993</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>995</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>997</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>187</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>999</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="https://www.hfma.org/" xr:uid="{FAD2F71A-A537-4FD5-AF5D-6954B237B293}"/>
+    <hyperlink ref="B3" r:id="rId2" display="https://www.beckershospitalreview.com/" xr:uid="{E89BC5BF-5431-4F5E-B1D1-020EBB6C7EC8}"/>
+    <hyperlink ref="B4" r:id="rId3" display="https://www.beckershospitalreview.com/supply-chain/" xr:uid="{5EE1FFDF-8EB0-402C-A431-BC8F4F61E6AB}"/>
+    <hyperlink ref="B5" r:id="rId4" display="https://www.beckershospitalreview.com/print-issue-category/beckers-clinical-leadership/" xr:uid="{0A81105F-B936-4C23-9BD1-1EFC5EA696A6}"/>
+    <hyperlink ref="B6" r:id="rId5" display="https://www.ache.org/" xr:uid="{CE97D364-485D-4667-B364-BB2D370B83D1}"/>
+    <hyperlink ref="B7" r:id="rId6" display="https://www.mgma.com/" xr:uid="{1D2641C2-5A27-498C-8FDD-3D5E48100E92}"/>
+    <hyperlink ref="B8" r:id="rId7" display="https://www.cms.gov/training-education/medicare-learning-networkr-mln/resources-training/mln-matters-articles" xr:uid="{7ECE03F7-5E0E-42B3-A2E3-43918D0F32D8}"/>
+    <hyperlink ref="B9" r:id="rId8" display="https://www.ismworld.org/" xr:uid="{807CA2EB-D259-4BB9-8F6A-691099A27556}"/>
+    <hyperlink ref="B10" r:id="rId9" display="https://www.himss.org/" xr:uid="{846A2FC2-11CC-4B41-8AAF-6DFAA78AD3FC}"/>
+    <hyperlink ref="B11" r:id="rId10" display="https://www.ihi.org/" xr:uid="{C65DC3B6-4CC8-49F9-BFD6-61C567123CB2}"/>
+    <hyperlink ref="B12" r:id="rId11" display="https://nahq.org/?keyword=nahq&amp;matchtype=e&amp;device=c&amp;lpurl=https%3A%2F%2Fnahq.org%2F&amp;campaign=Microsoft%20-%20NAHQ%20Brand&amp;adgroup=%5Bnahq%5D&amp;msclkid=ca7a19f143d8170f51ee73b72cfceff6&amp;utm_source=bing&amp;utm_medium=cpc&amp;utm_campaign=Microsoft%20-%20NAHQ%20Brand&amp;utm_term=nahq&amp;utm_content=%5Bnahq%5D" xr:uid="{6F464490-87CE-4EE0-A617-14C356DA6FDA}"/>
+    <hyperlink ref="B13" r:id="rId12" xr:uid="{86995982-B5A6-4E8F-8736-0250EFD4BD30}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId13"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/data/Resources and Terminology for Healthcare Indsutry Trends Website.xlsx
+++ b/data/Resources and Terminology for Healthcare Indsutry Trends Website.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30305"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://impactadvisors3-my.sharepoint.com/personal/john_decicco_impact-advisors_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6556BCE9-2C9C-42B7-87BC-20CBF2E3985C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{51E13B2B-C04E-4AD6-887E-44694F737EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="1" xr2:uid="{AE6C2486-B33D-41C7-9864-3BA3013F76A0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{AE6C2486-B33D-41C7-9864-3BA3013F76A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Healthcare Resources" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1829" uniqueCount="1000">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2284" uniqueCount="1166">
   <si>
     <t xml:space="preserve">Title of Source </t>
   </si>
@@ -982,6 +982,48 @@
     <t>HealthcareReader</t>
   </si>
   <si>
+    <t>The Growth of Private Equity in US Health Care: Impact and Outlook</t>
+  </si>
+  <si>
+    <t>NIHCM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why Owns a Hospital: Nonprofit, For-Profit &amp; Government </t>
+  </si>
+  <si>
+    <t>legalclarity.org</t>
+  </si>
+  <si>
+    <t>https://legalclarity.org/who-owns-a-hospital-ownership-structures-explained/</t>
+  </si>
+  <si>
+    <t>Breaking Down U.S. Hospital Payor Mixes</t>
+  </si>
+  <si>
+    <t>Understanding Hospital Payor Mixes Across the U.S</t>
+  </si>
+  <si>
+    <t>UnitedHealthcare 2026 Health Trends Report</t>
+  </si>
+  <si>
+    <t>UnitedHealthcare</t>
+  </si>
+  <si>
+    <t>UnitedHealthcare 2026 Health Trends Report | Employer | UnitedHealthcare</t>
+  </si>
+  <si>
+    <t>What's Behind Rising Health Insurance Costs?</t>
+  </si>
+  <si>
+    <t>What’s Behind Rising Health Insurance Costs? | Johns Hopkins | Bloomberg School of Public Health</t>
+  </si>
+  <si>
+    <t>The Pros and Cons of the Affordable Care Act</t>
+  </si>
+  <si>
+    <t>Health Markets</t>
+  </si>
+  <si>
     <t xml:space="preserve">Term Name </t>
   </si>
   <si>
@@ -2977,77 +3019,533 @@
     <t>A patient is treated for pneumonia during an inpatient stay. The provider documents the diagnosis, treatment, medications, and procedures. A medical coder reviews the documentation and assigns the correct ICD-10 diagnosis code and procedure codes so the hospital can submit an accurate claim to the payer.</t>
   </si>
   <si>
-    <t>Website Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Link </t>
-  </si>
-  <si>
-    <t>HFMA.org</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beckers Hospital Review </t>
-  </si>
-  <si>
-    <t>Becker's Hospital Review | Healthcare News &amp; Analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beckers Supply Chain </t>
-  </si>
-  <si>
-    <t>Supply Chain Archives - Becker's Hospital Review | Healthcare News &amp; Analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beckers Clinical Leadership </t>
-  </si>
-  <si>
-    <t>Becker's Clinical Leadership Archives - Becker's Hospital Review | Healthcare News &amp; Analysis</t>
-  </si>
-  <si>
-    <t>American College of Healthcare Executives | American College of Healthcare Executives</t>
-  </si>
-  <si>
-    <t>MGMA.com</t>
-  </si>
-  <si>
-    <t>Medical Group Management Association - MGMA</t>
-  </si>
-  <si>
-    <t>CMS.gov</t>
-  </si>
-  <si>
-    <t>MLN Matters® Articles | CMS</t>
-  </si>
-  <si>
-    <t>Home</t>
-  </si>
-  <si>
-    <t>HIMSS.org</t>
-  </si>
-  <si>
-    <t>Healthcare Information and Management Systems Society | HIMSS</t>
-  </si>
-  <si>
-    <t>IHI.org</t>
-  </si>
-  <si>
-    <t>Home | Institute for Healthcare Improvement</t>
-  </si>
-  <si>
-    <t>NAHQ.org</t>
-  </si>
-  <si>
-    <t>Home - NAHQ</t>
-  </si>
-  <si>
-    <t>https://www.ahrmm.org/</t>
+    <t>Authorization Throughput</t>
+  </si>
+  <si>
+    <t>Authorization Throughput measures how quickly and efficiently a healthcare organization completes prior authorizations for services, procedures, medications, or tests before care is delivered. It helps show whether the authorization team is keeping up with request volume and preventing delays in patient care or reimbursement.</t>
+  </si>
+  <si>
+    <t>A hospital tracks how many MRI authorization requests are completed each day. If requests are piling up and approvals are taking too long, patients may experience scheduling delays and the hospital may risk denied claims if care happens before approval is received.</t>
+  </si>
+  <si>
+    <t>Point-of-Service (POS) Collections</t>
+  </si>
+  <si>
+    <t>Point-of-Service Collections refers to the process of collecting a patient's financial responsibility at or before the time care is provided. This can include copays, deductibles, coinsurance, outstanding balances, or self-pay estimates.</t>
+  </si>
+  <si>
+    <t>A patient arrives for an outpatient surgery, and the front desk collects the estimated $150 copay before the procedure. This helpe the hospital improve cash flow and reduce the amount it has to collect after the visit.</t>
+  </si>
+  <si>
+    <t>Payment Variance</t>
+  </si>
+  <si>
+    <t>Payment variance is the difference between the amount a healthcare organization is expected to receive from a payer and the amount it actually received. It is often caused by underpayments, overpayments, contract differences, payer errors, coding issues, or incorrect reimbursement calculations</t>
+  </si>
+  <si>
+    <t>HFMA / CMS</t>
+  </si>
+  <si>
+    <t>A hospital expects Blue Cross to pay $2,500 for a procedure based on its contract, but the payer only sends $2,200. The $300 difference is a payment variance that the revenue cycle team would review and potentially appeal to correct.</t>
+  </si>
+  <si>
+    <t>Workqueues</t>
+  </si>
+  <si>
+    <t>Workqueues are organized lists of tasks, accounts, claims, or issues that need action from a revenue cycle team. They help staff prioritize work such as claim edits, denials, missing authorizations, coding holds, registration errors, or unpaid balances.</t>
+  </si>
+  <si>
+    <t>A hospital billing team may used a denial workqueue to see every claim that was denied by insurance. Staff work through the queue, fix the issue, submit an appeal it needed, and move the claim forward for payment.</t>
+  </si>
+  <si>
+    <t>Charge Lag</t>
+  </si>
+  <si>
+    <t>Charge lag is the amount of time between when a healthcare service is provided and when the charge is entered into the billing system. A high charge lag can delay claim submission, slow reimbursement, and create revenue leakage if charges are missed.</t>
+  </si>
+  <si>
+    <t>A patient receives lab work on Monday, but the charge is not entered into the system until Friday. That four-day delay is charge lag and can slow down the hospital's ability to bill the payer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decentralized Reconciliation Model </t>
+  </si>
+  <si>
+    <t>A decentralized reconciliation model is when reconciliation work is handled by multiple departments, teams, or locations instead of one centralized team. In healthcare revenue cycle, this may mean different clinics, departments, or billing teams are responsible for reconciling their own charges, payments, denials, or account balances.</t>
+  </si>
+  <si>
+    <t>A health system has each hospital department reconcile its own payment variances and charge issues instead of sending everything to one central revenue cycle team. This can give departments more ownership, but it may also create inconsistency if team follows a different process.</t>
+  </si>
+  <si>
+    <t>Quality Program</t>
+  </si>
+  <si>
+    <t>A quality program is a structured set of initiatives, metrics, standards, and improvement efforts used to measure and improve the saefty, effectiveness, efficiency, and patient experience of care. In healthcare, quality programs often track outcomes, readmissions, infections, patient satisfaction, compliance, and performance against value-based care meaures.</t>
+  </si>
+  <si>
+    <t>A hospital may run a quality program focused on reducing hospital-acquired infections. The team tracks infection rates, reviews root causes, updates clinical workflows, trains staff, and measures whether patient outcomes improve over time.</t>
+  </si>
+  <si>
+    <t>Central Sterile Processing Department (CSPD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Central Sterile Processing Department is the hospital department responsible for cleaning, disinfecting, sterilizing, storing, and distributing surgical instruments, medical equipment, and supplies.  CSPD helps ensure that clinical teams have safe, sterile, and ready-to-use instruments for patient care. </t>
+  </si>
+  <si>
+    <t>AAMI</t>
+  </si>
+  <si>
+    <t>Before an operating room case, used surgical instruments are sent to CSPD, where they are cleaned, sterilized, packaged, and returned so they can be safely used for the next patient procedure.</t>
+  </si>
+  <si>
+    <t>The Role of Private Equity Funds in Healthcare: Trends, Impact, and Policy Responses</t>
+  </si>
+  <si>
+    <t>ScienceDirect</t>
+  </si>
+  <si>
+    <t>The role of private equity funds in healthcare: trends, impact and policy responses - ScienceDirect</t>
+  </si>
+  <si>
+    <t>OMB Grant Rules Raises Compliance Question For Hospital Federal Funding</t>
+  </si>
+  <si>
+    <t>https://www.hfma.org/payment-reimbursement-and-managed-care/omb-grant-rule-hospital-federal-funding/</t>
+  </si>
+  <si>
+    <t>MedPAC Sees No Broad Medicare Advantage Hit To Hospital Finances</t>
+  </si>
+  <si>
+    <t>Medicare Advantage hospital finances | HFMA</t>
+  </si>
+  <si>
+    <t>House Bill Would Increase Tax-Exempt Hospital Reporting Requirements</t>
+  </si>
+  <si>
+    <t>Tax-exempt hospital reporting bill advances | HFMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hospital Drug and Supply Expenses Push Finance Teams To Rethink Cost Strategy </t>
+  </si>
+  <si>
+    <t>Hospital drug and supply costs pressure finance teams | HFMA</t>
+  </si>
+  <si>
+    <t>White House Zooms In On Hospital Contracts</t>
+  </si>
+  <si>
+    <t>scrutiny of hospital contract provisions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Hospital of the future, with Jeni Williams </t>
+  </si>
+  <si>
+    <t>The hospital of the future, with Jeni Williams | HFMA</t>
+  </si>
+  <si>
+    <t>Stable Staff-To-Physician Ratios Might Conceal Real Strain in Your Practice</t>
+  </si>
+  <si>
+    <t>Stable staff-to-physician ratios might conceal real strain in your practice</t>
+  </si>
+  <si>
+    <t>Revenue Growth Narrows As Costs Climb: The 2026 Squeeze on Medical Practices</t>
+  </si>
+  <si>
+    <t>Revenue growth narrows as costs climb: the 2026 squeeze on medical practices</t>
+  </si>
+  <si>
+    <t>Operating Costs Keep Climbing For Medical Practices in 2026</t>
+  </si>
+  <si>
+    <t>Operating costs keep climbing for medical practices in 2026</t>
+  </si>
+  <si>
+    <t>Medicare Practice Worker Benefits: Where Retention Tools Meet Cost Pressure</t>
+  </si>
+  <si>
+    <t>Medical practice worker benefits: Where retention tools meet cost pressure</t>
+  </si>
+  <si>
+    <t>Why Change Fails in Medical Groups and How Leaders Can Remove The Friction</t>
+  </si>
+  <si>
+    <t>Why change fails in medical groups and how leaders can remove the friction</t>
+  </si>
+  <si>
+    <t>Fill The Right Slot: Designing Backfill and Overbooking By Specialty</t>
+  </si>
+  <si>
+    <t>Fill the right slot: Designing backfill and overbooking by specialty</t>
+  </si>
+  <si>
+    <t>In Preliminary Rate Filings, ACA Marketplace Insurers Largely Propose Double-Digit Premium Increase For 2027</t>
+  </si>
+  <si>
+    <t>In Preliminary Rate Filings, ACA Marketplace Insurers Largely Propose Double-Digit Premium Increase For 2027, Following a Steep Climb This Year  | KFF</t>
+  </si>
+  <si>
+    <t>The Average Marketplace Deductible Grew by About $1,000 Per Person in 2026</t>
+  </si>
+  <si>
+    <t>The Average Marketplace Deductible Grew by About $1,000 Per Person in 2026, With More Enrollees Shifting to Higher-Deductible Plans as Enhanced Tax Credits Expired | KFF</t>
+  </si>
+  <si>
+    <t>ACA Marketplace Enrollment Is Down By 3 Million After Big Jump in Premium Payments</t>
+  </si>
+  <si>
+    <t>ACA Marketplace Enrollment Is Down By 3 Million After Big Jump in Premium Payments | KFF Quick Takes</t>
+  </si>
+  <si>
+    <t>Did the Affordable Care Act Make Health Care More Affordable</t>
+  </si>
+  <si>
+    <t>Did the Affordable Care Act Make Health Care More Affordable? | KFF</t>
+  </si>
+  <si>
+    <t>The Affordable Care Act 101</t>
+  </si>
+  <si>
+    <t>The Affordable Care Act 101 | KFF</t>
+  </si>
+  <si>
+    <t>Health Care Costs Keep Rising… Why and Who Pays?</t>
+  </si>
+  <si>
+    <t>Health Care Costs Keep Rising … Why and Who Pays? | KFF</t>
+  </si>
+  <si>
+    <t>KFF Health Tracking Poll: Health Care Costs and The Midterms</t>
+  </si>
+  <si>
+    <t>KFF Health Tracking Poll: Health Care Costs and the Midterms | KFF</t>
+  </si>
+  <si>
+    <t>Americans' Challenges With Health Care Costs</t>
+  </si>
+  <si>
+    <t>Americans’ Challenges with Health Care Costs | KFF</t>
+  </si>
+  <si>
+    <t>Hospital Prices Have Risen Much Faster for Private Insurance Than Medicare Since 2019</t>
+  </si>
+  <si>
+    <t>Hospital Prices Have Risen Much Faster for Private Insurance Than Medicare Since 2019 | KFF</t>
+  </si>
+  <si>
+    <t>What Are the Recent Trends in Employer-Based Health Coverage?</t>
+  </si>
+  <si>
+    <t>What Are the Recent Trends in Employer-Based Health Coverage? | KFF</t>
+  </si>
+  <si>
+    <t>Policy Changes Bring Renewed Focus on High-Deductible Health Plans</t>
+  </si>
+  <si>
+    <t>Policy Changes Bring Renewed Focus on High-Deductible Health Plans  | KFF</t>
+  </si>
+  <si>
+    <t>What Your Employer-Based Health Coverage Really Costs</t>
+  </si>
+  <si>
+    <t>What Your Employer-Based Health Coverage Really Costs | KFF</t>
+  </si>
+  <si>
+    <t>A New Option for Long-Term Care Costs</t>
+  </si>
+  <si>
+    <t>A New Option for Long-Term Care Costs - KFF Health News</t>
+  </si>
+  <si>
+    <t>11 Healthcare Bankruptcies in 2026</t>
+  </si>
+  <si>
+    <t>9 healthcare bankruptcies in 2026</t>
+  </si>
+  <si>
+    <t>Hospital Margins Dip To 2.9% Average As Expenses Grow, Care Shifts: 5 notes</t>
+  </si>
+  <si>
+    <t>Hospital margins dip to 2.9% average as expenses grow, care shifts: 5 notes - Becker's Hospital Review | Healthcare News &amp; Analysis</t>
+  </si>
+  <si>
+    <t>The Term 'Payvider' Isn't Very Useful</t>
+  </si>
+  <si>
+    <t>The term ‘payvider’ makes no sense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Medicaid Squeeze Hospitals Can't Lobby Their Way Out </t>
+  </si>
+  <si>
+    <t>The Medicaid squeeze hospitals can’t lobby their way out of</t>
+  </si>
+  <si>
+    <t>Anthropic's Claude Now Handles Healthcare Claims, Care Management</t>
+  </si>
+  <si>
+    <t>Anthropic’s Claude now handles healthcare claims, care management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 Healthcare Organizations Moving To Epic </t>
+  </si>
+  <si>
+    <t>7 health systems moving to Epic</t>
+  </si>
+  <si>
+    <t>How Value-Based Care Empowers Independent Practices</t>
+  </si>
+  <si>
+    <t>How Value-Based Care Empowers Independent Practices | Health Care Delivery Models | AMA STEPS Forward | AMA Ed Hub</t>
+  </si>
+  <si>
+    <t>Understanding Physician Billing and Coding To Reduce Documentation Burden</t>
+  </si>
+  <si>
+    <t>Simplified Outpatient Documentation and Coding: Understanding Physician Billing and Coding to Reduce Documentation Burden | Workflow and Process | AMA STEPS Forward | AMA Ed Hub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sharing Clinical Notes With Patients: A New Era of Transparency in Medicine </t>
+  </si>
+  <si>
+    <t>Sharing Clinical Notes With Patients: A New Era of Transparency in Medicine | Shared Decision Making and Communication | AMA STEPS Forward | AMA Ed Hub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revolutionizing Healthcare: The Role of Artificial Intelligence in Clinical Practice </t>
+  </si>
+  <si>
+    <t>NIH</t>
+  </si>
+  <si>
+    <t>Revolutionizing healthcare: the role of artificial intelligence in clinical practice - PMC</t>
+  </si>
+  <si>
+    <t>The Rise of AI in Healthcare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mayo Clinic </t>
+  </si>
+  <si>
+    <t>7 Ways AI is Transforming Healthcare</t>
+  </si>
+  <si>
+    <t>World Economic Forum</t>
+  </si>
+  <si>
+    <t>7 ways AI is transforming healthcare | World Economic Forum</t>
+  </si>
+  <si>
+    <t>Flipping The Script on Payer Denials and Downcoding</t>
+  </si>
+  <si>
+    <t>Healthcare Dive</t>
+  </si>
+  <si>
+    <t>Flipping the script on payer denials and downcoding | Healthcare Dive</t>
+  </si>
+  <si>
+    <t>What The Revenue Cycle Leaders of 2030 Will Know</t>
+  </si>
+  <si>
+    <t>What the revenue cycle leaders of 2030 will know </t>
+  </si>
+  <si>
+    <t>How Healthcare AI is Closing The Revenue Gap</t>
+  </si>
+  <si>
+    <t>How healthcare AI is closing the revenue gap | Healthcare Dive</t>
+  </si>
+  <si>
+    <t>Balancing AI Innovation and Risk: 5 Takeaways From HIMSS26</t>
+  </si>
+  <si>
+    <t>Balancing AI innovation and risk: 5 takeaways from HIMSS26 | Healthcare Dive</t>
+  </si>
+  <si>
+    <t>How Health Insurance Works When You Live In Multiple States</t>
+  </si>
+  <si>
+    <t>VeryWell Health</t>
+  </si>
+  <si>
+    <t>How Health Insurance Works When You Live in Multiple States</t>
+  </si>
+  <si>
+    <t>How To Protect Revenue In a Digital-First Ecosystem</t>
+  </si>
+  <si>
+    <t>How to protect revenue in a digital-first ecosystem | HFMA</t>
+  </si>
+  <si>
+    <t>Future Success Means Treating Revenue Cycle As A Strategic Asset, Not a Support Function</t>
+  </si>
+  <si>
+    <t>Future success means treating revenue cycle as a strategic asset, not a support function | HFMA</t>
+  </si>
+  <si>
+    <t>Why AI Alone Fails in Healthcare and How AI+ Human Co-Management Drives Better Outcomes</t>
+  </si>
+  <si>
+    <t>Why AI Alone Fails in Healthcare and How AI + Human Co-Management Drives Better Outcomes | HFMA</t>
+  </si>
+  <si>
+    <t>Medicare Claims Processing Modernization Gains Urgency At CMS</t>
+  </si>
+  <si>
+    <t>Medicare claims processing modernization at CMS | HFMA</t>
+  </si>
+  <si>
+    <t>Modernize Your Operations Model for RCM Success</t>
+  </si>
+  <si>
+    <t>Modernize Your Operations Model for RCM Success | HFMA</t>
+  </si>
+  <si>
+    <t>Healthcare Compliance Risks Rise as CMS Expands Fraud Enforcement</t>
+  </si>
+  <si>
+    <t>Healthcare fraud compliance and CMS oversight | HFMA</t>
+  </si>
+  <si>
+    <t>Building a More Effective Remittance Automation Strategy</t>
+  </si>
+  <si>
+    <t>Building a More Effective Remittance Automation Strategy | HFMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Healthcare Affordability and Financial Sustainability Concerns Test CFO Strategy </t>
+  </si>
+  <si>
+    <t>Healthcare affordability and sustainability | HFMA</t>
+  </si>
+  <si>
+    <t>Tracking Healthcare Data Breaches</t>
+  </si>
+  <si>
+    <t>Tracking healthcare data breaches | Healthcare Dive</t>
+  </si>
+  <si>
+    <t>ACA Premiums Set To Spike Again in 2027</t>
+  </si>
+  <si>
+    <t>ACA premiums set to spike again in 2027 | Healthcare Dive</t>
+  </si>
+  <si>
+    <t>Epic President To Step Down This Summer</t>
+  </si>
+  <si>
+    <t>Epic president to step down this summer | Healthcare Dive</t>
+  </si>
+  <si>
+    <t>AdaptHealth Discloses Patient Data Was Stolen in Cyberattack</t>
+  </si>
+  <si>
+    <t>AdaptHealth discloses patient data was stolen in cyberattack | Healthcare Dive</t>
+  </si>
+  <si>
+    <t>Private Equity May Skirt Oversight With Nonprofit Healthcare Joint Ventures</t>
+  </si>
+  <si>
+    <t>Private equity may skirt oversight with nonprofit healthcare joint ventures | Healthcare Dive</t>
+  </si>
+  <si>
+    <t>Healthcare Faces Congressional Oversight Heading Into 2026 Midterms and Beyond</t>
+  </si>
+  <si>
+    <t>Healthcare faces congressional oversight heading into 2026 midterms and beyond | Healthcare Dive</t>
+  </si>
+  <si>
+    <t>Nearly 4M Medicare Beneficiaries Could Access GLP-1s for Weight Loss Under New Program: Analysis</t>
+  </si>
+  <si>
+    <t>Nearly 4M Medicare beneficiaries could access GLP-1s for weight loss under new program: analysis | Healthcare Dive</t>
+  </si>
+  <si>
+    <t>US Health Spending spikes to $5.7T in 2025, Though growth should moderate, CMS finds</t>
+  </si>
+  <si>
+    <t>US health spending spikes to $5.7T in 2025, though growth should moderate, CMS finds | Healthcare Dive</t>
+  </si>
+  <si>
+    <t>Hackensack Meridan Health, Hunterdon Health Explore Merger in New Jersey</t>
+  </si>
+  <si>
+    <t>Hackensack Meridian Health, Hunterdon Health explore merger in New Jersey | Healthcare Dive</t>
+  </si>
+  <si>
+    <t>Centene Offers Employee Buyouts Amid Membership Losses</t>
+  </si>
+  <si>
+    <t>Centene offers employee buyouts amid membership losses | Healthcare Dive</t>
+  </si>
+  <si>
+    <t>Three Federal Streams, One Goverance Problem: Building Unified AI Oversight In Health Systems</t>
+  </si>
+  <si>
+    <t>Health Affairs</t>
+  </si>
+  <si>
+    <t>Three Federal Streams, One Governance Problem: Building Unified AI Oversight In Health Systems | Health Affairs</t>
+  </si>
+  <si>
+    <t>Medical Ethics Responds To Private Equity</t>
+  </si>
+  <si>
+    <t>Medical Ethics Responds To Private Equity | Health Affairs</t>
+  </si>
+  <si>
+    <t>Trends In US Health Care Spending By Income, 2005-2023</t>
+  </si>
+  <si>
+    <t>Trends In US Health Care Spending By Income, 2005–23 | Health Affairs</t>
+  </si>
+  <si>
+    <t>States Are Exceeding Their Health Care Cost Growth Targets. What Does It Mean?</t>
+  </si>
+  <si>
+    <t>States Are Exceeding Their Health Care Cost Growth Targets. What Does It Mean? | Health Affairs</t>
+  </si>
+  <si>
+    <t>Why New Drugs And AI Chatbots Won't Cure Health Care's Cost Disease</t>
+  </si>
+  <si>
+    <t>Why New Drugs And AI Chatbots Won’t Cure Health Care’s Cost Disease | Health Affairs</t>
+  </si>
+  <si>
+    <t>Price Transparency, Medicare, Medicaid, And More</t>
+  </si>
+  <si>
+    <t>Price Transparency, Medicare, Medicaid, And More | Health Affairs</t>
+  </si>
+  <si>
+    <t>Cost-Effectiveness Thresholds: Overvaluing Innovation, Undervaluing Health</t>
+  </si>
+  <si>
+    <t>Cost-Effectiveness Thresholds: Overvaluing Innovation, Undervaluing Health | Health Affairs</t>
+  </si>
+  <si>
+    <t>Levels, Growth, And Semantics: The Role Of Prices In Driving Health Care Spending</t>
+  </si>
+  <si>
+    <t>Levels, Growth, And Semantics: The Role Of Prices In Driving Health Care Spending | Health Affairs</t>
+  </si>
+  <si>
+    <t>Medicare's Unrealized Opportunity: Using ACOs To Create Real Competition</t>
+  </si>
+  <si>
+    <t>Medicare’s Unrealized Opportunity: Using ACOs To Create Real Competition | Health Affairs</t>
+  </si>
+  <si>
+    <t>The US Health Spending Problem Is Still About Prices</t>
+  </si>
+  <si>
+    <t>The US Health Spending Problem Is Still About Prices | Health Affairs</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3082,16 +3580,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -3108,12 +3626,89 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3124,12 +3719,87 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3143,8 +3813,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A2C3F0C7-761E-4B5C-A66C-E7C10F64F36F}" name="Table4" displayName="Table4" ref="A1:F134" totalsRowShown="0">
-  <autoFilter ref="A1:F134" xr:uid="{A2C3F0C7-761E-4B5C-A66C-E7C10F64F36F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A2C3F0C7-761E-4B5C-A66C-E7C10F64F36F}" name="Table4" displayName="Table4" ref="A1:F140" totalsRowShown="0">
+  <autoFilter ref="A1:F140" xr:uid="{A2C3F0C7-761E-4B5C-A66C-E7C10F64F36F}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{3A186EF0-DE4D-4AF5-9E14-55E37A3897F0}" name="Title of Source "/>
     <tableColumn id="2" xr3:uid="{431EDF38-AFCC-4E7A-8DE6-340618238528}" name="Website"/>
@@ -3158,8 +3828,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3A77FCFC-C270-4744-BFD3-3F97DC940B05}" name="Table5" displayName="Table5" ref="A1:E201" totalsRowShown="0">
-  <autoFilter ref="A1:E201" xr:uid="{3A77FCFC-C270-4744-BFD3-3F97DC940B05}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3A77FCFC-C270-4744-BFD3-3F97DC940B05}" name="Table5" displayName="Table5" ref="A1:E209" totalsRowShown="0">
+  <autoFilter ref="A1:E209" xr:uid="{3A77FCFC-C270-4744-BFD3-3F97DC940B05}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{6D94F78D-1D88-44BF-BBF7-E41A3F3189C7}" name="Term Name "/>
     <tableColumn id="4" xr3:uid="{DAAC4614-0F72-4E8E-BC14-F93F50235DB0}" name="Category "/>
@@ -3172,11 +3842,12 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{784C7AC4-9FB5-4B70-80B8-CEDD6F54E6AD}" name="Table1" displayName="Table1" ref="A1:B13" totalsRowShown="0">
-  <autoFilter ref="A1:B13" xr:uid="{784C7AC4-9FB5-4B70-80B8-CEDD6F54E6AD}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A6B81BD4-499C-446C-B47D-C4E5B034153F}" name="Website Name"/>
-    <tableColumn id="3" xr3:uid="{90F40EED-2070-4DA8-9D31-3E64E20D5963}" name="Link "/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E9F4E0EC-4852-4D2C-9BBE-852F6FF4678D}" name="Table1" displayName="Table1" ref="A1:C135" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="1" tableBorderDxfId="2">
+  <autoFilter ref="A1:C135" xr:uid="{E9F4E0EC-4852-4D2C-9BBE-852F6FF4678D}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{6D3E6D37-6386-4019-A6CA-7BDAEBD1BE76}" name="Title of Source "/>
+    <tableColumn id="2" xr3:uid="{86F8332B-8A32-497D-8E0C-91EF83BC9E63}" name="Website" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{5E9AB6AE-A04A-4E39-82CC-B13F8878BBCE}" name="Link to The Source " dataCellStyle="Hyperlink"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3499,7 +4170,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55440D71-C7D2-4E96-BABC-0BFC761058E3}">
-  <dimension ref="A1:F134"/>
+  <dimension ref="A1:F140"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="83.28515625" bestFit="1" customWidth="1"/>
@@ -6190,6 +6861,126 @@
       </c>
       <c r="F134" s="1" t="s">
         <v>311</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="A135" t="s">
+        <v>313</v>
+      </c>
+      <c r="B135" t="s">
+        <v>314</v>
+      </c>
+      <c r="C135" t="s">
+        <v>106</v>
+      </c>
+      <c r="D135" t="s">
+        <v>13</v>
+      </c>
+      <c r="E135" t="s">
+        <v>10</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
+      <c r="A136" t="s">
+        <v>315</v>
+      </c>
+      <c r="B136" t="s">
+        <v>316</v>
+      </c>
+      <c r="C136" t="s">
+        <v>106</v>
+      </c>
+      <c r="D136" t="s">
+        <v>13</v>
+      </c>
+      <c r="E136" t="s">
+        <v>10</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
+      <c r="A137" t="s">
+        <v>318</v>
+      </c>
+      <c r="B137" t="s">
+        <v>268</v>
+      </c>
+      <c r="C137" t="s">
+        <v>106</v>
+      </c>
+      <c r="D137" t="s">
+        <v>36</v>
+      </c>
+      <c r="E137" t="s">
+        <v>10</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="A138" t="s">
+        <v>320</v>
+      </c>
+      <c r="B138" t="s">
+        <v>321</v>
+      </c>
+      <c r="C138" t="s">
+        <v>106</v>
+      </c>
+      <c r="D138" t="s">
+        <v>13</v>
+      </c>
+      <c r="E138" t="s">
+        <v>10</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="A139" t="s">
+        <v>323</v>
+      </c>
+      <c r="B139" t="s">
+        <v>288</v>
+      </c>
+      <c r="C139" t="s">
+        <v>106</v>
+      </c>
+      <c r="D139" t="s">
+        <v>13</v>
+      </c>
+      <c r="E139" t="s">
+        <v>10</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="A140" t="s">
+        <v>325</v>
+      </c>
+      <c r="B140" t="s">
+        <v>326</v>
+      </c>
+      <c r="C140" t="s">
+        <v>106</v>
+      </c>
+      <c r="D140" t="s">
+        <v>13</v>
+      </c>
+      <c r="E140" t="s">
+        <v>10</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -6328,20 +7119,26 @@
     <hyperlink ref="F132" r:id="rId131" display="https://www.medesk.net/en/blog/denial-management/" xr:uid="{FA17B41C-8B24-4291-A101-5198BBC8E873}"/>
     <hyperlink ref="F133" r:id="rId132" display="https://www.pgmbilling.com/blog/what-is-a-claim-scrubber-and-why-it-matters-more-than-ever/" xr:uid="{1F547038-58B3-469A-B4B1-374DF14DF44A}"/>
     <hyperlink ref="F134" r:id="rId133" display="https://healthcarereaders.com/insights/supply-chain-management-in-healthcare" xr:uid="{AF85B86A-1A58-4C25-98F0-322102D0D4DA}"/>
+    <hyperlink ref="F135" r:id="rId134" display="https://nihcm.org/publications/the-growth-of-private-equity-in-us-health-care-impact-and-outlook" xr:uid="{EBAB0126-37AC-4579-B4A4-701BD6628B90}"/>
+    <hyperlink ref="F136" r:id="rId135" xr:uid="{DC7C964B-BC97-4FF1-A5AC-D17CCCAEC447}"/>
+    <hyperlink ref="F137" r:id="rId136" display="https://www.definitivehc.com/resources/healthcare-insights/breaking-down-us-hospital-payor-mixes" xr:uid="{FAFD8B8F-A33B-4B00-A534-A1FC8E461731}"/>
+    <hyperlink ref="F138" r:id="rId137" display="https://www.uhc.com/employer/news-strategies/annual-health-trends-report" xr:uid="{93A8F29A-7DB8-41BC-98E2-B73D44BB32C4}"/>
+    <hyperlink ref="F139" r:id="rId138" display="https://publichealth.jhu.edu/2025/whats-behind-rising-health-insurance-costs" xr:uid="{1B195895-6B11-43E1-AEBC-6F5B595DC9EF}"/>
+    <hyperlink ref="F140" r:id="rId139" display="https://www.healthmarkets.com/resources/health-insurance/affordable-care-act-pros-and-cons" xr:uid="{48A8169A-44A3-45DA-B7E5-67B03E94E781}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId134"/>
+    <tablePart r:id="rId140"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57CA2FE6-5472-4004-98CD-B2FEB2BFF00A}">
-  <dimension ref="A1:E201"/>
+  <dimension ref="A1:E209"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.140625" customWidth="1"/>
     <col min="3" max="3" width="65.85546875" customWidth="1"/>
     <col min="4" max="4" width="42.85546875" bestFit="1" customWidth="1"/>
@@ -6350,172 +7147,172 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="B1" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="C1" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="D1" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="E1" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="72.599999999999994">
       <c r="A2" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="B2" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="D2" t="s">
         <v>105</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="43.5">
       <c r="A3" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="B3" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="D3" t="s">
         <v>253</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="57.95">
       <c r="A4" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="B4" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="D4" t="s">
         <v>253</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="72.599999999999994">
       <c r="A5" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="B5" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="D5" t="s">
         <v>105</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="57.95">
       <c r="A6" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="B6" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="D6" t="s">
         <v>253</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="72.599999999999994">
       <c r="A7" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="B7" t="s">
         <v>54</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="D7" t="s">
         <v>253</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="43.5">
       <c r="A8" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="B8" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="D8" t="s">
         <v>253</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="57.95">
       <c r="A9" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="B9" t="s">
         <v>54</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="D9" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="72.599999999999994">
       <c r="A10" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="B10" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="D10" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="72.599999999999994">
@@ -6523,2208 +7320,2208 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="D11" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="72.599999999999994">
       <c r="A12" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="B12" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="D12" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="72.599999999999994">
       <c r="A13" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="B13" t="s">
         <v>45</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="D13" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="57.95">
       <c r="A14" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="B14" t="s">
         <v>45</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="D14" t="s">
         <v>187</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="72.599999999999994">
       <c r="A15" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B15" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="D15" t="s">
         <v>253</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="72.599999999999994">
       <c r="A16" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="B16" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="72.599999999999994">
       <c r="A17" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="B17" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="D17" t="s">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="72.599999999999994">
       <c r="A18" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="B18" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="D18" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="72.599999999999994">
       <c r="A19" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="B19" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="D19" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="72.599999999999994">
       <c r="A20" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="B20" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="D20" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="57.95">
       <c r="A21" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="B21" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="D21" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="72.599999999999994">
       <c r="A22" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="B22" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="D22" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="72.599999999999994">
       <c r="A23" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="B23" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="D23" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="87">
       <c r="A24" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="B24" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="D24" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="72.599999999999994">
       <c r="A25" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="B25" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="D25" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="72.599999999999994">
       <c r="A26" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="B26" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="D26" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="72.599999999999994">
       <c r="A27" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="B27" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="D27" t="s">
         <v>187</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="57.95">
       <c r="A28" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="B28" t="s">
         <v>134</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="D28" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="57.95">
       <c r="A29" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="B29" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="D29" t="s">
         <v>202</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="57.95">
       <c r="A30" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="B30" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="D30" t="s">
         <v>253</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="72.599999999999994">
       <c r="A31" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="B31" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="D31" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="57.95">
       <c r="A32" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="B32" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="D32" t="s">
         <v>142</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="72.599999999999994">
       <c r="A33" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="B33" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="D33" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>429</v>
+        <v>443</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="72.599999999999994">
       <c r="A34" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="B34" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="D34" t="s">
         <v>253</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>432</v>
+        <v>446</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="72.599999999999994">
       <c r="A35" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="B35" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="D35" t="s">
         <v>105</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="72.599999999999994">
       <c r="A36" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="B36" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="D36" t="s">
         <v>105</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="72.599999999999994">
       <c r="A37" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="B37" t="s">
         <v>45</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="D37" t="s">
         <v>187</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="101.45">
       <c r="A38" t="s">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="B38" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="72.599999999999994">
       <c r="A39" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="B39" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="D39" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="72.599999999999994">
       <c r="A40" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="B40" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="D40" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="87">
       <c r="A41" t="s">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="B41" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="D41" t="s">
         <v>139</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>453</v>
+        <v>467</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="57.95">
       <c r="A42" t="s">
-        <v>454</v>
+        <v>468</v>
       </c>
       <c r="B42" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="D42" t="s">
         <v>105</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="57.95">
       <c r="A43" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B43" t="s">
         <v>134</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c r="D43" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>460</v>
+        <v>474</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="72.599999999999994">
       <c r="A44" t="s">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="B44" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="D44" t="s">
         <v>105</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="72.599999999999994">
       <c r="A45" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="B45" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="D45" t="s">
         <v>105</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="72.599999999999994">
       <c r="A46" t="s">
-        <v>467</v>
+        <v>481</v>
       </c>
       <c r="B46" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="D46" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>469</v>
+        <v>483</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="72.599999999999994">
       <c r="A47" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="B47" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>471</v>
+        <v>485</v>
       </c>
       <c r="D47" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>472</v>
+        <v>486</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="57.95">
       <c r="A48" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="B48" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="D48" t="s">
         <v>253</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>475</v>
+        <v>489</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="72.599999999999994">
       <c r="A49" t="s">
-        <v>476</v>
+        <v>490</v>
       </c>
       <c r="B49" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>477</v>
+        <v>491</v>
       </c>
       <c r="D49" t="s">
-        <v>478</v>
+        <v>492</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>479</v>
+        <v>493</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="72.599999999999994">
       <c r="A50" t="s">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="B50" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>481</v>
+        <v>495</v>
       </c>
       <c r="D50" t="s">
         <v>253</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>482</v>
+        <v>496</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="72.599999999999994">
       <c r="A51" t="s">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="B51" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="D51" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>485</v>
+        <v>499</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="57.95">
       <c r="A52" t="s">
-        <v>486</v>
+        <v>500</v>
       </c>
       <c r="B52" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="D52" t="s">
         <v>105</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>488</v>
+        <v>502</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="72.599999999999994">
       <c r="A53" t="s">
-        <v>489</v>
+        <v>503</v>
       </c>
       <c r="B53" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>490</v>
+        <v>504</v>
       </c>
       <c r="D53" t="s">
         <v>253</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>491</v>
+        <v>505</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="72.599999999999994">
       <c r="A54" t="s">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="B54" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="D54" t="s">
-        <v>494</v>
+        <v>508</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>495</v>
+        <v>509</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="72.599999999999994">
       <c r="A55" t="s">
-        <v>496</v>
+        <v>510</v>
       </c>
       <c r="B55" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="D55" t="s">
         <v>105</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>498</v>
+        <v>512</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="57.95">
       <c r="A56" t="s">
-        <v>499</v>
+        <v>513</v>
       </c>
       <c r="B56" t="s">
         <v>54</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="D56" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>501</v>
+        <v>515</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="72.599999999999994">
       <c r="A57" t="s">
-        <v>476</v>
+        <v>490</v>
       </c>
       <c r="B57" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="D57" t="s">
-        <v>478</v>
+        <v>492</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>503</v>
+        <v>517</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="72.599999999999994">
       <c r="A58" t="s">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="B58" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="D58" t="s">
         <v>253</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="72.599999999999994">
       <c r="A59" t="s">
-        <v>507</v>
+        <v>521</v>
       </c>
       <c r="B59" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="D59" t="s">
         <v>187</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="57.95">
       <c r="A60" t="s">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="B60" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>511</v>
+        <v>525</v>
       </c>
       <c r="D60" t="s">
         <v>187</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>512</v>
+        <v>526</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="57.95">
       <c r="A61" t="s">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="B61" t="s">
         <v>45</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>514</v>
+        <v>528</v>
       </c>
       <c r="D61" t="s">
         <v>187</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>515</v>
+        <v>529</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="57.95">
       <c r="A62" t="s">
-        <v>516</v>
+        <v>530</v>
       </c>
       <c r="B62" t="s">
         <v>45</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="D62" t="s">
         <v>187</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="72.599999999999994">
       <c r="A63" t="s">
-        <v>519</v>
+        <v>533</v>
       </c>
       <c r="B63" t="s">
         <v>45</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>520</v>
+        <v>534</v>
       </c>
       <c r="D63" t="s">
         <v>187</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>521</v>
+        <v>535</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="57.95">
       <c r="A64" t="s">
-        <v>522</v>
+        <v>536</v>
       </c>
       <c r="B64" t="s">
         <v>45</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>523</v>
+        <v>537</v>
       </c>
       <c r="D64" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>524</v>
+        <v>538</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="57.95">
       <c r="A65" t="s">
-        <v>525</v>
+        <v>539</v>
       </c>
       <c r="B65" t="s">
         <v>45</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>526</v>
+        <v>540</v>
       </c>
       <c r="D65" t="s">
-        <v>527</v>
+        <v>541</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>528</v>
+        <v>542</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="72.599999999999994">
       <c r="A66" t="s">
-        <v>529</v>
+        <v>543</v>
       </c>
       <c r="B66" t="s">
         <v>45</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>530</v>
+        <v>544</v>
       </c>
       <c r="D66" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>531</v>
+        <v>545</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="87">
       <c r="A67" t="s">
-        <v>532</v>
+        <v>546</v>
       </c>
       <c r="B67" t="s">
         <v>45</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>533</v>
+        <v>547</v>
       </c>
       <c r="D67" t="s">
         <v>187</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>534</v>
+        <v>548</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="57.95">
       <c r="A68" t="s">
-        <v>535</v>
+        <v>549</v>
       </c>
       <c r="B68" t="s">
         <v>45</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>536</v>
+        <v>550</v>
       </c>
       <c r="D68" t="s">
-        <v>537</v>
+        <v>551</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>538</v>
+        <v>552</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="72.599999999999994">
       <c r="A69" t="s">
-        <v>539</v>
+        <v>553</v>
       </c>
       <c r="B69" t="s">
         <v>45</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>540</v>
+        <v>554</v>
       </c>
       <c r="D69" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>541</v>
+        <v>555</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="72.599999999999994">
       <c r="A70" t="s">
-        <v>542</v>
+        <v>556</v>
       </c>
       <c r="B70" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>543</v>
+        <v>557</v>
       </c>
       <c r="D70" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>544</v>
+        <v>558</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="72.599999999999994">
       <c r="A71" t="s">
-        <v>545</v>
+        <v>559</v>
       </c>
       <c r="B71" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="D71" t="s">
         <v>187</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>547</v>
+        <v>561</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="72.599999999999994">
       <c r="A72" t="s">
-        <v>548</v>
+        <v>562</v>
       </c>
       <c r="B72" t="s">
         <v>45</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="D72" t="s">
         <v>187</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>550</v>
+        <v>564</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="72.599999999999994">
       <c r="A73" t="s">
-        <v>551</v>
+        <v>565</v>
       </c>
       <c r="B73" t="s">
         <v>45</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>552</v>
+        <v>566</v>
       </c>
       <c r="D73" t="s">
         <v>187</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>553</v>
+        <v>567</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="72.599999999999994">
       <c r="A74" t="s">
-        <v>554</v>
+        <v>568</v>
       </c>
       <c r="B74" t="s">
         <v>45</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>553</v>
+        <v>567</v>
       </c>
       <c r="D74" t="s">
         <v>187</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>555</v>
+        <v>569</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="72.599999999999994">
       <c r="A75" t="s">
-        <v>556</v>
+        <v>570</v>
       </c>
       <c r="B75" t="s">
         <v>45</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>557</v>
+        <v>571</v>
       </c>
       <c r="D75" t="s">
         <v>187</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>558</v>
+        <v>572</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="72.599999999999994">
       <c r="A76" t="s">
-        <v>559</v>
+        <v>573</v>
       </c>
       <c r="B76" t="s">
         <v>45</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>560</v>
+        <v>574</v>
       </c>
       <c r="D76" t="s">
-        <v>561</v>
+        <v>575</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>562</v>
+        <v>576</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="72.599999999999994">
       <c r="A77" t="s">
-        <v>563</v>
+        <v>577</v>
       </c>
       <c r="B77" t="s">
         <v>45</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>564</v>
+        <v>578</v>
       </c>
       <c r="D77" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>565</v>
+        <v>579</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="72.599999999999994">
       <c r="A78" t="s">
-        <v>566</v>
+        <v>580</v>
       </c>
       <c r="B78" t="s">
         <v>45</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>567</v>
+        <v>581</v>
       </c>
       <c r="D78" t="s">
-        <v>561</v>
+        <v>575</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>568</v>
+        <v>582</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="57.95">
       <c r="A79" t="s">
-        <v>569</v>
+        <v>583</v>
       </c>
       <c r="B79" t="s">
         <v>45</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="D79" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>571</v>
+        <v>585</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="72.599999999999994">
       <c r="A80" t="s">
-        <v>572</v>
+        <v>586</v>
       </c>
       <c r="B80" t="s">
         <v>45</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>573</v>
+        <v>587</v>
       </c>
       <c r="D80" t="s">
         <v>187</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>574</v>
+        <v>588</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="72.599999999999994">
       <c r="A81" t="s">
-        <v>575</v>
+        <v>589</v>
       </c>
       <c r="B81" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>576</v>
+        <v>590</v>
       </c>
       <c r="D81" t="s">
         <v>187</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>577</v>
+        <v>591</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="72.599999999999994">
       <c r="A82" t="s">
-        <v>578</v>
+        <v>592</v>
       </c>
       <c r="B82" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>579</v>
+        <v>593</v>
       </c>
       <c r="D82" t="s">
-        <v>580</v>
+        <v>594</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>581</v>
+        <v>595</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="72.599999999999994">
       <c r="A83" t="s">
-        <v>582</v>
+        <v>596</v>
       </c>
       <c r="B83" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>583</v>
+        <v>597</v>
       </c>
       <c r="D83" t="s">
-        <v>584</v>
+        <v>598</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>585</v>
+        <v>599</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="72.599999999999994">
       <c r="A84" t="s">
-        <v>586</v>
+        <v>600</v>
       </c>
       <c r="B84" t="s">
         <v>45</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>587</v>
+        <v>601</v>
       </c>
       <c r="D84" t="s">
         <v>187</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>588</v>
+        <v>602</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="72.599999999999994">
       <c r="A85" t="s">
-        <v>589</v>
+        <v>603</v>
       </c>
       <c r="B85" t="s">
         <v>45</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>590</v>
+        <v>604</v>
       </c>
       <c r="D85" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>591</v>
+        <v>605</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="87">
       <c r="A86" t="s">
-        <v>592</v>
+        <v>606</v>
       </c>
       <c r="B86" t="s">
         <v>45</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>593</v>
+        <v>607</v>
       </c>
       <c r="D86" t="s">
-        <v>594</v>
+        <v>608</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>595</v>
+        <v>609</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="57.95">
       <c r="A87" t="s">
-        <v>596</v>
+        <v>610</v>
       </c>
       <c r="B87" t="s">
         <v>111</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>597</v>
+        <v>611</v>
       </c>
       <c r="D87" t="s">
         <v>202</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>598</v>
+        <v>612</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="87">
       <c r="A88" t="s">
-        <v>599</v>
+        <v>613</v>
       </c>
       <c r="B88" t="s">
         <v>111</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>600</v>
+        <v>614</v>
       </c>
       <c r="D88" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>601</v>
+        <v>615</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="72.599999999999994">
       <c r="A89" t="s">
-        <v>602</v>
+        <v>616</v>
       </c>
       <c r="B89" t="s">
         <v>111</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>603</v>
+        <v>617</v>
       </c>
       <c r="D89" t="s">
         <v>202</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>604</v>
+        <v>618</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="57.95">
       <c r="A90" t="s">
-        <v>605</v>
+        <v>619</v>
       </c>
       <c r="B90" t="s">
         <v>111</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>606</v>
+        <v>620</v>
       </c>
       <c r="D90" t="s">
         <v>202</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>607</v>
+        <v>621</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="72.599999999999994">
       <c r="A91" t="s">
-        <v>608</v>
+        <v>622</v>
       </c>
       <c r="B91" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>609</v>
+        <v>623</v>
       </c>
       <c r="D91" t="s">
-        <v>478</v>
+        <v>492</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>610</v>
+        <v>624</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="57.95">
       <c r="A92" t="s">
-        <v>611</v>
+        <v>625</v>
       </c>
       <c r="B92" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>612</v>
+        <v>626</v>
       </c>
       <c r="D92" t="s">
         <v>105</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>613</v>
+        <v>627</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="87">
       <c r="A93" t="s">
-        <v>614</v>
+        <v>628</v>
       </c>
       <c r="B93" t="s">
         <v>111</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>615</v>
+        <v>629</v>
       </c>
       <c r="D93" t="s">
         <v>202</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>616</v>
+        <v>630</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="72.599999999999994">
       <c r="A94" t="s">
-        <v>617</v>
+        <v>631</v>
       </c>
       <c r="B94" t="s">
         <v>134</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>618</v>
+        <v>632</v>
       </c>
       <c r="D94" t="s">
-        <v>594</v>
+        <v>608</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>619</v>
+        <v>633</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="87">
       <c r="A95" t="s">
-        <v>620</v>
+        <v>634</v>
       </c>
       <c r="B95" t="s">
         <v>111</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>621</v>
+        <v>635</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>622</v>
+        <v>636</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="87">
       <c r="A96" t="s">
-        <v>623</v>
+        <v>637</v>
       </c>
       <c r="B96" t="s">
         <v>111</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>624</v>
+        <v>638</v>
       </c>
       <c r="D96" t="s">
         <v>202</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>625</v>
+        <v>639</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="87">
       <c r="A97" t="s">
-        <v>626</v>
+        <v>640</v>
       </c>
       <c r="B97" t="s">
         <v>111</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>627</v>
+        <v>641</v>
       </c>
       <c r="D97" t="s">
         <v>202</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>628</v>
+        <v>642</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="87">
       <c r="A98" t="s">
-        <v>629</v>
+        <v>643</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>630</v>
+        <v>644</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>631</v>
+        <v>645</v>
       </c>
       <c r="D98" t="s">
-        <v>494</v>
+        <v>508</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>632</v>
+        <v>646</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="57.95">
       <c r="A99" t="s">
-        <v>633</v>
+        <v>647</v>
       </c>
       <c r="B99" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>634</v>
+        <v>648</v>
       </c>
       <c r="D99" t="s">
-        <v>635</v>
+        <v>649</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>636</v>
+        <v>650</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="72.599999999999994">
       <c r="A100" t="s">
-        <v>637</v>
+        <v>651</v>
       </c>
       <c r="B100" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>638</v>
+        <v>652</v>
       </c>
       <c r="D100" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>640</v>
+        <v>654</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="57.95">
       <c r="A101" t="s">
-        <v>641</v>
+        <v>655</v>
       </c>
       <c r="B101" t="s">
         <v>134</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>642</v>
+        <v>656</v>
       </c>
       <c r="D101" t="s">
-        <v>643</v>
+        <v>657</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>644</v>
+        <v>658</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="87">
       <c r="A102" t="s">
-        <v>645</v>
+        <v>659</v>
       </c>
       <c r="B102" t="s">
         <v>134</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>646</v>
+        <v>660</v>
       </c>
       <c r="D102" t="s">
-        <v>635</v>
+        <v>649</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>647</v>
+        <v>661</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="87">
       <c r="A103" t="s">
-        <v>648</v>
+        <v>662</v>
       </c>
       <c r="B103" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>649</v>
+        <v>663</v>
       </c>
       <c r="D103" t="s">
         <v>296</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>650</v>
+        <v>664</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="72.599999999999994">
       <c r="A104" t="s">
-        <v>651</v>
+        <v>665</v>
       </c>
       <c r="B104" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>652</v>
+        <v>666</v>
       </c>
       <c r="D104" t="s">
-        <v>653</v>
+        <v>667</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>654</v>
+        <v>668</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="57.95">
       <c r="A105" t="s">
-        <v>655</v>
+        <v>669</v>
       </c>
       <c r="B105" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>656</v>
+        <v>670</v>
       </c>
       <c r="D105" t="s">
         <v>105</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>657</v>
+        <v>671</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="72.599999999999994">
       <c r="A106" t="s">
-        <v>658</v>
+        <v>672</v>
       </c>
       <c r="B106" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>659</v>
+        <v>673</v>
       </c>
       <c r="D106" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>660</v>
+        <v>674</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="72.599999999999994">
       <c r="A107" t="s">
-        <v>661</v>
+        <v>675</v>
       </c>
       <c r="B107" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>662</v>
+        <v>676</v>
       </c>
       <c r="D107" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>663</v>
+        <v>677</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="72.599999999999994">
       <c r="A108" t="s">
-        <v>664</v>
+        <v>678</v>
       </c>
       <c r="B108" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>665</v>
+        <v>679</v>
       </c>
       <c r="D108" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>666</v>
+        <v>680</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="57.95">
       <c r="A109" t="s">
-        <v>667</v>
+        <v>681</v>
       </c>
       <c r="B109" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>668</v>
+        <v>682</v>
       </c>
       <c r="D109" t="s">
         <v>253</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>669</v>
+        <v>683</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="72.599999999999994">
       <c r="A110" t="s">
-        <v>670</v>
+        <v>684</v>
       </c>
       <c r="B110" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>671</v>
+        <v>685</v>
       </c>
       <c r="D110" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>672</v>
+        <v>686</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="72.599999999999994">
       <c r="A111" t="s">
-        <v>673</v>
+        <v>687</v>
       </c>
       <c r="B111" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>674</v>
+        <v>688</v>
       </c>
       <c r="D111" t="s">
         <v>139</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>675</v>
+        <v>689</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="57.95">
       <c r="A112" t="s">
-        <v>676</v>
+        <v>690</v>
       </c>
       <c r="B112" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>677</v>
+        <v>691</v>
       </c>
       <c r="D112" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>678</v>
+        <v>692</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="57.95">
       <c r="A113" t="s">
-        <v>679</v>
+        <v>693</v>
       </c>
       <c r="B113" t="s">
         <v>45</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>680</v>
+        <v>694</v>
       </c>
       <c r="D113" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>681</v>
+        <v>695</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="72.599999999999994">
       <c r="A114" t="s">
-        <v>682</v>
+        <v>696</v>
       </c>
       <c r="B114" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>683</v>
+        <v>697</v>
       </c>
       <c r="D114" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>684</v>
+        <v>698</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="72.599999999999994">
       <c r="A115" t="s">
-        <v>685</v>
+        <v>699</v>
       </c>
       <c r="B115" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>686</v>
+        <v>700</v>
       </c>
       <c r="D115" t="s">
-        <v>687</v>
+        <v>701</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>688</v>
+        <v>702</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="87">
       <c r="A116" t="s">
-        <v>689</v>
+        <v>703</v>
       </c>
       <c r="B116" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>690</v>
+        <v>704</v>
       </c>
       <c r="D116" t="s">
-        <v>687</v>
+        <v>701</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>691</v>
+        <v>705</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="72.599999999999994">
       <c r="A117" t="s">
-        <v>692</v>
+        <v>706</v>
       </c>
       <c r="B117" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>693</v>
+        <v>707</v>
       </c>
       <c r="D117" t="s">
-        <v>687</v>
+        <v>701</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>694</v>
+        <v>708</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="87">
       <c r="A118" t="s">
-        <v>695</v>
+        <v>709</v>
       </c>
       <c r="B118" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>696</v>
+        <v>710</v>
       </c>
       <c r="D118" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>697</v>
+        <v>711</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="57.95">
       <c r="A119" t="s">
-        <v>698</v>
+        <v>712</v>
       </c>
       <c r="B119" t="s">
         <v>45</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>699</v>
+        <v>713</v>
       </c>
       <c r="D119" t="s">
         <v>187</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>700</v>
+        <v>714</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="72.599999999999994">
       <c r="A120" t="s">
+        <v>715</v>
+      </c>
+      <c r="B120" t="s">
+        <v>393</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D120" t="s">
         <v>701</v>
       </c>
-      <c r="B120" t="s">
-        <v>379</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>702</v>
-      </c>
-      <c r="D120" t="s">
-        <v>687</v>
-      </c>
       <c r="E120" s="4" t="s">
-        <v>703</v>
+        <v>717</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="72.599999999999994">
       <c r="A121" t="s">
-        <v>704</v>
+        <v>718</v>
       </c>
       <c r="B121" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>705</v>
+        <v>719</v>
       </c>
       <c r="D121" t="s">
-        <v>687</v>
+        <v>701</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>706</v>
+        <v>720</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="72.599999999999994">
       <c r="A122" t="s">
-        <v>707</v>
+        <v>721</v>
       </c>
       <c r="B122" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="D122" t="s">
-        <v>687</v>
+        <v>701</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>709</v>
+        <v>723</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="72.599999999999994">
       <c r="A123" t="s">
-        <v>710</v>
+        <v>724</v>
       </c>
       <c r="B123" t="s">
         <v>134</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>711</v>
+        <v>725</v>
       </c>
       <c r="D123" t="s">
-        <v>712</v>
+        <v>726</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>713</v>
+        <v>727</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="72.599999999999994">
       <c r="A124" t="s">
-        <v>714</v>
+        <v>728</v>
       </c>
       <c r="B124" t="s">
         <v>134</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>715</v>
+        <v>729</v>
       </c>
       <c r="D124" t="s">
-        <v>716</v>
+        <v>730</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>717</v>
+        <v>731</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="72.599999999999994">
       <c r="A125" t="s">
-        <v>718</v>
+        <v>732</v>
       </c>
       <c r="B125" t="s">
         <v>134</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>719</v>
+        <v>733</v>
       </c>
       <c r="D125" t="s">
-        <v>720</v>
+        <v>734</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>721</v>
+        <v>735</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="72.599999999999994">
       <c r="A126" t="s">
-        <v>722</v>
+        <v>736</v>
       </c>
       <c r="B126" t="s">
         <v>134</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>723</v>
+        <v>737</v>
       </c>
       <c r="D126" t="s">
-        <v>724</v>
+        <v>738</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>725</v>
+        <v>739</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="72.599999999999994">
       <c r="A127" t="s">
-        <v>726</v>
+        <v>740</v>
       </c>
       <c r="B127" t="s">
         <v>134</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>727</v>
+        <v>741</v>
       </c>
       <c r="D127" t="s">
-        <v>724</v>
+        <v>738</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>728</v>
+        <v>742</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="72.599999999999994">
       <c r="A128" t="s">
-        <v>729</v>
+        <v>743</v>
       </c>
       <c r="B128" t="s">
         <v>134</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>730</v>
+        <v>744</v>
       </c>
       <c r="D128" t="s">
-        <v>724</v>
+        <v>738</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>731</v>
+        <v>745</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="72.599999999999994">
       <c r="A129" t="s">
-        <v>732</v>
+        <v>746</v>
       </c>
       <c r="B129" t="s">
         <v>134</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>733</v>
+        <v>747</v>
       </c>
       <c r="D129" t="s">
-        <v>724</v>
+        <v>738</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>734</v>
+        <v>748</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="72.599999999999994">
       <c r="A130" t="s">
-        <v>735</v>
+        <v>749</v>
       </c>
       <c r="B130" t="s">
         <v>134</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>736</v>
+        <v>750</v>
       </c>
       <c r="D130" t="s">
-        <v>724</v>
+        <v>738</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>737</v>
+        <v>751</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="72.599999999999994">
       <c r="A131" t="s">
-        <v>738</v>
+        <v>752</v>
       </c>
       <c r="B131" t="s">
         <v>134</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>739</v>
+        <v>753</v>
       </c>
       <c r="D131" t="s">
-        <v>724</v>
+        <v>738</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>740</v>
+        <v>754</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="72.599999999999994">
       <c r="A132" t="s">
-        <v>741</v>
+        <v>755</v>
       </c>
       <c r="B132" t="s">
         <v>134</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>742</v>
+        <v>756</v>
       </c>
       <c r="D132" t="s">
-        <v>743</v>
+        <v>757</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>744</v>
+        <v>758</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="72.599999999999994">
       <c r="A133" t="s">
-        <v>745</v>
+        <v>759</v>
       </c>
       <c r="B133" t="s">
         <v>134</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>746</v>
+        <v>760</v>
       </c>
       <c r="D133" t="s">
-        <v>743</v>
+        <v>757</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>747</v>
+        <v>761</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="72.599999999999994">
       <c r="A134" t="s">
-        <v>748</v>
+        <v>762</v>
       </c>
       <c r="B134" t="s">
         <v>54</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>749</v>
+        <v>763</v>
       </c>
       <c r="D134" t="s">
         <v>253</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>750</v>
+        <v>764</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="72.599999999999994">
       <c r="A135" t="s">
-        <v>751</v>
+        <v>765</v>
       </c>
       <c r="B135" t="s">
-        <v>752</v>
+        <v>766</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>753</v>
+        <v>767</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>754</v>
+        <v>768</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="72.599999999999994">
       <c r="A136" t="s">
-        <v>755</v>
+        <v>769</v>
       </c>
       <c r="B136" t="s">
-        <v>752</v>
+        <v>766</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>756</v>
+        <v>770</v>
       </c>
       <c r="D136" t="s">
         <v>253</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>757</v>
+        <v>771</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="72.599999999999994">
       <c r="A137" t="s">
-        <v>758</v>
+        <v>772</v>
       </c>
       <c r="B137" t="s">
-        <v>752</v>
+        <v>766</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>759</v>
+        <v>773</v>
       </c>
       <c r="D137" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>760</v>
+        <v>774</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="72.599999999999994">
       <c r="A138" t="s">
-        <v>761</v>
+        <v>775</v>
       </c>
       <c r="B138" t="s">
-        <v>752</v>
+        <v>766</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>762</v>
+        <v>776</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>763</v>
+        <v>777</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="57.95">
       <c r="A139" t="s">
-        <v>764</v>
+        <v>778</v>
       </c>
       <c r="B139" t="s">
         <v>54</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>765</v>
+        <v>779</v>
       </c>
       <c r="D139" t="s">
-        <v>766</v>
+        <v>780</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>767</v>
+        <v>781</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="72.599999999999994">
       <c r="A140" t="s">
-        <v>768</v>
+        <v>782</v>
       </c>
       <c r="B140" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>769</v>
+        <v>783</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>770</v>
+        <v>784</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="57.95">
       <c r="A141" t="s">
-        <v>771</v>
+        <v>785</v>
       </c>
       <c r="B141" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>772</v>
+        <v>786</v>
       </c>
       <c r="D141" t="s">
         <v>253</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>773</v>
+        <v>787</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="87">
@@ -8735,1016 +9532,1152 @@
         <v>111</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
       <c r="D142" t="s">
-        <v>775</v>
+        <v>789</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>776</v>
+        <v>790</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="72.599999999999994">
       <c r="A143" t="s">
-        <v>777</v>
+        <v>791</v>
       </c>
       <c r="B143" t="s">
-        <v>630</v>
+        <v>644</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>778</v>
+        <v>792</v>
       </c>
       <c r="D143" t="s">
         <v>202</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>779</v>
+        <v>793</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="87">
       <c r="A144" t="s">
-        <v>780</v>
+        <v>794</v>
       </c>
       <c r="B144" t="s">
         <v>111</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>781</v>
+        <v>795</v>
       </c>
       <c r="D144" t="s">
-        <v>782</v>
+        <v>796</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>783</v>
+        <v>797</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="57.95">
       <c r="A145" t="s">
-        <v>784</v>
+        <v>798</v>
       </c>
       <c r="B145" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>785</v>
+        <v>799</v>
       </c>
       <c r="D145" t="s">
-        <v>786</v>
+        <v>800</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>787</v>
+        <v>801</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="72.599999999999994">
       <c r="A146" t="s">
-        <v>788</v>
+        <v>802</v>
       </c>
       <c r="B146" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>789</v>
+        <v>803</v>
       </c>
       <c r="D146" t="s">
-        <v>790</v>
+        <v>804</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>791</v>
+        <v>805</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="57.95">
       <c r="A147" t="s">
-        <v>792</v>
+        <v>806</v>
       </c>
       <c r="B147" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>793</v>
+        <v>807</v>
       </c>
       <c r="D147" t="s">
-        <v>794</v>
+        <v>808</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>795</v>
+        <v>809</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="72.599999999999994">
       <c r="A148" t="s">
-        <v>796</v>
+        <v>810</v>
       </c>
       <c r="B148" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>797</v>
+        <v>811</v>
       </c>
       <c r="D148" t="s">
-        <v>798</v>
+        <v>812</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>799</v>
+        <v>813</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="72.599999999999994">
       <c r="A149" t="s">
-        <v>800</v>
+        <v>814</v>
       </c>
       <c r="B149" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>801</v>
+        <v>815</v>
       </c>
       <c r="D149" t="s">
-        <v>802</v>
+        <v>816</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>803</v>
+        <v>817</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="72.599999999999994">
       <c r="A150" t="s">
-        <v>804</v>
+        <v>818</v>
       </c>
       <c r="B150" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>805</v>
+        <v>819</v>
       </c>
       <c r="D150" t="s">
-        <v>802</v>
+        <v>816</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>806</v>
+        <v>820</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="57.95">
       <c r="A151" t="s">
-        <v>807</v>
+        <v>821</v>
       </c>
       <c r="B151" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>808</v>
+        <v>822</v>
       </c>
       <c r="D151" t="s">
-        <v>802</v>
+        <v>816</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>809</v>
+        <v>823</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="57.95">
       <c r="A152" t="s">
-        <v>810</v>
+        <v>824</v>
       </c>
       <c r="B152" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>811</v>
+        <v>825</v>
       </c>
       <c r="D152" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>812</v>
+        <v>826</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="57.95">
       <c r="A153" t="s">
-        <v>813</v>
+        <v>827</v>
       </c>
       <c r="B153" t="s">
         <v>45</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>814</v>
+        <v>828</v>
       </c>
       <c r="D153" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>815</v>
+        <v>829</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="57.95">
       <c r="A154" t="s">
-        <v>816</v>
+        <v>830</v>
       </c>
       <c r="B154" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>817</v>
+        <v>831</v>
       </c>
       <c r="D154" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>818</v>
+        <v>832</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="72.599999999999994">
       <c r="A155" t="s">
-        <v>819</v>
+        <v>833</v>
       </c>
       <c r="B155" t="s">
         <v>45</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>820</v>
+        <v>834</v>
       </c>
       <c r="D155" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>821</v>
+        <v>835</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="43.5">
       <c r="A156" t="s">
-        <v>822</v>
+        <v>836</v>
       </c>
       <c r="B156" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>823</v>
+        <v>837</v>
       </c>
       <c r="D156" t="s">
-        <v>824</v>
+        <v>838</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>825</v>
+        <v>839</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="57.95">
       <c r="A157" t="s">
-        <v>826</v>
+        <v>840</v>
       </c>
       <c r="B157" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>827</v>
+        <v>841</v>
       </c>
       <c r="D157" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>828</v>
+        <v>842</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="57.95">
       <c r="A158" t="s">
-        <v>829</v>
+        <v>843</v>
       </c>
       <c r="B158" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>830</v>
+        <v>844</v>
       </c>
       <c r="D158" t="s">
-        <v>831</v>
+        <v>845</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>832</v>
+        <v>846</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="57.95">
       <c r="A159" t="s">
-        <v>833</v>
+        <v>847</v>
       </c>
       <c r="B159" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>834</v>
+        <v>848</v>
       </c>
       <c r="D159" t="s">
-        <v>831</v>
+        <v>845</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>835</v>
+        <v>849</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="87">
       <c r="A160" t="s">
-        <v>836</v>
+        <v>850</v>
       </c>
       <c r="B160" t="s">
         <v>111</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>837</v>
+        <v>851</v>
       </c>
       <c r="D160" t="s">
-        <v>838</v>
+        <v>852</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>839</v>
+        <v>853</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="57.95">
       <c r="A161" t="s">
-        <v>840</v>
+        <v>854</v>
       </c>
       <c r="B161" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>841</v>
+        <v>855</v>
       </c>
       <c r="D161" t="s">
-        <v>842</v>
+        <v>856</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>843</v>
+        <v>857</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="72.599999999999994">
       <c r="A162" t="s">
-        <v>844</v>
+        <v>858</v>
       </c>
       <c r="B162" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>845</v>
+        <v>859</v>
       </c>
       <c r="D162" t="s">
-        <v>802</v>
+        <v>816</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>846</v>
+        <v>860</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="72.599999999999994">
       <c r="A163" t="s">
-        <v>847</v>
+        <v>861</v>
       </c>
       <c r="B163" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>848</v>
+        <v>862</v>
       </c>
       <c r="D163" t="s">
-        <v>802</v>
+        <v>816</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>849</v>
+        <v>863</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="72.599999999999994">
       <c r="A164" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="B164" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>851</v>
+        <v>865</v>
       </c>
       <c r="D164" t="s">
-        <v>852</v>
+        <v>866</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>853</v>
+        <v>867</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="72.599999999999994">
       <c r="A165" t="s">
-        <v>854</v>
+        <v>868</v>
       </c>
       <c r="B165" t="s">
         <v>45</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>855</v>
+        <v>869</v>
       </c>
       <c r="D165" t="s">
-        <v>856</v>
+        <v>870</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>857</v>
+        <v>871</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="72.599999999999994">
       <c r="A166" t="s">
-        <v>858</v>
+        <v>872</v>
       </c>
       <c r="B166" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>859</v>
+        <v>873</v>
       </c>
       <c r="D166" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>860</v>
+        <v>874</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="72.599999999999994">
       <c r="A167" t="s">
-        <v>861</v>
+        <v>875</v>
       </c>
       <c r="B167" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>862</v>
+        <v>876</v>
       </c>
       <c r="D167" t="s">
-        <v>687</v>
+        <v>701</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>863</v>
+        <v>877</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="72.599999999999994">
       <c r="A168" t="s">
-        <v>864</v>
+        <v>878</v>
       </c>
       <c r="B168" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>865</v>
+        <v>879</v>
       </c>
       <c r="D168" t="s">
-        <v>687</v>
+        <v>701</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>866</v>
+        <v>880</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="57.95">
       <c r="A169" t="s">
-        <v>867</v>
+        <v>881</v>
       </c>
       <c r="B169" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>868</v>
+        <v>882</v>
       </c>
       <c r="D169" t="s">
-        <v>687</v>
+        <v>701</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>869</v>
+        <v>883</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="87">
       <c r="A170" t="s">
-        <v>870</v>
+        <v>884</v>
       </c>
       <c r="B170" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>871</v>
+        <v>885</v>
       </c>
       <c r="D170" t="s">
-        <v>687</v>
+        <v>701</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>872</v>
+        <v>886</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="72.599999999999994">
       <c r="A171" t="s">
-        <v>873</v>
+        <v>887</v>
       </c>
       <c r="B171" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>874</v>
+        <v>888</v>
       </c>
       <c r="D171" t="s">
-        <v>580</v>
+        <v>594</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>875</v>
+        <v>889</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="72.599999999999994">
       <c r="A172" t="s">
-        <v>876</v>
+        <v>890</v>
       </c>
       <c r="B172" t="s">
         <v>134</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>877</v>
+        <v>891</v>
       </c>
       <c r="D172" t="s">
         <v>105</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>878</v>
+        <v>892</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="57.95">
       <c r="A173" t="s">
-        <v>879</v>
+        <v>893</v>
       </c>
       <c r="B173" t="s">
         <v>134</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>880</v>
+        <v>894</v>
       </c>
       <c r="D173" t="s">
         <v>105</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>881</v>
+        <v>895</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="72.599999999999994">
       <c r="A174" t="s">
-        <v>882</v>
+        <v>896</v>
       </c>
       <c r="B174" t="s">
         <v>134</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>883</v>
+        <v>897</v>
       </c>
       <c r="D174" t="s">
-        <v>884</v>
+        <v>898</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>885</v>
+        <v>899</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="57.95">
       <c r="A175" t="s">
-        <v>886</v>
+        <v>900</v>
       </c>
       <c r="B175" t="s">
-        <v>752</v>
+        <v>766</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>887</v>
+        <v>901</v>
       </c>
       <c r="D175" t="s">
-        <v>888</v>
+        <v>902</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>889</v>
+        <v>903</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="72.599999999999994">
       <c r="A176" t="s">
-        <v>890</v>
+        <v>904</v>
       </c>
       <c r="B176" t="s">
-        <v>752</v>
+        <v>766</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>891</v>
+        <v>905</v>
       </c>
       <c r="D176" t="s">
-        <v>892</v>
+        <v>906</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>893</v>
+        <v>907</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="57.95">
       <c r="A177" t="s">
-        <v>894</v>
+        <v>908</v>
       </c>
       <c r="B177" t="s">
-        <v>752</v>
+        <v>766</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>895</v>
+        <v>909</v>
       </c>
       <c r="D177" t="s">
-        <v>802</v>
+        <v>816</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>896</v>
+        <v>910</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="72.599999999999994">
       <c r="A178" t="s">
-        <v>897</v>
+        <v>911</v>
       </c>
       <c r="B178" t="s">
         <v>54</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>898</v>
+        <v>912</v>
       </c>
       <c r="D178" t="s">
-        <v>899</v>
+        <v>913</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>900</v>
+        <v>914</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="72.599999999999994">
       <c r="A179" t="s">
-        <v>901</v>
+        <v>915</v>
       </c>
       <c r="B179" t="s">
         <v>54</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>902</v>
+        <v>916</v>
       </c>
       <c r="D179" t="s">
-        <v>794</v>
+        <v>808</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>903</v>
+        <v>917</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="72.599999999999994">
       <c r="A180" t="s">
-        <v>904</v>
+        <v>918</v>
       </c>
       <c r="B180" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>905</v>
+        <v>919</v>
       </c>
       <c r="D180" t="s">
-        <v>906</v>
+        <v>920</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>907</v>
+        <v>921</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="72.599999999999994">
       <c r="A181" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="B181" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>909</v>
+        <v>923</v>
       </c>
       <c r="D181" t="s">
-        <v>906</v>
+        <v>920</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>910</v>
+        <v>924</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="57.95">
       <c r="A182" t="s">
-        <v>911</v>
+        <v>925</v>
       </c>
       <c r="B182" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>912</v>
+        <v>926</v>
       </c>
       <c r="D182" t="s">
-        <v>892</v>
+        <v>906</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>913</v>
+        <v>927</v>
       </c>
     </row>
     <row r="183" spans="1:5" ht="57.95">
       <c r="A183" t="s">
-        <v>914</v>
+        <v>928</v>
       </c>
       <c r="B183" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>915</v>
+        <v>929</v>
       </c>
       <c r="D183" t="s">
-        <v>916</v>
+        <v>930</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>917</v>
+        <v>931</v>
       </c>
     </row>
     <row r="184" spans="1:5" ht="72.599999999999994">
       <c r="A184" t="s">
-        <v>918</v>
+        <v>932</v>
       </c>
       <c r="B184" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>919</v>
+        <v>933</v>
       </c>
       <c r="D184" t="s">
-        <v>916</v>
+        <v>930</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>920</v>
+        <v>934</v>
       </c>
     </row>
     <row r="185" spans="1:5" ht="57.95">
       <c r="A185" t="s">
-        <v>921</v>
+        <v>935</v>
       </c>
       <c r="B185" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>922</v>
+        <v>936</v>
       </c>
       <c r="D185" t="s">
-        <v>884</v>
+        <v>898</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>923</v>
+        <v>937</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="57.95">
       <c r="A186" t="s">
-        <v>924</v>
+        <v>938</v>
       </c>
       <c r="B186" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>925</v>
+        <v>939</v>
       </c>
       <c r="D186" t="s">
-        <v>884</v>
+        <v>898</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>926</v>
+        <v>940</v>
       </c>
     </row>
     <row r="187" spans="1:5" ht="57.95">
       <c r="A187" t="s">
-        <v>927</v>
+        <v>941</v>
       </c>
       <c r="B187" t="s">
         <v>45</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>928</v>
+        <v>942</v>
       </c>
       <c r="D187" t="s">
-        <v>929</v>
+        <v>943</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>930</v>
+        <v>944</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="57.95">
       <c r="A188" t="s">
-        <v>931</v>
+        <v>945</v>
       </c>
       <c r="B188" t="s">
         <v>111</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>932</v>
+        <v>946</v>
       </c>
       <c r="D188" t="s">
-        <v>933</v>
+        <v>947</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>934</v>
+        <v>948</v>
       </c>
     </row>
     <row r="189" spans="1:5" ht="57.95">
       <c r="A189" t="s">
-        <v>935</v>
+        <v>949</v>
       </c>
       <c r="B189" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>936</v>
+        <v>950</v>
       </c>
       <c r="D189" t="s">
-        <v>786</v>
+        <v>800</v>
       </c>
       <c r="E189" s="4" t="s">
-        <v>937</v>
+        <v>951</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="72.599999999999994">
       <c r="A190" t="s">
-        <v>938</v>
+        <v>952</v>
       </c>
       <c r="B190" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>939</v>
+        <v>953</v>
       </c>
       <c r="D190" t="s">
-        <v>786</v>
+        <v>800</v>
       </c>
       <c r="E190" s="4" t="s">
-        <v>940</v>
+        <v>954</v>
       </c>
     </row>
     <row r="191" spans="1:5" ht="57.95">
       <c r="A191" t="s">
-        <v>941</v>
+        <v>955</v>
       </c>
       <c r="B191" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>942</v>
+        <v>956</v>
       </c>
       <c r="D191" t="s">
-        <v>943</v>
+        <v>957</v>
       </c>
       <c r="E191" s="4" t="s">
-        <v>944</v>
+        <v>958</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="72.599999999999994">
       <c r="A192" t="s">
-        <v>945</v>
+        <v>959</v>
       </c>
       <c r="B192" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>946</v>
+        <v>960</v>
       </c>
       <c r="D192" t="s">
-        <v>947</v>
+        <v>961</v>
       </c>
       <c r="E192" s="4" t="s">
-        <v>948</v>
+        <v>962</v>
       </c>
     </row>
     <row r="193" spans="1:5" ht="87">
       <c r="A193" t="s">
-        <v>949</v>
+        <v>963</v>
       </c>
       <c r="B193" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>950</v>
+        <v>964</v>
       </c>
       <c r="D193" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="E193" s="4" t="s">
-        <v>951</v>
+        <v>965</v>
       </c>
     </row>
     <row r="194" spans="1:5" ht="72.599999999999994">
       <c r="A194" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="B194" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>952</v>
+        <v>966</v>
       </c>
       <c r="D194" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="E194" s="4" t="s">
-        <v>953</v>
+        <v>967</v>
       </c>
     </row>
     <row r="195" spans="1:5" ht="72.599999999999994">
       <c r="A195" t="s">
-        <v>954</v>
+        <v>968</v>
       </c>
       <c r="B195" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>955</v>
+        <v>969</v>
       </c>
       <c r="D195" t="s">
-        <v>956</v>
+        <v>970</v>
       </c>
       <c r="E195" s="4" t="s">
-        <v>957</v>
+        <v>971</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="57.95">
       <c r="A196" t="s">
-        <v>958</v>
+        <v>972</v>
       </c>
       <c r="B196" t="s">
         <v>54</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>959</v>
+        <v>973</v>
       </c>
       <c r="D196" t="s">
-        <v>960</v>
+        <v>974</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>961</v>
+        <v>975</v>
       </c>
     </row>
     <row r="197" spans="1:5" ht="43.5">
       <c r="A197" t="s">
-        <v>962</v>
+        <v>976</v>
       </c>
       <c r="B197" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>963</v>
+        <v>977</v>
       </c>
       <c r="D197" t="s">
         <v>105</v>
       </c>
       <c r="E197" s="4" t="s">
-        <v>964</v>
+        <v>978</v>
       </c>
     </row>
     <row r="198" spans="1:5" ht="29.1">
       <c r="A198" t="s">
-        <v>965</v>
+        <v>979</v>
       </c>
       <c r="B198" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>966</v>
+        <v>980</v>
       </c>
       <c r="D198" t="s">
-        <v>916</v>
+        <v>930</v>
       </c>
       <c r="E198" s="4" t="s">
-        <v>967</v>
+        <v>981</v>
       </c>
     </row>
     <row r="199" spans="1:5" ht="29.1">
       <c r="A199" t="s">
-        <v>968</v>
+        <v>982</v>
       </c>
       <c r="B199" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>969</v>
+        <v>983</v>
       </c>
       <c r="D199" t="s">
-        <v>916</v>
-      </c>
-      <c r="E199" t="s">
-        <v>970</v>
+        <v>930</v>
+      </c>
+      <c r="E199" s="4" t="s">
+        <v>984</v>
       </c>
     </row>
     <row r="200" spans="1:5" ht="57.95">
       <c r="A200" t="s">
-        <v>971</v>
+        <v>985</v>
       </c>
       <c r="B200" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>972</v>
+        <v>986</v>
       </c>
       <c r="D200" t="s">
-        <v>842</v>
+        <v>856</v>
       </c>
       <c r="E200" s="4" t="s">
-        <v>973</v>
+        <v>987</v>
       </c>
     </row>
     <row r="201" spans="1:5" ht="72.599999999999994">
       <c r="A201" t="s">
-        <v>974</v>
+        <v>988</v>
       </c>
       <c r="B201" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>975</v>
+        <v>989</v>
       </c>
       <c r="D201" t="s">
-        <v>976</v>
+        <v>990</v>
       </c>
       <c r="E201" s="4" t="s">
-        <v>977</v>
+        <v>991</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" ht="72.599999999999994">
+      <c r="A202" t="s">
+        <v>992</v>
+      </c>
+      <c r="B202" t="s">
+        <v>333</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>993</v>
+      </c>
+      <c r="D202" t="s">
+        <v>800</v>
+      </c>
+      <c r="E202" s="4" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" ht="43.5">
+      <c r="A203" t="s">
+        <v>995</v>
+      </c>
+      <c r="B203" t="s">
+        <v>333</v>
+      </c>
+      <c r="C203" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="D203" t="s">
+        <v>856</v>
+      </c>
+      <c r="E203" s="4" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" ht="72.599999999999994">
+      <c r="A204" t="s">
+        <v>998</v>
+      </c>
+      <c r="B204" t="s">
+        <v>333</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>999</v>
+      </c>
+      <c r="D204" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E204" s="4" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" ht="57.95">
+      <c r="A205" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B205" t="s">
+        <v>333</v>
+      </c>
+      <c r="C205" s="4" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D205" t="s">
+        <v>105</v>
+      </c>
+      <c r="E205" s="4" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" ht="57.95">
+      <c r="A206" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B206" t="s">
+        <v>333</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D206" t="s">
+        <v>105</v>
+      </c>
+      <c r="E206" s="4" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" ht="72.599999999999994">
+      <c r="A207" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B207" t="s">
+        <v>333</v>
+      </c>
+      <c r="C207" s="4" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D207" t="s">
+        <v>105</v>
+      </c>
+      <c r="E207" s="4" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" ht="72.599999999999994">
+      <c r="A208" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B208" t="s">
+        <v>766</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D208" t="s">
+        <v>253</v>
+      </c>
+      <c r="E208" s="4" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" ht="72.599999999999994">
+      <c r="A209" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B209" t="s">
+        <v>359</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D209" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E209" s="4" t="s">
+        <v>1017</v>
       </c>
     </row>
   </sheetData>
@@ -9757,135 +10690,1640 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8D0B573-CB40-455A-8450-09C524808966}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:C135"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="91.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="77.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="155.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>978</v>
-      </c>
-      <c r="B1" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>980</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>981</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>983</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>985</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>712</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>988</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>990</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>274</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>993</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>995</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>997</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>187</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>999</v>
+    <row r="1" spans="1:3">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="12" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="14" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B66" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B67" t="s">
+        <v>105</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B68" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B69" t="s">
+        <v>105</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B70" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B71" t="s">
+        <v>105</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B73" t="s">
+        <v>202</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B74" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B75" t="s">
+        <v>202</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B76" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B77" t="s">
+        <v>202</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B78" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B79" t="s">
+        <v>296</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B80" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B81" t="s">
+        <v>296</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B82" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B83" t="s">
+        <v>296</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B84" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B85" t="s">
+        <v>296</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B86" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B87" t="s">
+        <v>296</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B88" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B89" t="s">
+        <v>296</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B90" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B92" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B93" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B94" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B95" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B96" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B97" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B98" t="s">
+        <v>242</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B99" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B100" s="13" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B101" s="13" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B102" s="13" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B103" s="13" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B104" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B105" s="13" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B106" s="13" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B107" s="13" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B108" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B109" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B110" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B111" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B112" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B113" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B114" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B115" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B116" s="13" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B117" s="13" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B118" s="13" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B119" s="13" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B120" s="13" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B121" s="13" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B122" s="13" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B123" s="13" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B124" s="13" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B125" s="13" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B126" s="13" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B127" s="13" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B128" s="13" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B129" s="13" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B130" s="13" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B131" s="13" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B132" s="13" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B133" s="13" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B134" s="13" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B135" s="13" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>1165</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="https://www.hfma.org/" xr:uid="{FAD2F71A-A537-4FD5-AF5D-6954B237B293}"/>
-    <hyperlink ref="B3" r:id="rId2" display="https://www.beckershospitalreview.com/" xr:uid="{E89BC5BF-5431-4F5E-B1D1-020EBB6C7EC8}"/>
-    <hyperlink ref="B4" r:id="rId3" display="https://www.beckershospitalreview.com/supply-chain/" xr:uid="{5EE1FFDF-8EB0-402C-A431-BC8F4F61E6AB}"/>
-    <hyperlink ref="B5" r:id="rId4" display="https://www.beckershospitalreview.com/print-issue-category/beckers-clinical-leadership/" xr:uid="{0A81105F-B936-4C23-9BD1-1EFC5EA696A6}"/>
-    <hyperlink ref="B6" r:id="rId5" display="https://www.ache.org/" xr:uid="{CE97D364-485D-4667-B364-BB2D370B83D1}"/>
-    <hyperlink ref="B7" r:id="rId6" display="https://www.mgma.com/" xr:uid="{1D2641C2-5A27-498C-8FDD-3D5E48100E92}"/>
-    <hyperlink ref="B8" r:id="rId7" display="https://www.cms.gov/training-education/medicare-learning-networkr-mln/resources-training/mln-matters-articles" xr:uid="{7ECE03F7-5E0E-42B3-A2E3-43918D0F32D8}"/>
-    <hyperlink ref="B9" r:id="rId8" display="https://www.ismworld.org/" xr:uid="{807CA2EB-D259-4BB9-8F6A-691099A27556}"/>
-    <hyperlink ref="B10" r:id="rId9" display="https://www.himss.org/" xr:uid="{846A2FC2-11CC-4B41-8AAF-6DFAA78AD3FC}"/>
-    <hyperlink ref="B11" r:id="rId10" display="https://www.ihi.org/" xr:uid="{C65DC3B6-4CC8-49F9-BFD6-61C567123CB2}"/>
-    <hyperlink ref="B12" r:id="rId11" display="https://nahq.org/?keyword=nahq&amp;matchtype=e&amp;device=c&amp;lpurl=https%3A%2F%2Fnahq.org%2F&amp;campaign=Microsoft%20-%20NAHQ%20Brand&amp;adgroup=%5Bnahq%5D&amp;msclkid=ca7a19f143d8170f51ee73b72cfceff6&amp;utm_source=bing&amp;utm_medium=cpc&amp;utm_campaign=Microsoft%20-%20NAHQ%20Brand&amp;utm_term=nahq&amp;utm_content=%5Bnahq%5D" xr:uid="{6F464490-87CE-4EE0-A617-14C356DA6FDA}"/>
-    <hyperlink ref="B13" r:id="rId12" xr:uid="{86995982-B5A6-4E8F-8736-0250EFD4BD30}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{B982DB95-FBE9-4EC0-922C-65C6E6EA9513}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{77FD4EF4-07FE-4261-9587-ADC58F010FF2}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{E1BAF727-8FE2-4017-BD4A-18813BC2FB6F}"/>
+    <hyperlink ref="C5" r:id="rId4" display="https://www.hfma.org/revenue-cycle/the-kpis-that-define-revenue-cycle-excellence/" xr:uid="{AFB97646-57E7-4F83-BC49-609EBA49CEA7}"/>
+    <hyperlink ref="C6" r:id="rId5" display="https://www.hfma.org/revenue-cycle/revenue-cycle-strategies-for-hospitals-facing-growing-financial-pressures/" xr:uid="{69CA50DC-862B-40E5-AFFC-43B29F592559}"/>
+    <hyperlink ref="C7" r:id="rId6" xr:uid="{99DF3E2A-53FD-4113-9FE7-CEAA852FB244}"/>
+    <hyperlink ref="C8" r:id="rId7" display="https://www.hfma.org/revenue-cycle/healthcare-providers-debate-ways-to-offer-patients-manageable-payment-options/" xr:uid="{18173A91-DAAE-4F7B-BA01-5E8E7D993389}"/>
+    <hyperlink ref="C9" r:id="rId8" display="https://www.hfma.org/reference/understand-claims-denial-friction/" xr:uid="{A1F1F68D-126E-4C00-9D46-AE3352C8D354}"/>
+    <hyperlink ref="C10" r:id="rId9" display="https://www.hfma.org/revenue-cycle/denials-management/navigating-the-rising-tide-of-denials/" xr:uid="{2CF6B11F-E233-458C-B70D-FC0F2121B5DC}"/>
+    <hyperlink ref="C11" r:id="rId10" display="https://www.hfma.org/revenue-cycle/denials-management/the-impact-of-claims-denials-on-the-financial-health-of-healthcare/" xr:uid="{AEC669AE-C71E-4C5A-8141-88040663F758}"/>
+    <hyperlink ref="C12" r:id="rId11" display="https://www.hfma.org/fast-finance/labor-outsourcing-shifts-to-non-clinical-roles/" xr:uid="{25B073F8-836E-4855-ADD8-A2A064BA7DE6}"/>
+    <hyperlink ref="C13" r:id="rId12" display="https://www.hfma.org/finance-and-business-strategy/why-labor-benchmarking-is-so-critical-to-healthcare-productivity/" xr:uid="{6ED3885E-89C5-4098-815B-89B7C9B25A3E}"/>
+    <hyperlink ref="C14" r:id="rId13" display="https://www.aha.org/guides-and-reports/2026-06-02-making-health-care-more-affordable" xr:uid="{90121FE9-87B7-4F7B-83C8-65DA125D03D4}"/>
+    <hyperlink ref="C15" r:id="rId14" display="https://www.aha.org/case-studies/2026-05-29-examples-how-hospitals-are-lowering-costs-and-enhancing-value" xr:uid="{FA927214-38B9-429E-A9B3-A8076BA89F07}"/>
+    <hyperlink ref="C16" r:id="rId15" display="https://www.aha.org/aha-center-health-innovation-market-scan/2026-01-05-/future-physician-workforce-optimization" xr:uid="{3A2526B7-D746-4D02-8BAA-80D9C22CBE09}"/>
+    <hyperlink ref="C17" r:id="rId16" display="https://www.beckershospitalreview.com/finance/revenue-cycle-management/5-recent-rcm-company-ma-moves/" xr:uid="{2336F0E4-D6BE-4B8F-80E4-CC4570DF336C}"/>
+    <hyperlink ref="C18" r:id="rId17" display="https://www.beckershospitalreview.com/finance/revenue-cycle-management/beyond-the-dashboard-why-the-most-damaging-denials-never-get-flagged/" xr:uid="{96B8AD2D-1B71-42FA-BB2B-0D4EE771A515}"/>
+    <hyperlink ref="C19" r:id="rId18" display="https://www.beckershospitalreview.com/healthcare-information-technology/ehrs/oracle-health-to-bring-ai-to-the-operating-room/" xr:uid="{8B730166-78F4-4E46-8A48-766E986D4590}"/>
+    <hyperlink ref="C20" r:id="rId19" display="https://www.beckershospitalreview.com/healthcare-information-technology/ehrs/will-ai-replace-physicians-epics-judy-faulkner-is-skeptical/" xr:uid="{0C1CEBEF-CE98-4DB5-B0C9-55AFF055DFFC}"/>
+    <hyperlink ref="C21" r:id="rId20" xr:uid="{E0C626A6-627F-4678-9B82-EA51DD8C470F}"/>
+    <hyperlink ref="C22" r:id="rId21" xr:uid="{C01CC20D-252E-4A9D-8A96-CC0A1D71C3B9}"/>
+    <hyperlink ref="C23" r:id="rId22" display="https://www.modernhealthcare.com/providers/mh-supply-chain-silos-amazon-business/" xr:uid="{EF2D6605-3F94-4E1D-B2A2-06F668E5301C}"/>
+    <hyperlink ref="C24" r:id="rId23" display="https://www.modernhealthcare.com/supply-chain/how-supply-chain-innovation-can-drive-efficiency-amid-cost-and-labor-headwinds/" xr:uid="{F1BCEC5C-260A-43D6-B7FB-C58A04305C1A}"/>
+    <hyperlink ref="C25" r:id="rId24" display="https://www.modernhealthcare.com/digital-health/ai-supply-chain-management-hospitals/" xr:uid="{5A3DB292-B129-4FA8-8FEC-FA8A425533AA}"/>
+    <hyperlink ref="C26" r:id="rId25" display="https://www.modernhealthcare.com/opinion/healthcare-consolidation-mergers-private-equity-james-calver/" xr:uid="{A80903FD-DA0C-45E7-88B8-DED70BBAF77A}"/>
+    <hyperlink ref="C27" r:id="rId26" display="https://www.modernhealthcare.com/safety-quality/how-hospitals-quality-improvements-shrinking-margins-leapfrog-group-CMS/" xr:uid="{8F5683F7-44A0-40A0-BDD5-819FA2CAEC17}"/>
+    <hyperlink ref="C28" r:id="rId27" display="https://www.mgma.com/articles/7-essential-components-of-a-high-performing-physician-enterprise" xr:uid="{15015813-0E75-4812-8F2E-55CEF2ABE697}"/>
+    <hyperlink ref="C29" r:id="rId28" display="https://www.mgma.com/articles/4-steps-for-creating-value-in-the-hospital-based-physician-enterprise" xr:uid="{7B3B65FA-DDC0-4EE1-A064-136509B7FD2C}"/>
+    <hyperlink ref="C30" r:id="rId29" display="https://www.mgma.com/articles/optimizing-physician-enterprise-performance-in-the-shift-to-value" xr:uid="{24034F1D-7957-422E-B20D-E246CDA1CD41}"/>
+    <hyperlink ref="C31" r:id="rId30" display="https://www.chartis.com/insights/why-time-has-come-evolve-physician-enterprise-roger-ray-md" xr:uid="{69FED3E0-0791-4AFF-BBA0-A2915D2509F3}"/>
+    <hyperlink ref="C32" r:id="rId31" display="https://nam.edu/perspectives/electronic-health-record-optimization-and-clinician-well-being-a-potential-roadmap-toward-action/" xr:uid="{07BADA26-2C9C-4CF2-BEB5-F009AF27CBA1}"/>
+    <hyperlink ref="C33" r:id="rId32" display="https://www.hfma.org/payment-reimbursement-and-managed-care/medicare-funding-projections-hi-trust-fund/" xr:uid="{726D89DF-6A5D-4470-9C86-DF2EEB69012B}"/>
+    <hyperlink ref="C34" r:id="rId33" display="https://www.hfma.org/payment-reimbursement-and-managed-care/medicare-payment-policy-changes-2027-hhs-hearings/" xr:uid="{B5D39D52-B9B5-4C31-8A2F-2765D05005B8}"/>
+    <hyperlink ref="C35" r:id="rId34" display="https://www.cdw.com/content/cdw/en/articles/digitalworkspace/how-clinical-workflow-optimization-creates-better-patient-outcomes.html?msockid=0a1b6b7b02a56ef323677c1e03966f9a" xr:uid="{66B75B10-FF64-419E-939B-C437F9A121CA}"/>
+    <hyperlink ref="C36" r:id="rId35" display="https://www.aha.org/aha-center-health-innovation-market-scan/2025-12-09-health-care-workforce-system-under-pressure-poised-reinvention" xr:uid="{4D560E3E-BD36-44CC-89D3-48378D5F72ED}"/>
+    <hyperlink ref="C37" r:id="rId36" display="https://www.modernhealthcare.com/politics-regulation/mh-us-health-spending-2034-cms/" xr:uid="{0CF95044-1CCF-4D79-90FC-C8274AC7A960}"/>
+    <hyperlink ref="C38" r:id="rId37" display="https://www.mgma.com/mgma-stat/keeping-your-clinician-productivity-on-track-throughout-2026" xr:uid="{38376598-160E-4122-9B39-6D6C0396A9D4}"/>
+    <hyperlink ref="C39" r:id="rId38" display="https://www.hfma.org/fast-finance/hospital-labor-trends-in-2025-show-slower-hiring-but-continued-workforce-growth/" xr:uid="{9878FDD7-6A47-467B-BA82-C735003F539D}"/>
+    <hyperlink ref="C40" r:id="rId39" display="https://www.hfma.org/how-a-health-system-can-reduce-premium-labor-while-building-a-sustainable-workforce/" xr:uid="{C4A314AA-0428-4FB4-905B-F638097E991C}"/>
+    <hyperlink ref="C41" r:id="rId40" display="https://www.ama-assn.org/practice-management/physician-health/when-health-care-teams-run-short-physician-burnout-rises" xr:uid="{4B625CF2-8597-46BB-998A-E06B2EB07402}"/>
+    <hyperlink ref="C42" r:id="rId41" xr:uid="{50837057-9C4C-459E-86AE-F8A65D62D99C}"/>
+    <hyperlink ref="C43" r:id="rId42" display="https://www.hfma.org/revenue-cycle/billing-and-collections/patient-pos-collections-pose-a-growing-rcm-problem/" xr:uid="{5438FC84-AD73-470B-AF61-E582BCAC9D80}"/>
+    <hyperlink ref="C44" r:id="rId43" display="https://www.hfma.org/revenue-cycle/billing-and-collections/prior-authorization-is-draining-revenue-which-is-why-automation-has-become-a-strategic-imperative/" xr:uid="{CF81E748-8C97-4D64-81B5-0844F2DD2D95}"/>
+    <hyperlink ref="C45" r:id="rId44" xr:uid="{060460A9-7A6E-4F65-ABDA-9E52B839A882}"/>
+    <hyperlink ref="C46" r:id="rId45" display="https://health.usnews.com/medicare/articles/your-guide-to-medicare-coverage" xr:uid="{49CFF0CC-F5ED-4038-AA6D-6C9436662F47}"/>
+    <hyperlink ref="C47" r:id="rId46" display="https://www.congress.gov/crs_external_products/R/PDF/R43357/R43357.21.pdf" xr:uid="{C69D2977-82CC-42D8-8196-CFA240CF9161}"/>
+    <hyperlink ref="C48" r:id="rId47" display="https://www.definitivehc.com/blog/the-difference-between-non-profit-and-for-profit-hospitals" xr:uid="{C4E6D896-AEA2-4156-9B19-157C6C82C422}"/>
+    <hyperlink ref="C49" r:id="rId48" display="https://www.healthcare-brew.com/stories/2025/09/29/difference-between-for-profit-nonprofit-hospitals" xr:uid="{318816D9-A902-4BA1-BF56-7B6F977CB130}"/>
+    <hyperlink ref="C50" r:id="rId49" display="https://www.ihi.org/library/blog/guiding-flock-3-simple-rules-improve-hospital-wide-patient-flow" xr:uid="{44313CC0-A1DA-471F-B790-A20B70405460}"/>
+    <hyperlink ref="C51" r:id="rId50" display="https://www.hfma.org/61738/" xr:uid="{BF46AE86-6158-44F6-B0E4-AA02A1FBB03E}"/>
+    <hyperlink ref="C52" r:id="rId51" display="https://www.kff.org/health-costs/key-facts-about-hospitals/" xr:uid="{CF8BD38B-1E9F-43EB-9F13-BAC58C834AC9}"/>
+    <hyperlink ref="C53" r:id="rId52" display="https://www.definitivehc.com/resources/healthcare-insights/hospital-operating-margins-united-states" xr:uid="{65B14E3D-ED45-4406-A012-E10D29E14174}"/>
+    <hyperlink ref="C54" r:id="rId53" display="https://www.beckershospitalreview.com/finance/from-2-2-to-16-5-36-health-systems-ranked-by-operating-margins-in-2025/" xr:uid="{23C82067-8E3E-4DB0-B203-096266095E3A}"/>
+    <hyperlink ref="C55" r:id="rId54" display="https://www.healthpartners.com/blog/medical-claim/" xr:uid="{3E3FEDC5-2489-438C-ACD2-D525FCD56387}"/>
+    <hyperlink ref="C56" r:id="rId55" display="https://www.medesk.net/en/blog/denial-management/" xr:uid="{592BF7EC-FFCA-4ACE-9148-DD9932CFC814}"/>
+    <hyperlink ref="C57" r:id="rId56" display="https://www.pgmbilling.com/blog/what-is-a-claim-scrubber-and-why-it-matters-more-than-ever/" xr:uid="{914634F4-692F-46C8-8291-E54A6E3331AF}"/>
+    <hyperlink ref="C58" r:id="rId57" display="https://healthcarereaders.com/insights/supply-chain-management-in-healthcare" xr:uid="{68BF8A32-144B-4916-949B-D71B4E67FD13}"/>
+    <hyperlink ref="C59" r:id="rId58" display="https://nihcm.org/publications/the-growth-of-private-equity-in-us-health-care-impact-and-outlook" xr:uid="{87FF73B9-EA0D-400F-A4FE-A372EF35BFDA}"/>
+    <hyperlink ref="C60" r:id="rId59" xr:uid="{E3A2D03F-A3B0-4419-BCC9-83B2A64BF450}"/>
+    <hyperlink ref="C61" r:id="rId60" display="https://www.definitivehc.com/resources/healthcare-insights/breaking-down-us-hospital-payor-mixes" xr:uid="{F056777D-BB12-462E-AFB4-35C81B489660}"/>
+    <hyperlink ref="C62" r:id="rId61" display="https://www.uhc.com/employer/news-strategies/annual-health-trends-report" xr:uid="{448F918A-0272-42AC-8111-FFC5E39012B6}"/>
+    <hyperlink ref="C63" r:id="rId62" display="https://publichealth.jhu.edu/2025/whats-behind-rising-health-insurance-costs" xr:uid="{FE9BDCF8-1682-401C-8799-60F27C681E8F}"/>
+    <hyperlink ref="C64" r:id="rId63" display="https://www.healthmarkets.com/resources/health-insurance/affordable-care-act-pros-and-cons" xr:uid="{3D578AA9-DE86-45F5-9003-740742DB790E}"/>
+    <hyperlink ref="C65" r:id="rId64" display="https://www.sciencedirect.com/science/article/pii/S0168851025001940" xr:uid="{70221E8B-AFC0-4159-94C9-2F06B0F95C1C}"/>
+    <hyperlink ref="C66" r:id="rId65" xr:uid="{78210D35-C927-4D02-93D0-1D002BB79C92}"/>
+    <hyperlink ref="C67" r:id="rId66" display="https://www.hfma.org/payment-reimbursement-and-managed-care/medicare-advantage-hospital-finances/" xr:uid="{06A39705-55DA-49F9-A4B1-A69081CD602C}"/>
+    <hyperlink ref="C68" r:id="rId67" display="https://www.hfma.org/accounting-and-financial-reporting/tax-exempt-hospital-reporting-requirements/" xr:uid="{5B236091-7DC0-4796-9E12-BA36C8B2FEEC}"/>
+    <hyperlink ref="C69" r:id="rId68" display="https://www.hfma.org/finance-and-business-strategy/hospital-drug-supply-costs/" xr:uid="{254AAC4F-0101-4F16-858B-203134B98D2C}"/>
+    <hyperlink ref="C70" r:id="rId69" display="https://www.hfma.org/payment-reimbursement-and-managed-care/contracting/white-house-zooms-in-on-hospital-contracts/" xr:uid="{4C7E1BC4-A0FB-42FC-A389-B3BC9FA33A5A}"/>
+    <hyperlink ref="C71" r:id="rId70" display="https://www.hfma.org/finance-and-business-strategy/healthcare-business-trends/the-hospital-of-the-future-with-jeni-williams/" xr:uid="{3559D1AC-00DD-4329-9C2F-AF32DB0C6A08}"/>
+    <hyperlink ref="C72" r:id="rId71" display="https://www.mgma.com/mgma-stat/stable-staff-to-physician-ratios-might-conceal-real-strain-in-your-practice" xr:uid="{FFE78512-8CFE-4DB0-A12B-63CC54B9F349}"/>
+    <hyperlink ref="C73" r:id="rId72" display="https://www.mgma.com/mgma-stat/revenue-growth-narrows-as-costs-climb-2026-squeeze" xr:uid="{740BC534-C9A0-4AF5-BB43-D0C526E6B8EF}"/>
+    <hyperlink ref="C74" r:id="rId73" display="https://www.mgma.com/mgma-stat/operating-costs-keep-climbing-for-medical-practices-in-2026" xr:uid="{7BE272E5-7AF4-4ECA-8513-C295270F72DD}"/>
+    <hyperlink ref="C75" r:id="rId74" display="https://www.mgma.com/mgma-stat/worker-benefits-where-retention-tools-meet-cost-pressure" xr:uid="{08F9AC08-815A-45A8-B58B-A3BDF2042DE6}"/>
+    <hyperlink ref="C76" r:id="rId75" display="https://www.mgma.com/articles/why-change-fails-in-medical-groups" xr:uid="{7D524D0A-460E-4DF2-97D7-BE22E57AD724}"/>
+    <hyperlink ref="C77" r:id="rId76" display="https://www.mgma.com/articles/designing-backfill-and-overbooking-by-specialty" xr:uid="{9B047851-BA08-4FE7-A9EC-40B367CE9084}"/>
+    <hyperlink ref="C78" r:id="rId77" display="https://www.kff.org/affordable-care-act/in-preliminary-rate-filings-aca-marketplace-insurers-largely-propose-double-digit-premium-increase-for-2027-following-a-steep-climb-this-year/" xr:uid="{95970B99-88DE-4B77-87D9-347DC113D924}"/>
+    <hyperlink ref="C79" r:id="rId78" display="https://www.kff.org/affordable-care-act/the-average-marketplace-deductible-grew-by-about-1000-per-person-in-2026-with-more-enrollees-shifting-to-higher-deductible-plans-as-enhanced-tax-credits-expired/" xr:uid="{F209C121-3B24-4230-B410-B0302E889464}"/>
+    <hyperlink ref="C80" r:id="rId79" display="https://www.kff.org/quick-insights/aca-marketplace-enrollment-is-down-by-3-million-after-big-jump-in-premium-payments/" xr:uid="{2AF6E803-CBA7-4B2B-9CB1-D02763DAAD8E}"/>
+    <hyperlink ref="C81" r:id="rId80" display="https://www.kff.org/health-costs/did-the-affordable-care-act-make-health-care-more-affordable/" xr:uid="{7BF8D13A-1412-481E-BF77-ECF0C5762002}"/>
+    <hyperlink ref="C82" r:id="rId81" display="https://www.kff.org/affordable-care-act/health-policy-101-the-affordable-care-act/" xr:uid="{8954F661-F310-4383-A271-A3B6083998C3}"/>
+    <hyperlink ref="C83" r:id="rId82" display="https://www.kff.org/health-costs/health-care-costs-keep-rising-why-and-who-pays/" xr:uid="{8AF914E6-E79E-49F5-8AFD-6F5BB9AAD1AF}"/>
+    <hyperlink ref="C84" r:id="rId83" display="https://www.kff.org/public-opinion/kff-health-tracking-poll-health-care-costs-and-the-midterms/" xr:uid="{1FBAD32A-EE4F-478A-9072-5F66C9110B7C}"/>
+    <hyperlink ref="C85" r:id="rId84" display="https://www.kff.org/health-costs/americans-challenges-with-health-care-costs/" xr:uid="{0835179D-699D-4646-9219-BCF3EE566F73}"/>
+    <hyperlink ref="C86" r:id="rId85" display="https://www.kff.org/health-costs/hospital-prices-have-risen-much-faster-for-private-insurance-than-medicare-since-2019/" xr:uid="{11B64026-B65B-4035-8D20-06B2616B3EA0}"/>
+    <hyperlink ref="C87" r:id="rId86" display="https://www.kff.org/health-costs/long-term-trends-in-employer-based-coverage/" xr:uid="{53DE45B8-B36B-48C1-8A56-2962301916DA}"/>
+    <hyperlink ref="C88" r:id="rId87" display="https://www.kff.org/patient-consumer-protections/policy-changes-bring-renewed-focus-on-high-deductible-health-plans/" xr:uid="{47351567-3580-473F-904C-B5A02F1B0E27}"/>
+    <hyperlink ref="C89" r:id="rId88" display="https://www.kff.org/health-costs/what-your-employer-based-health-coverage-really-costs/" xr:uid="{5492A1D3-EF9B-44EC-890B-BFD879A99B79}"/>
+    <hyperlink ref="C90" r:id="rId89" display="https://kffhealthnews.org/syndicate/long-term-care-costs-washington-state-payroll-option/" xr:uid="{E5E7EA74-3A13-45DC-807E-2C39C18FA09E}"/>
+    <hyperlink ref="B91" r:id="rId90" display="https://www.beckershospitalreview.com/finance/9-healthcare-bankruptcies-in-2026/" xr:uid="{4C7F5159-7C11-43CE-96A7-30E0E05D301B}"/>
+    <hyperlink ref="C91" r:id="rId91" display="https://www.beckershospitalreview.com/finance/9-healthcare-bankruptcies-in-2026/" xr:uid="{C0F1765B-90E7-4737-95E5-EDEAB043CB8A}"/>
+    <hyperlink ref="C92" r:id="rId92" display="https://www.beckershospitalreview.com/finance/hospital-margins-dip-to-2-9-average-as-expenses-grow-care-shifts-5-notes/" xr:uid="{2288C69D-2BC6-4042-88A1-1098651BE84E}"/>
+    <hyperlink ref="C93" r:id="rId93" display="https://www.beckershospitalreview.com/finance/the-term-payvider-makes-no-sense/" xr:uid="{BDB8C796-1019-4121-9F6C-F5AB08FA4A00}"/>
+    <hyperlink ref="C94" r:id="rId94" display="https://www.beckershospitalreview.com/finance/the-medicaid-squeeze-hospitals-cant-lobby-their-way-out-of/" xr:uid="{8C8318B2-32AD-4012-9AC0-FE729638B842}"/>
+    <hyperlink ref="C95" r:id="rId95" display="https://www.beckershospitalreview.com/healthcare-information-technology/ai/anthropics-claude-now-handles-healthcare-claims-care-management/" xr:uid="{CC7DEE30-3791-4535-86A1-2DCF199A6128}"/>
+    <hyperlink ref="C96" r:id="rId96" display="https://www.beckershospitalreview.com/healthcare-information-technology/ehrs/7-health-systems-moving-to-epic/" xr:uid="{3D8BDDF9-443A-44E7-93C2-42524C36BB97}"/>
+    <hyperlink ref="C97" r:id="rId97" display="https://edhub.ama-assn.org/steps-forward/audio-player/19032227?resultClick=1&amp;bypassSolrId=M_19032227" xr:uid="{4D8873B9-4680-4CF8-BF0E-E71871B1EABE}"/>
+    <hyperlink ref="C98" r:id="rId98" display="https://edhub.ama-assn.org/steps-forward/module/2844245?resultClick=1&amp;bypassSolrId=J_2844245" xr:uid="{96BA98DF-EC43-4DF1-B2FE-470B601ED37E}"/>
+    <hyperlink ref="C99" r:id="rId99" display="https://edhub.ama-assn.org/steps-forward/module/2781026?resultClick=1&amp;bypassSolrId=J_2781026" xr:uid="{F9943495-16D0-4890-920A-451B4BD5FB92}"/>
+    <hyperlink ref="C100" r:id="rId100" display="https://pmc.ncbi.nlm.nih.gov/articles/PMC10517477/" xr:uid="{B0184DD7-B152-4874-80EB-88A2AB606DD0}"/>
+    <hyperlink ref="C101" r:id="rId101" display="https://mayomagazine.mayoclinic.org/2026/04/ai-in-healthcare/" xr:uid="{C1240FFA-CAC6-49A2-BF9F-524C9F26FE7B}"/>
+    <hyperlink ref="C102" r:id="rId102" display="https://www.weforum.org/stories/health-and-healthcare-systems/ai-transforming-global-health/" xr:uid="{428F3DF0-A3A6-4C2F-B5B2-D88DB17F0A85}"/>
+    <hyperlink ref="C103" r:id="rId103" display="https://www.healthcaredive.com/spons/flipping-the-script-on-payer-denials-and-downcoding/824302/" xr:uid="{49F16536-227C-4254-A33E-E3622EEE0BC8}"/>
+    <hyperlink ref="C104" r:id="rId104" display="https://www.beckershospitalreview.com/finance/revenue-cycle-management/what-the-revenue-cycle-leaders-of-2030-will-know/" xr:uid="{53119244-DAA0-4B06-833B-1762966E5612}"/>
+    <hyperlink ref="C105" r:id="rId105" display="https://www.healthcaredive.com/spons/how-healthcare-ai-is-closing-the-revenue-gap/822195/" xr:uid="{03E774A3-278E-449A-8E64-7F75E033FC72}"/>
+    <hyperlink ref="C106" r:id="rId106" display="https://www.healthcaredive.com/news/himss-2026-takeaways-ai-innovation-agents-cybersecurity-governance-interoperability/814812/" xr:uid="{A34B8F48-E66E-4AC6-A388-558CA7A2D245}"/>
+    <hyperlink ref="C107" r:id="rId107" display="https://www.verywellhealth.com/health-insurance-for-multiple-states-4584359" xr:uid="{512E99DB-81FB-490E-A27C-B368DD14D8CC}"/>
+    <hyperlink ref="C108" r:id="rId108" display="https://www.hfma.org/technology/how-to-protect-revenue-in-a-digital-first-ecosystem/" xr:uid="{3A423EEB-CB75-485B-861F-8B93C1AD9DB1}"/>
+    <hyperlink ref="C109" r:id="rId109" display="https://www.hfma.org/technology/healthcare-revenue-cycle-transformation-three-priorities/" xr:uid="{30E0AFF3-5EA6-4CD1-94FB-905B6920D88B}"/>
+    <hyperlink ref="C110" r:id="rId110" display="https://www.hfma.org/technology/why-ai-alone-fails-in-healthcare-and-how-ai-human-co-management-drives-better-outcomes/" xr:uid="{DAE47884-B51E-4638-97B9-457EC83E1C8E}"/>
+    <hyperlink ref="C111" r:id="rId111" display="https://www.hfma.org/technology/medicare-claims-processing-modernization-cms/" xr:uid="{65E616D8-AEB8-435C-9AA4-22BB62F22DBC}"/>
+    <hyperlink ref="C112" r:id="rId112" display="https://www.hfma.org/revenue-cycle/modernize-your-operations-model-for-rcm-success/" xr:uid="{580A493E-9B72-438E-B317-4327030E645C}"/>
+    <hyperlink ref="C113" r:id="rId113" display="https://www.hfma.org/legal-and-regulatory-compliance/compliance/healthcare-fraud-compliance-cms-oversight/" xr:uid="{8A98ABB0-159B-4E33-A69F-A430692AAD6E}"/>
+    <hyperlink ref="C114" r:id="rId114" display="https://www.hfma.org/finance-and-business-strategy/building-a-more-effective-remittance-automation-strategy/" xr:uid="{970F056F-D30E-4B09-9450-32F576583FBC}"/>
+    <hyperlink ref="C115" r:id="rId115" display="https://www.hfma.org/finance-and-business-strategy/healthcare-affordability-financial-sustainability/" xr:uid="{554E107D-F704-49E5-BF8B-50FDB9FBEB3D}"/>
+    <hyperlink ref="C116" r:id="rId116" display="https://www.healthcaredive.com/news/tracking-healthcare-data-breaches-cybersecurity-hacking-hospitals/696184/" xr:uid="{5371A869-8E44-4A35-B84F-FABECC1C3C04}"/>
+    <hyperlink ref="C117" r:id="rId117" display="https://www.healthcaredive.com/news/affordable-care-act-premium-increase-2027-kff-peterson-center-healthcare/824695/" xr:uid="{B6F77715-FFAA-4275-B867-26D25D34D831}"/>
+    <hyperlink ref="C118" r:id="rId118" display="https://www.healthcaredive.com/news/epic-president-sumit-rana-step-down/824462/" xr:uid="{BA68F5CC-4C7D-4911-8AC0-EBC10B41F5DF}"/>
+    <hyperlink ref="C119" r:id="rId119" display="https://www.healthcaredive.com/news/adapthealth-discloses-patient-data-was-stolen-in-cyberattack/824601/" xr:uid="{7F1E13A2-B5AF-4522-89EA-756A9719C6EE}"/>
+    <hyperlink ref="C120" r:id="rId120" display="https://www.healthcaredive.com/news/private-equity-firms-may-skirt-healthcare-oversight-joint-ventures-nonprofits-pesp/824556/" xr:uid="{FA009102-A1D7-4124-828F-BD5E7558FB0C}"/>
+    <hyperlink ref="C121" r:id="rId121" display="https://www.healthcaredive.com/news/healthcare-faces-congressional-oversight-2026-midterms/824526/" xr:uid="{D90293DD-2974-4A65-A037-88E4FDC22785}"/>
+    <hyperlink ref="C122" r:id="rId122" display="https://www.healthcaredive.com/news/medicare-glp1-bridge-four-million-eligible-kff/824126/" xr:uid="{97E3F2B1-1C76-4584-BA72-374986F07B80}"/>
+    <hyperlink ref="C123" r:id="rId123" display="https://www.healthcaredive.com/news/us-health-spending-spikes-57t-2025/823660/" xr:uid="{F2000854-73E7-459F-9A02-7E24ADD05B01}"/>
+    <hyperlink ref="C124" r:id="rId124" display="https://www.healthcaredive.com/news/hackensack-meridian-hunterdon-explore-merger-nj-hospitals/823489/" xr:uid="{7C54EBAA-8A0E-4EC2-8235-6F2C0C3199EC}"/>
+    <hyperlink ref="C125" r:id="rId125" display="https://www.healthcaredive.com/news/centene-offers-employee-buyouts-membership-losses/823005/" xr:uid="{47565002-B618-4D8D-A378-2F0CF6B53B4F}"/>
+    <hyperlink ref="C126" r:id="rId126" display="https://www.healthaffairs.org/content/forefront/three-federal-streams-one-governance-problem-building-unified-ai-oversight-health" xr:uid="{EEFE2BB1-253E-4A5C-BA8E-49D7F45A6476}"/>
+    <hyperlink ref="C127" r:id="rId127" display="https://www.healthaffairs.org/content/forefront/medical-ethics-responds-private-equity" xr:uid="{981E0006-F1FB-4D04-8893-779D5F8F62B4}"/>
+    <hyperlink ref="C128" r:id="rId128" display="https://www.healthaffairs.org/doi/10.1377/hlthaff.2025.01325" xr:uid="{90091F37-B8BD-4BFC-A019-906839FABFB8}"/>
+    <hyperlink ref="C129" r:id="rId129" display="https://www.healthaffairs.org/content/forefront/states-exceeding-their-health-care-cost-growth-targets-does-mean" xr:uid="{07B09092-E3BB-4060-80CB-4D88E106A619}"/>
+    <hyperlink ref="C130" r:id="rId130" display="https://www.healthaffairs.org/content/forefront/why-new-drugs-and-ai-chatbots-won-t-cure-health-care-s-cost-disease" xr:uid="{4F073D69-1937-4F8D-8868-0CBA2A6219A7}"/>
+    <hyperlink ref="C131" r:id="rId131" display="https://www.healthaffairs.org/doi/10.1377/hlthaff.2026.00749" xr:uid="{3FAA25BD-2508-45E7-9827-E195A9CE2164}"/>
+    <hyperlink ref="C132" r:id="rId132" display="https://www.healthaffairs.org/content/forefront/cost-effectiveness-thresholds-overvaluing-innovation-undervaluing-health" xr:uid="{EC5E9BE7-5C6E-4049-A64D-C590235C2176}"/>
+    <hyperlink ref="C133" r:id="rId133" display="https://www.healthaffairs.org/content/forefront/levels-growth-and-semantics-role-prices-driving-health-care-spending" xr:uid="{1DD36C96-2124-485D-B38E-FD12539A44C2}"/>
+    <hyperlink ref="C134" r:id="rId134" display="https://www.healthaffairs.org/content/forefront/medicare-s-unrealized-opportunity-using-acos-create-real-competition" xr:uid="{A1AD029D-39C2-4AF6-8D1D-D213C93D7D93}"/>
+    <hyperlink ref="C135" r:id="rId135" display="https://www.healthaffairs.org/content/forefront/us-health-spending-problem-still-prices" xr:uid="{28D17A2C-13E5-42A2-BFB6-0A65FD4FFB24}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId13"/>
+    <tablePart r:id="rId136"/>
   </tableParts>
 </worksheet>
 </file>